--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -655,7 +655,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -759,7 +760,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -1192,7 +1194,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing → </t>
+            <t xml:space="preserve">repeatability uses non-standard phrasing
+</t>
           </r>
           <r>
             <rPr>
@@ -1287,7 +1290,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing → </t>
+            <t xml:space="preserve">repeatability uses non-standard phrasing
+</t>
           </r>
           <r>
             <rPr>
@@ -1381,50 +1385,7 @@
         <v>2</v>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">description → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>The first of three intensive courses that introduce students to the inner workings of European art music of the 18th and 19th centuries. This course covers diatonic harmony, as well as part-writing, voice-leading, and harmonization techniques.</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">outcomes, from the syllabus → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Read, write, and analyze the fundamental materials of tonal music using correct terminology and nomenclature. 2. Construct and identify all triad and seventh chord types in root position and inversion. 3. Write four-part (SATB) harmonic progressions using I, V, V⁷, and their inversions, applying basic voice-leading principles. 4. Compose and analyze two-voice counterpoint through fourth species. 5. Apply theoretical concepts at the keyboard and in performance on the student's primary instrument or voice.</t>
-          </r>
-        </is>
-      </c>
+      <c r="U10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1504,50 +1465,7 @@
         <v>2</v>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">description → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>The second of three intensive courses that introduce students to the inner workings of European art music of the 18th and 19th centuries. This course completes diatonic harmony and introduces advanced part-writing, voice-leading, and harmonization techniques.</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">outcomes, from the syllabus → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Write and analyze SATB progressions using the full vocabulary of diatonic harmony, including all diatonic triads and seventh chords. 2. Identify and apply embellishing chords, the cadential 6/4, and other 6/4 chord types in functional context. 3. Recognize and compose diatonic sequences. 4. Analyze tonal works using Roman numerals, figured bass, and functional labels. 5. Apply diatonic harmonic vocabulary at the keyboard and in performance on the student's primary instrument or voice.</t>
-          </r>
-        </is>
-      </c>
+      <c r="U11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1629,7 +1547,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">requires MUS 118A, renumbered or discontinued → </t>
+            <t xml:space="preserve">requires MUS 118A, renumbered or discontinued
+</t>
           </r>
           <r>
             <rPr>
@@ -1645,15 +1564,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-05-05, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">
+last revised 2016-05-05, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -1673,16 +1586,35 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcomes, from the syllabus → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Sight-sing diatonic melodies in major keys and simple meters using solfège or scale degrees, with accurate pitch, rhythm, and conducting. 2. Take melodic and rhythmic dictation in simple meters, notating pitch and rhythm accurately, including ties and the dotted beat. 3. Detect and correct errors in performed and notated examples. 4. Read fluently across all fifteen major keys.</t>
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>First of three concurrent aural skills courses. Sight-singing and dictation of diatonic melodies in major keys and simple meters, rhythmic and pitch notation, error detection, and fluency across all fifteen major keys.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+description is identical to the other courses in its track, so the levels are indistinguishable in the catalog
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>see the proposed description above</t>
           </r>
         </is>
       </c>
@@ -1771,7 +1703,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">requires MUS 118B, renumbered or discontinued → </t>
+            <t xml:space="preserve">requires MUS 118B, renumbered or discontinued
+</t>
           </r>
           <r>
             <rPr>
@@ -1787,15 +1720,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-05-05, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">
+last revised 2016-05-05, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -1815,16 +1742,35 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcomes, from the syllabus → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Sight-sing diatonic melodies in minor mode, approached through both relative and parallel major and including chromatic 6 and 7 by modal borrowing, and in compound meters, using solfège or scale degrees. 2. Take melodic and rhythmic dictation extending to triplets and duplets, quadruple division in simple meter, sextuple division in compound meter, and syncopation. 3. Perform lower chromatic neighbors and melodic skips to chord tones as prefix neighbors through the tonic, dominant, and subdominant triads. 4. Sing the dominant seventh chord in melodic context.</t>
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Second of three concurrent aural skills courses. Sight-singing and dictation in minor mode through relative and parallel major, compound meters, chromatic neighbors and skips to chord tones, triplets and syncopation, and the dominant seventh in melodic context.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+description is identical to the other courses in its track, so the levels are indistinguishable in the catalog
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>see the proposed description above</t>
           </r>
         </is>
       </c>
@@ -1911,16 +1857,35 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcomes, from the syllabus → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Perform major and minor five-finger patterns and their triads in all common keys. 2. Perform all four triad qualities (major, minor, augmented, diminished) in root position. 3. Play major scales in tetrachord position with correct fingering, and use the damper pedal. 4. Harmonize simple melodies using basic diatonic chords. 5. Sight-read short examples in grand staff at a basic level.</t>
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>First of three concurrent keyboard courses for music majors. Major and minor five-finger patterns and their triads, all four triad qualities, major scales in tetrachord position, damper pedal, and basic sight-reading and harmonization.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+description is identical to the other courses in its track, so the levels are indistinguishable in the catalog
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>see the proposed description above</t>
           </r>
         </is>
       </c>
@@ -2010,16 +1975,35 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcomes, from the syllabus → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Perform major and minor scales and arpeggios across Group 1 and Group 2 keys, two octaves. 2. Play triads in all inversions and perform the dominant seventh chord in block and broken patterns. 3. Harmonize short melodies using primary chords (I, IV, V⁷) in major and minor, with idiomatic accompaniment patterns including Alberti and waltz bass. 4. Sing a melody while playing a two-hand accompaniment. 5. Realize basic lead-sheet symbols and Roman numerals at the keyboard. 6. Sight-read in grand staff, hands together, in four-to-eight-bar examples.</t>
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Second of three concurrent keyboard courses for music majors. Major and minor scales and arpeggios across the first two key groups, primary chords in block and broken patterns, melodic harmonization, lead-sheet realization, and hands-together sight-reading.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+description is identical to the other courses in its track, so the levels are indistinguishable in the catalog
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>see the proposed description above</t>
           </r>
         </is>
       </c>
@@ -2283,7 +2267,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">classified C09 large group where MUS 111 and MUS 112 are C10 small group → </t>
+            <t xml:space="preserve">classified C09 large group where MUS 111 and MUS 112 are C10 small group
+</t>
           </r>
           <r>
             <rPr>
@@ -2296,50 +2281,7 @@
           </r>
         </is>
       </c>
-      <c r="U18" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">description → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>The last of three intensive courses that introduce students to the inner workings of European art music of the 18th and 19th centuries. This course covers chromatic harmony, tonicization and modulation, and other advanced tonal procedures.</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">outcomes, from the syllabus → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Write and analyze chromatic harmony, including applied dominants, modal mixture, the Neapolitan sixth, augmented sixth chords, and altered chords. 2. Identify and compose modulations to the dominant and to closely related keys. 3. Analyze chromatic sequences and chromatic modulation. 4. Evaluate tonal works combining diatonic and chromatic vocabulary in extended harmonic contexts. 5. Apply chromatic harmonic vocabulary at the keyboard and in performance on the student's primary instrument or voice.</t>
-          </r>
-        </is>
-      </c>
+      <c r="U18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -2425,7 +2367,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-05-10, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-05-10, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -2445,16 +2388,17 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcomes, from the syllabus → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Sing and hear harmonically, following harmonic rhythm and cadences. 2. Work in two-voice textures and take bass-line dictation. 3. Identify root-position and first-inversion triads and all four triad qualities by ear, and sing melodic skips through every diatonic triad (leading-tone, supertonic, submediant, and mediant). 4. Handle the dominant seventh chord in harmonic context, with the voice-leading techniques that close the lower-division sequence.</t>
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Third of three concurrent aural skills courses. Harmonic listening and dictation: harmonic rhythm and cadences, two-voice textures, bass-line dictation, triad quality and inversion by ear, and melodic skips through every diatonic triad.</t>
           </r>
         </is>
       </c>
@@ -2544,16 +2488,35 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcomes, from the syllabus → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Perform major and minor scales and arpeggios across all key groups, and play chromatic, whole-tone, and blues scales. 2. Perform secondary triads (ii, iii, vi) and seventh chords in harmonic context, with correct voice leading. 3. Play melodies and accompaniments in all six church modes. 4. Harmonize melodies using the full diatonic vocabulary including secondary chords. 5. Transpose short examples to other keys and improvise within defined modal and harmonic frameworks. 6. Prepare and perform repertoire from Alfred's Book 1 for peers and instructor.</t>
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Third of three concurrent keyboard courses for music majors. Scales and arpeggios in all key groups, secondary triads and seventh chords in harmonic context, chromatic, whole-tone, and blues scales, and playing in all six church modes.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+description is identical to the other courses in its track, so the levels are indistinguishable in the catalog
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>see the proposed description above</t>
           </r>
         </is>
       </c>
@@ -2922,7 +2885,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-05-01, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-05-01, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -3014,7 +2978,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-05-01, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-05-01, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -3194,7 +3159,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">repeat cap of 4 units where the individual lower division applied norm is 8 → </t>
+            <t xml:space="preserve">repeat cap of 4 units where the individual lower division applied norm is 8
+</t>
           </r>
           <r>
             <rPr>
@@ -3214,7 +3180,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -3317,7 +3284,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">prerequisite of MUS 111 where MUS 262G and MUS 263G require none → </t>
+            <t xml:space="preserve">prerequisite of MUS 111 where MUS 262G and MUS 263G require none
+</t>
           </r>
           <r>
             <rPr>
@@ -3417,7 +3385,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -3516,7 +3485,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcomes 1 and 2 are merged into a single numbered item → </t>
+            <t xml:space="preserve">outcomes 1 and 2 are merged into a single numbered item
+</t>
           </r>
           <r>
             <rPr>
@@ -3614,7 +3584,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description runs to 46 words, over the 40-word limit → </t>
+            <t xml:space="preserve">description runs to 46 words, over the 40-word limit
+</t>
           </r>
           <r>
             <rPr>
@@ -3634,7 +3605,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -3650,15 +3622,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">outcome 3 names the violin in a course covering violin, viola, cello, bass, guitar, and harp → </t>
+            <t xml:space="preserve">
+outcome 3 names the violin in a course covering violin, viola, cello, bass, guitar, and harp
+</t>
           </r>
           <r>
             <rPr>
@@ -3837,7 +3803,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description runs to 45 words, over the 40-word limit → </t>
+            <t xml:space="preserve">description runs to 45 words, over the 40-word limit
+</t>
           </r>
           <r>
             <rPr>
@@ -3857,7 +3824,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -3873,15 +3841,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">outcome 3 names the flute in a course covering flute, clarinet, oboe, bassoon, and saxophone → </t>
+            <t xml:space="preserve">
+outcome 3 names the flute in a course covering flute, clarinet, oboe, bassoon, and saxophone
+</t>
           </r>
           <r>
             <rPr>
@@ -3979,7 +3941,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -4077,7 +4040,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">repeat cap of 4 units where the individual lower division applied norm is 8 → </t>
+            <t xml:space="preserve">repeat cap of 4 units where the individual lower division applied norm is 8
+</t>
           </r>
           <r>
             <rPr>
@@ -4097,7 +4061,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -4278,7 +4243,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-05-09, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-05-09, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -4294,15 +4260,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">classified S36 where other studio courses are C36 → </t>
+            <t xml:space="preserve">
+classified S36 where other studio courses are C36
+</t>
           </r>
           <r>
             <rPr>
@@ -4318,48 +4278,36 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">fixed at 1 unit, so a junior or senior recitalist cannot enroll in the 2 units the handbook requires in the recital semester → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set units to 1-2</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no credit restriction published, though the handbook states coaching units do not count toward graduation requirements → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>add the credit restriction: Units may not be used towards the Music Major or Minor.</t>
+            <t xml:space="preserve">
+fixed at 1 unit, so a recitalist cannot enroll in the 2 units the handbook requires in the recital semester
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set units to 1–2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+no credit restriction published, though the handbook states coaching units do not count toward graduation requirements
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>add: Units may not be used towards the Music Major or Minor.</t>
           </r>
         </is>
       </c>
@@ -4370,7 +4318,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -4386,15 +4335,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">outcomes are the generic applied study set and outcome 2 addresses tone production on the primary instrument → </t>
+            <t xml:space="preserve">
+outcomes are the generic applied study set, and outcome 2 addresses tone production on the primary instrument
+</t>
           </r>
           <r>
             <rPr>
@@ -4496,7 +4439,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-05-09, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-05-09, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -4512,15 +4456,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">classified S36 where other studio courses are C36 → </t>
+            <t xml:space="preserve">
+classified S36 where other studio courses are C36
+</t>
           </r>
           <r>
             <rPr>
@@ -4536,48 +4474,36 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">fixed at 1 unit, so a junior or senior recitalist cannot enroll in the 2 units the handbook requires in the recital semester → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set units to 1-2</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no credit restriction published, though the handbook states coaching units do not count toward graduation requirements → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>add the credit restriction: Units may not be used towards the Music Major or Minor.</t>
+            <t xml:space="preserve">
+fixed at 1 unit, so a recitalist cannot enroll in the 2 units the handbook requires in the recital semester
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set units to 1–2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+no credit restriction published, though the handbook states coaching units do not count toward graduation requirements
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>add: Units may not be used towards the Music Major or Minor.</t>
           </r>
         </is>
       </c>
@@ -4588,7 +4514,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -4604,15 +4531,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">outcomes are the generic applied study set and outcome 2 addresses tone production on the primary instrument → </t>
+            <t xml:space="preserve">
+outcomes are the generic applied study set, and outcome 2 addresses tone production on the primary instrument
+</t>
           </r>
           <r>
             <rPr>
@@ -5071,7 +4992,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description runs to 43 words, over the 40-word limit → </t>
+            <t xml:space="preserve">description runs to 43 words, over the 40-word limit
+</t>
           </r>
           <r>
             <rPr>
@@ -5087,15 +5009,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">reclassification pending per the theory and musicianship guide, effective fall 2027 → </t>
+            <t xml:space="preserve">
+reclassification pending per the theory and musicianship guide, effective fall 2027
+</t>
           </r>
           <r>
             <rPr>
@@ -5115,7 +5031,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -5125,30 +5042,6 @@
               <sz val="10"/>
             </rPr>
             <t>Analysis of style and structural form in European art music of the 18th and 19th centuries. Topics include phrase and sentence structure, thematic organization, binary and ternary forms, variation and rondo forms, slow movement forms, and sonata forms.</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">outcomes, from the syllabus → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Demonstrate understanding of the forms used in tonal music, including sentence, period, binary, ternary, rondo, and sonata forms. 2. Analyze and evaluate complete tonal works in their technical, aesthetic, and historical contexts, supporting interpretive claims with evidence from the score. 3. Apply the harmonic and contrapuntal knowledge of the lower-division sequence to extended musical works. 4. Identify phrase structure, hypermeter, and formal boundaries both visually and aurally. 5. Construct written analyses using appropriate terminology, Roman numerals, figured bass, and formal labels. 6. Implement the principles and concepts studied in class via performance on the student's major instrument or voice.</t>
           </r>
         </is>
       </c>
@@ -5235,7 +5128,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description runs to 42 words, over the 40-word limit → </t>
+            <t xml:space="preserve">description runs to 42 words, over the 40-word limit
+</t>
           </r>
           <r>
             <rPr>
@@ -5255,7 +5149,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -5568,7 +5463,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -5656,7 +5552,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no learning outcomes published → </t>
+            <t xml:space="preserve">no learning outcomes published
+</t>
           </r>
           <r>
             <rPr>
@@ -5672,15 +5569,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing → </t>
+            <t xml:space="preserve">
+repeatability uses non-standard phrasing
+</t>
           </r>
           <r>
             <rPr>
@@ -5700,7 +5591,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no outcomes published → </t>
+            <t xml:space="preserve">no outcomes published
+</t>
           </r>
           <r>
             <rPr>
@@ -5792,7 +5684,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -5808,15 +5701,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-02-18, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">
+last revised 2016-02-18, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -5908,7 +5795,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -6003,7 +5891,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">units publish as 3 where the record holds 2 → </t>
+            <t xml:space="preserve">units publish as 3 where the record holds 2
+</t>
           </r>
           <r>
             <rPr>
@@ -6019,15 +5908,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-04-26, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">
+last revised 2016-04-26, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -6043,15 +5926,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">units publish as 3 where the record holds 2 → </t>
+            <t xml:space="preserve">
+units publish as 3 where the record holds 2
+</t>
           </r>
           <r>
             <rPr>
@@ -6148,7 +6025,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing → </t>
+            <t xml:space="preserve">repeatability uses non-standard phrasing
+</t>
           </r>
           <r>
             <rPr>
@@ -6246,7 +6124,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -6346,7 +6225,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">title published as Band: Wind Ensemble where the handbook names the ensemble East Bay Wind Symphony → </t>
+            <t xml:space="preserve">title published as Band: Wind Ensemble where the handbook names the ensemble East Bay Wind Symphony
+</t>
           </r>
           <r>
             <rPr>
@@ -6366,7 +6246,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -6465,7 +6346,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -6560,7 +6442,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing → </t>
+            <t xml:space="preserve">repeatability uses non-standard phrasing
+</t>
           </r>
           <r>
             <rPr>
@@ -6580,7 +6463,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -6679,7 +6563,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing → </t>
+            <t xml:space="preserve">repeatability uses non-standard phrasing
+</t>
           </r>
           <r>
             <rPr>
@@ -6695,15 +6580,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">grading A-F or CR/NC (student choice) where the chamber ensemble norm is A-F or CR/NC (student choice) → </t>
+            <t xml:space="preserve">
+grading A-F or CR/NC (student choice) where the chamber ensemble norm is A-F or CR/NC (student choice)
+</t>
           </r>
           <r>
             <rPr>
@@ -6798,7 +6677,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">repeat cap of 6 units where the chamber ensemble norm is 8 → </t>
+            <t xml:space="preserve">repeat cap of 6 units where the chamber ensemble norm is 8
+</t>
           </r>
           <r>
             <rPr>
@@ -6814,15 +6694,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">grading A-F grading only where the chamber ensemble norm is A-F or CR/NC (student choice) → </t>
+            <t xml:space="preserve">
+grading A-F grading only where the chamber ensemble norm is A-F or CR/NC (student choice)
+</t>
           </r>
           <r>
             <rPr>
@@ -6842,7 +6716,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -6936,7 +6811,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-05-12, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-05-12, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -6952,15 +6828,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">repeat cap of 4 units where the chamber ensemble norm is 8 → </t>
+            <t xml:space="preserve">
+repeat cap of 4 units where the chamber ensemble norm is 8
+</t>
           </r>
           <r>
             <rPr>
@@ -6976,15 +6846,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">grading A-F grading only where the chamber ensemble norm is A-F or CR/NC (student choice) → </t>
+            <t xml:space="preserve">
+grading A-F grading only where the chamber ensemble norm is A-F or CR/NC (student choice)
+</t>
           </r>
           <r>
             <rPr>
@@ -7004,7 +6868,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -7098,7 +6963,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">grading A-F grading only where the chamber ensemble norm is A-F or CR/NC (student choice) → </t>
+            <t xml:space="preserve">grading A-F grading only where the chamber ensemble norm is A-F or CR/NC (student choice)
+</t>
           </r>
           <r>
             <rPr>
@@ -7118,7 +6984,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -7212,7 +7079,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description runs to 41 words, over the 40-word limit → </t>
+            <t xml:space="preserve">description runs to 41 words, over the 40-word limit
+</t>
           </r>
           <r>
             <rPr>
@@ -7228,15 +7096,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing → </t>
+            <t xml:space="preserve">
+repeatability uses non-standard phrasing
+</t>
           </r>
           <r>
             <rPr>
@@ -7256,7 +7118,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -7352,7 +7215,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-05-12, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-05-12, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -7368,15 +7232,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">repeat cap of 4 units where the chamber ensemble norm is 8 → </t>
+            <t xml:space="preserve">
+repeat cap of 4 units where the chamber ensemble norm is 8
+</t>
           </r>
           <r>
             <rPr>
@@ -7396,7 +7254,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -7492,7 +7351,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">repeat cap of 6 units where the chamber ensemble norm is 8 → </t>
+            <t xml:space="preserve">repeat cap of 6 units where the chamber ensemble norm is 8
+</t>
           </r>
           <r>
             <rPr>
@@ -7508,15 +7368,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">grading A-F grading only where the chamber ensemble norm is A-F or CR/NC (student choice) → </t>
+            <t xml:space="preserve">
+grading A-F grading only where the chamber ensemble norm is A-F or CR/NC (student choice)
+</t>
           </r>
           <r>
             <rPr>
@@ -7536,7 +7390,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -7633,7 +7488,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-05-19, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-05-19, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -7649,15 +7505,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">repeat cap of 4 units where the chamber ensemble norm is 8 → </t>
+            <t xml:space="preserve">
+repeat cap of 4 units where the chamber ensemble norm is 8
+</t>
           </r>
           <r>
             <rPr>
@@ -7677,7 +7527,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -7773,7 +7624,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-05-19, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-05-19, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -7789,15 +7641,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">repeat cap of 4 units where the chamber ensemble norm is 8 → </t>
+            <t xml:space="preserve">
+repeat cap of 4 units where the chamber ensemble norm is 8
+</t>
           </r>
           <r>
             <rPr>
@@ -7817,7 +7663,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -7910,7 +7757,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">repeat cap of 4 units where the chamber ensemble norm is 8 → </t>
+            <t xml:space="preserve">repeat cap of 4 units where the chamber ensemble norm is 8
+</t>
           </r>
           <r>
             <rPr>
@@ -7926,15 +7774,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">title published as Jazz Singers where the handbook names the ensemble East Bay Jazz Singers → </t>
+            <t xml:space="preserve">
+title published as Jazz Singers where the handbook names the ensemble East Bay Jazz Singers
+</t>
           </r>
           <r>
             <rPr>
@@ -7954,7 +7796,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -8051,7 +7894,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -8218,7 +8062,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -8309,7 +8154,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">reclassification pending per the theory and musicianship guide, effective fall 2027 → </t>
+            <t xml:space="preserve">reclassification pending per the theory and musicianship guide, effective fall 2027
+</t>
           </r>
           <r>
             <rPr>
@@ -8329,16 +8175,17 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcomes, from the syllabus → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Demonstrate understanding of the different genres, styles, and techniques of 20th and 21st century art music. 2. Analyze and evaluate post-tonal works in their technical, aesthetic, and historical contexts, supporting interpretive claims with evidence from the score. 3. Construct and manipulate post-tonal pitch collections, including pitch-class sets in normal and prime form, and analyze twelve-tone rows and their transformations. 4. Apply knowledge from earlier theory courses to extended post-tonal and contemporary works. 5. Situate works within the major compositional movements of the 20th and 21st centuries, including serialism, spectralism, minimalism, and extended techniques. 6. Implement the principles and concepts studied in class via performance on the student's area of emphasis.</t>
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Analytical and compositional techniques of the 20th and 21st centuries: post-tonal collections, pitch-class sets, centricity, twelve-tone serialism, form in post-tonal music, and the movements that follow 1945, including spectralism and minimalism.</t>
           </r>
         </is>
       </c>
@@ -8650,7 +8497,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -8749,7 +8597,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -8845,7 +8694,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -8945,7 +8795,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">units publish as 3 where the record holds 2 → </t>
+            <t xml:space="preserve">units publish as 3 where the record holds 2
+</t>
           </r>
           <r>
             <rPr>
@@ -8961,15 +8812,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">
+last revised 2016-04-27, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -8985,15 +8830,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">units publish as 3 where the record holds 2 → </t>
+            <t xml:space="preserve">
+units publish as 3 where the record holds 2
+</t>
           </r>
           <r>
             <rPr>
@@ -9169,7 +9008,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -9272,7 +9112,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">requires MUS 261A, renumbered or discontinued → </t>
+            <t xml:space="preserve">requires MUS 261A, renumbered or discontinued
+</t>
           </r>
           <r>
             <rPr>
@@ -9292,7 +9133,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -9308,15 +9150,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">
+outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -9419,7 +9255,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -9522,7 +9359,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -9538,15 +9376,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">
+outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -9649,7 +9481,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -9747,7 +9580,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">prerequisite ends with a doubled period → </t>
+            <t xml:space="preserve">prerequisite ends with a doubled period
+</t>
           </r>
           <r>
             <rPr>
@@ -9767,7 +9601,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -9870,7 +9705,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -9973,7 +9809,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -10076,7 +9913,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -10174,7 +10012,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcomes 1 and 2 are merged into a single numbered item → </t>
+            <t xml:space="preserve">outcomes 1 and 2 are merged into a single numbered item
+</t>
           </r>
           <r>
             <rPr>
@@ -10190,15 +10029,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">
+outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -10301,7 +10134,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -10404,7 +10238,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -10506,7 +10341,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">requires MUS 180, renumbered or discontinued → </t>
+            <t xml:space="preserve">requires MUS 180, renumbered or discontinued
+</t>
           </r>
           <r>
             <rPr>
@@ -10522,15 +10358,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">prerequisite written without a space in the course number → </t>
+            <t xml:space="preserve">
+prerequisite written without a space in the course number
+</t>
           </r>
           <r>
             <rPr>
@@ -10550,7 +10380,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -10652,7 +10483,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">requires MUS 180, renumbered or discontinued → </t>
+            <t xml:space="preserve">requires MUS 180, renumbered or discontinued
+</t>
           </r>
           <r>
             <rPr>
@@ -10668,15 +10500,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">prerequisite written without a space in the course number → </t>
+            <t xml:space="preserve">
+prerequisite written without a space in the course number
+</t>
           </r>
           <r>
             <rPr>
@@ -10696,7 +10522,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -10798,7 +10625,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">prerequisite written without a space in the course number → </t>
+            <t xml:space="preserve">prerequisite written without a space in the course number
+</t>
           </r>
           <r>
             <rPr>
@@ -10818,7 +10646,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person → </t>
+            <t xml:space="preserve">outcome 3 reads creating new repertoire and addresses the student in the second person, where the lower division series reads learning new repertoire in the third person
+</t>
           </r>
           <r>
             <rPr>
@@ -10920,16 +10749,17 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no credit restriction published, though the handbook states coaching units do not count toward graduation requirements → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>add the credit restriction: Units may not be used towards the Music Major or Minor.</t>
+            <t xml:space="preserve">no credit restriction published, though the handbook states coaching units do not count toward graduation requirements
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>add: Units may not be used towards the Music Major or Minor.</t>
           </r>
         </is>
       </c>
@@ -10940,7 +10770,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -10956,15 +10787,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">outcomes are the generic applied study set and outcome 2 addresses tone production on the primary instrument → </t>
+            <t xml:space="preserve">
+outcomes are the generic applied study set, and outcome 2 addresses tone production on the primary instrument
+</t>
           </r>
           <r>
             <rPr>
@@ -11066,16 +10891,17 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no credit restriction published, though the handbook states coaching units do not count toward graduation requirements → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>add the credit restriction: Units may not be used towards the Music Major or Minor.</t>
+            <t xml:space="preserve">no credit restriction published, though the handbook states coaching units do not count toward graduation requirements
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>add: Units may not be used towards the Music Major or Minor.</t>
           </r>
         </is>
       </c>
@@ -11086,7 +10912,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -11102,15 +10929,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">outcomes are the generic applied study set and outcome 2 addresses tone production on the primary instrument → </t>
+            <t xml:space="preserve">
+outcomes are the generic applied study set, and outcome 2 addresses tone production on the primary instrument
+</t>
           </r>
           <r>
             <rPr>
@@ -11357,7 +11178,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no learning outcomes published → </t>
+            <t xml:space="preserve">no learning outcomes published
+</t>
           </r>
           <r>
             <rPr>
@@ -11373,15 +11195,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">
+no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -11401,7 +11217,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no outcomes published → </t>
+            <t xml:space="preserve">no outcomes published
+</t>
           </r>
           <r>
             <rPr>
@@ -11500,7 +11317,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">units publish as 1 where the record holds 2 → </t>
+            <t xml:space="preserve">units publish as 1 where the record holds 2
+</t>
           </r>
           <r>
             <rPr>
@@ -11516,15 +11334,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-05-13, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">
+last revised 2016-05-13, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -11540,15 +11352,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">units publish as 2 where the music education certificate roadmap and handbook give 1 → </t>
+            <t xml:space="preserve">
+units publish as 2 where the certificate roadmap and handbook give 1
+</t>
           </r>
           <r>
             <rPr>
@@ -11639,7 +11445,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-05-01, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">last revised 2016-05-01, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -11960,7 +11767,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">units publish as 1-3 where the record holds 1 → </t>
+            <t xml:space="preserve">units publish as 1-3 where the record holds 1
+</t>
           </r>
           <r>
             <rPr>
@@ -11976,24 +11784,18 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">record holds 1 unit where the catalog and handbook give 1-3 → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>correct the record to 1-3</t>
+            <t xml:space="preserve">
+record holds 1 unit where the catalog and handbook give 1–3
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>correct the record to 1–3</t>
           </r>
         </is>
       </c>
@@ -12080,7 +11882,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -12096,15 +11899,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-02-05, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">
+last revised 2016-02-05, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -12702,7 +12499,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -12718,15 +12516,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-02-24, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">
+last revised 2016-02-24, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -12981,7 +12773,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -13073,7 +12866,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -13172,7 +12966,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">prerequisite of department consent, absent on most graduate applied courses → </t>
+            <t xml:space="preserve">prerequisite of department consent, absent on most graduate applied courses
+</t>
           </r>
           <r>
             <rPr>
@@ -13270,7 +13065,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">requires MUS 669, renumbered or discontinued → </t>
+            <t xml:space="preserve">requires MUS 669, renumbered or discontinued
+</t>
           </r>
           <r>
             <rPr>
@@ -13286,15 +13082,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">prerequisite of department consent, absent on most graduate applied courses → </t>
+            <t xml:space="preserve">
+prerequisite of department consent, absent on most graduate applied courses
+</t>
           </r>
           <r>
             <rPr>
@@ -13392,7 +13182,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">prerequisite of department consent, absent on most graduate applied courses → </t>
+            <t xml:space="preserve">prerequisite of department consent, absent on most graduate applied courses
+</t>
           </r>
           <r>
             <rPr>
@@ -13491,7 +13282,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">prerequisite of department consent, absent on most graduate applied courses → </t>
+            <t xml:space="preserve">prerequisite of department consent, absent on most graduate applied courses
+</t>
           </r>
           <r>
             <rPr>
@@ -13586,7 +13378,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description runs to 41 words, over the 40-word limit → </t>
+            <t xml:space="preserve">description runs to 41 words, over the 40-word limit
+</t>
           </r>
           <r>
             <rPr>
@@ -13606,7 +13399,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -13923,7 +13717,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">units publish as 1 where the record holds 1-2 → </t>
+            <t xml:space="preserve">units publish as 1 where the record holds 1-2
+</t>
           </r>
           <r>
             <rPr>
@@ -13939,24 +13734,18 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">units publish as 1 where the other graduate applied courses publish 1-2 → </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set units to 1-2</t>
+            <t xml:space="preserve">
+units publish as 1 where the other graduate applied courses publish 1–2
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set units to 1–2</t>
           </r>
         </is>
       </c>
@@ -14273,7 +14062,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">prerequisite of department consent, absent on most graduate applied courses → </t>
+            <t xml:space="preserve">prerequisite of department consent, absent on most graduate applied courses
+</t>
           </r>
           <r>
             <rPr>
@@ -14517,7 +14307,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no learning outcomes published → </t>
+            <t xml:space="preserve">no learning outcomes published
+</t>
           </r>
           <r>
             <rPr>
@@ -14533,15 +14324,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing → </t>
+            <t xml:space="preserve">
+repeatability uses non-standard phrasing
+</t>
           </r>
           <r>
             <rPr>
@@ -14561,7 +14346,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no outcomes published → </t>
+            <t xml:space="preserve">no outcomes published
+</t>
           </r>
           <r>
             <rPr>
@@ -14660,7 +14446,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing → </t>
+            <t xml:space="preserve">repeatability uses non-standard phrasing
+</t>
           </r>
           <r>
             <rPr>
@@ -14752,7 +14539,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no learning outcomes published → </t>
+            <t xml:space="preserve">no learning outcomes published
+</t>
           </r>
           <r>
             <rPr>
@@ -14768,15 +14556,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing → </t>
+            <t xml:space="preserve">
+repeatability uses non-standard phrasing
+</t>
           </r>
           <r>
             <rPr>
@@ -14796,7 +14578,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no outcomes published → </t>
+            <t xml:space="preserve">no outcomes published
+</t>
           </r>
           <r>
             <rPr>
@@ -14883,7 +14666,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no learning outcomes published → </t>
+            <t xml:space="preserve">no learning outcomes published
+</t>
           </r>
           <r>
             <rPr>
@@ -14899,15 +14683,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">
+no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -14923,15 +14701,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-02-26, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">
+last revised 2016-02-26, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -14951,7 +14723,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no outcomes published → </t>
+            <t xml:space="preserve">no outcomes published
+</t>
           </r>
           <r>
             <rPr>
@@ -15044,7 +14817,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description runs to 42 words, over the 40-word limit → </t>
+            <t xml:space="preserve">description runs to 42 words, over the 40-word limit
+</t>
           </r>
           <r>
             <rPr>
@@ -15060,15 +14834,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">
+no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -15084,15 +14852,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-02-26, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">
+last revised 2016-02-26, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -15112,7 +14874,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">description → </t>
+            <t xml:space="preserve">description
+</t>
           </r>
           <r>
             <rPr>
@@ -15205,7 +14968,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">units publish as 1-6 where the record holds 6 → </t>
+            <t xml:space="preserve">units publish as 1-6 where the record holds 6
+</t>
           </r>
           <r>
             <rPr>
@@ -15374,7 +15138,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -15390,15 +15155,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-02-26, still on the 2016 conversion form → </t>
+            <t xml:space="preserve">
+last revised 2016-02-26, still on the 2016 conversion form
+</t>
           </r>
           <r>
             <rPr>
@@ -15486,7 +15245,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no learning outcomes published → </t>
+            <t xml:space="preserve">no learning outcomes published
+</t>
           </r>
           <r>
             <rPr>
@@ -15502,15 +15262,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no teaching component or classification on record → </t>
+            <t xml:space="preserve">
+no teaching component or classification on record
+</t>
           </r>
           <r>
             <rPr>
@@ -15526,15 +15280,9 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no proposal on record in the Curriculog archive → </t>
+            <t xml:space="preserve">
+no proposal on record in the Curriculog archive
+</t>
           </r>
           <r>
             <rPr>
@@ -15554,7 +15302,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no outcomes published → </t>
+            <t xml:space="preserve">no outcomes published
+</t>
           </r>
           <r>
             <rPr>
@@ -15648,7 +15397,8 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">units publish as 1-6 where the record holds 6 → </t>
+            <t xml:space="preserve">units publish as 1-6 where the record holds 6
+</t>
           </r>
           <r>
             <rPr>

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -453,8 +453,8 @@
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
@@ -1384,8 +1384,48 @@
       <c r="S10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="3" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">corequisite carries no equivalence or consent path for transfer students
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>corequisite: MUS 115 and MUS 118, or equivalent, or department consent</t>
+          </r>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">outcomes are generic to the sequence and name no level-specific content, where the syllabus outcomes from the musicianship overhaul are current
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Read, write, and analyze the fundamental materials of tonal music using correct terminology and nomenclature. 2. Construct and identify all triad and seventh chord types in root position and inversion. 3. Write four-part (SATB) harmonic progressions using I, V, V⁷, and their inversions, applying basic voice-leading principles. 4. Compose and analyze two-voice counterpoint through fourth species. 5. Apply theoretical concepts at the keyboard and in performance on the student's primary instrument or voice.</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1464,8 +1504,84 @@
       <c r="S11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="3" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">no prerequisite published, so Theory II is enterable without Theory I
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>prerequisite: MUS 111, or equivalent, or department consent</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+corequisite carries no equivalence or consent path
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>corequisite: MUS 116 and MUS 119, or equivalent, or department consent</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+strongly recommended preparation duplicates the proposed prerequisite
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>remove the strongly recommended preparation, now covered by the prerequisite</t>
+          </r>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">outcomes repeat the closing three of MUS 111 and MUS 211 and name no level-specific content, where the syllabus outcomes from the musicianship overhaul are current
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Write and analyze SATB progressions using the full vocabulary of diatonic harmony, including all diatonic triads and seventh chords. 2. Identify and apply embellishing chords, the cadential 6/4, and other 6/4 chord types in functional context. 3. Recognize and compose diatonic sequences. 4. Analyze tonal works using Roman numerals, figured bass, and functional labels. 5. Apply diatonic harmonic vocabulary at the keyboard and in performance on the student's primary instrument or voice.</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1547,17 +1663,17 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">requires MUS 118A, renumbered or discontinued
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>replace with MUS 118</t>
+            <t xml:space="preserve">last revised 2016-05-05, still on the 2016 conversion form
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>review the full record on the current form</t>
           </r>
           <r>
             <rPr>
@@ -1565,17 +1681,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-last revised 2016-05-05, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
+corequisite names MUS 118A, renumbered to MUS 118 in September 2019
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>corequisite: MUS 111 and MUS 118, or equivalent, or department consent</t>
           </r>
         </is>
       </c>
@@ -1604,17 +1720,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-description is identical to the other courses in its track, so the levels are indistinguishable in the catalog
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>see the proposed description above</t>
+outcomes are identical across MUS 115, MUS 116, and MUS 215, where the syllabus outcomes from the musicianship overhaul are current
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Sight-sing diatonic melodies in major keys and simple meters using solfège or scale degrees, with accurate pitch, rhythm, and conducting. 2. Take melodic and rhythmic dictation in simple meters, notating pitch and rhythm accurately, including ties and the dotted beat. 3. Detect and correct errors in performed and notated examples. 4. Read fluently across all fifteen major keys.</t>
           </r>
         </is>
       </c>
@@ -1703,17 +1819,17 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">requires MUS 118B, renumbered or discontinued
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>replace with MUS 119</t>
+            <t xml:space="preserve">last revised 2016-05-05, still on the 2016 conversion form
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>review the full record on the current form</t>
           </r>
           <r>
             <rPr>
@@ -1721,17 +1837,35 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-last revised 2016-05-05, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
+corequisite names MUS 118B, renumbered to MUS 119 in September 2019
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>prerequisite: MUS 115, or equivalent, or department consent</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+corequisite carries no equivalence or consent path
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>corequisite: MUS 112 and MUS 119, or equivalent, or department consent</t>
           </r>
         </is>
       </c>
@@ -1760,17 +1894,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-description is identical to the other courses in its track, so the levels are indistinguishable in the catalog
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>see the proposed description above</t>
+outcomes are identical across MUS 115, MUS 116, and MUS 215, where the syllabus outcomes from the musicianship overhaul are current
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Sight-sing diatonic melodies in minor mode, approached through both relative and parallel major and including chromatic 6 and 7 by modal borrowing, and in compound meters, using solfège or scale degrees. 2. Take melodic and rhythmic dictation extending to triplets and duplets, quadruple division in simple meter, sextuple division in compound meter, and syncopation. 3. Perform lower chromatic neighbors and melodic skips to chord tones as prefix neighbors through the tonic, dominant, and subdominant triads. 4. Sing the dominant seventh chord in melodic context.</t>
           </r>
         </is>
       </c>
@@ -1849,7 +1983,27 @@
       <c r="S14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T14" s="3" t="inlineStr"/>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">no corequisite published, though the guide runs the three tracks concurrently
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>corequisite: MUS 111 and MUS 115, or equivalent, or department consent</t>
+          </r>
+        </is>
+      </c>
       <c r="U14" s="5" t="inlineStr">
         <is>
           <r>
@@ -1875,17 +2029,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-description is identical to the other courses in its track, so the levels are indistinguishable in the catalog
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>see the proposed description above</t>
+nine outcomes, several naming activities rather than what a student can do, where the syllabus outcomes from the musicianship overhaul are current
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Perform major and minor five-finger patterns and their triads in all common keys. 2. Perform all four triad qualities (major, minor, augmented, diminished) in root position. 3. Play major scales in tetrachord position with correct fingering, and use the damper pedal. 4. Harmonize simple melodies using basic diatonic chords. 5. Sight-read short examples in grand staff at a basic level.</t>
           </r>
         </is>
       </c>
@@ -1967,7 +2121,45 @@
       <c r="S15" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T15" s="3" t="inlineStr"/>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">no prerequisite published, so Keyboard II is enterable without Keyboard I
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>prerequisite: MUS 118, or equivalent, or credit by exam</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+corequisite carries no equivalence or consent path
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>corequisite: MUS 112 and MUS 116, or equivalent, or department consent</t>
+          </r>
+        </is>
+      </c>
       <c r="U15" s="5" t="inlineStr">
         <is>
           <r>
@@ -1993,17 +2185,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-description is identical to the other courses in its track, so the levels are indistinguishable in the catalog
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>see the proposed description above</t>
+twelve outcomes, identical to MUS 218 and including activities rather than outcomes, where the syllabus outcomes from the musicianship overhaul are current
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Perform major and minor scales and arpeggios across Group 1 and Group 2 keys, two octaves. 2. Play triads in all inversions and perform the dominant seventh chord in block and broken patterns. 3. Harmonize short melodies using primary chords (I, IV, V⁷) in major and minor, with idiomatic accompaniment patterns including Alberti and waltz bass. 4. Sing a melody while playing a two-hand accompaniment. 5. Realize basic lead-sheet symbols and Roman numerals at the keyboard. 6. Sight-read in grand staff, hands together, in four-to-eight-bar examples.</t>
           </r>
         </is>
       </c>
@@ -2279,9 +2471,83 @@
             </rPr>
             <t>reclassify to C10</t>
           </r>
-        </is>
-      </c>
-      <c r="U18" s="3" t="inlineStr"/>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+corequisite carries no equivalence or consent path for transfer students
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>prerequisite: MUS 112, or equivalent, or department consent</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+corequisite carries no equivalence or consent path
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>corequisite: MUS 215 and MUS 218, or equivalent, or department consent</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+strongly recommended preparation duplicates the proposed prerequisite
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>remove the strongly recommended preparation, now covered by the prerequisite</t>
+          </r>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">outcomes repeat the closing three of MUS 111 and MUS 112 and name no level-specific content, where the syllabus outcomes from the musicianship overhaul are current
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Write and analyze chromatic harmony, including applied dominants, modal mixture, the Neapolitan sixth, augmented sixth chords, and altered chords. 2. Identify and compose modulations to the dominant and to closely related keys. 3. Analyze chromatic sequences and chromatic modulation. 4. Evaluate tonal works combining diatonic and chromatic vocabulary in extended harmonic contexts. 5. Apply chromatic harmonic vocabulary at the keyboard and in performance on the student's primary instrument or voice.</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -2379,6 +2645,42 @@
             </rPr>
             <t>review the full record on the current form</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+corequisite carries no equivalence or consent path for transfer students
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>prerequisite: MUS 112 and MUS 116, or equivalent, or department consent</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+corequisite carries no equivalence or consent path
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>corequisite: MUS 211, or equivalent, or department consent</t>
+          </r>
         </is>
       </c>
       <c r="U19" s="5" t="inlineStr">
@@ -2399,6 +2701,24 @@
               <sz val="10"/>
             </rPr>
             <t>Third of three concurrent aural skills courses. Harmonic listening and dictation: harmonic rhythm and cadences, two-voice textures, bass-line dictation, triad quality and inversion by ear, and melodic skips through every diatonic triad.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+outcomes are identical across MUS 115, MUS 116, and MUS 215, where the syllabus outcomes from the musicianship overhaul are current
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Sing and hear harmonically, following harmonic rhythm and cadences. 2. Work in two-voice textures and take bass-line dictation. 3. Identify root-position and first-inversion triads and all four triad qualities by ear, and sing melodic skips through every diatonic triad (leading-tone, supertonic, submediant, and mediant). 4. Handle the dominant seventh chord in harmonic context, with the voice-leading techniques that close the lower-division sequence.</t>
           </r>
         </is>
       </c>
@@ -2480,7 +2800,45 @@
       <c r="S20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T20" s="3" t="inlineStr"/>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">no prerequisite published, so Keyboard III is enterable without Keyboard I or II
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>prerequisite: MUS 119, or equivalent, or credit by exam</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+corequisite carries no equivalence or consent path
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>corequisite: MUS 211 and MUS 215, or equivalent, or department consent</t>
+          </r>
+        </is>
+      </c>
       <c r="U20" s="5" t="inlineStr">
         <is>
           <r>
@@ -2506,17 +2864,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-description is identical to the other courses in its track, so the levels are indistinguishable in the catalog
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>see the proposed description above</t>
+twelve outcomes, identical to MUS 119 and including activities rather than outcomes, where the syllabus outcomes from the musicianship overhaul are current
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Perform major and minor scales and arpeggios across all key groups, and play chromatic, whole-tone, and blues scales. 2. Perform secondary triads (ii, iii, vi) and seventh chords in harmonic context, with correct voice leading. 3. Play melodies and accompaniments in all six church modes. 4. Harmonize melodies using the full diatonic vocabulary including secondary chords. 5. Transpose short examples to other keys and improvise within defined modal and harmonic frameworks. 6. Prepare and perform repertoire from Alfred's Book 1 for peers and instructor.</t>
           </r>
         </is>
       </c>
@@ -5022,6 +5380,24 @@
             </rPr>
             <t>set 2 units C05 plus 1 unit C10</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+prerequisite misspells successful
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>correct to: MUS 211, or successful Theory and Musicianship Placement Exam</t>
+          </r>
         </is>
       </c>
       <c r="U44" s="5" t="inlineStr">
@@ -5042,6 +5418,24 @@
               <sz val="10"/>
             </rPr>
             <t>Analysis of style and structural form in European art music of the 18th and 19th centuries. Topics include phrase and sentence structure, thematic organization, binary and ternary forms, variation and rondo forms, slow movement forms, and sonata forms.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+four outcomes where the syllabus carries six, omitting phrase structure, hypermeter, and written analysis, where the syllabus outcomes from the musicianship overhaul are current
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Demonstrate understanding of the forms used in tonal music, including sentence, period, binary, ternary, rondo, and sonata forms. 2. Analyze and evaluate complete tonal works in their technical, aesthetic, and historical contexts, supporting interpretive claims with evidence from the score. 3. Apply the harmonic and contrapuntal knowledge of the lower-division sequence to extended musical works. 4. Identify phrase structure, hypermeter, and formal boundaries both visually and aurally. 5. Construct written analyses using appropriate terminology, Roman numerals, figured bass, and formal labels. 6. Implement the principles and concepts studied in class via performance on the student's major instrument or voice.</t>
           </r>
         </is>
       </c>
@@ -8166,6 +8560,24 @@
             </rPr>
             <t>set 2 units C05 plus 1 unit C10</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+no prerequisite published, though the guide states MUS 312
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>prerequisite: MUS 312, or equivalent, or department consent</t>
+          </r>
         </is>
       </c>
       <c r="U72" s="5" t="inlineStr">
@@ -8186,6 +8598,24 @@
               <sz val="10"/>
             </rPr>
             <t>Analytical and compositional techniques of the 20th and 21st centuries: post-tonal collections, pitch-class sets, centricity, twelve-tone serialism, form in post-tonal music, and the movements that follow 1945, including spectralism and minimalism.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+four outcomes where the syllabus carries six, omitting pitch-class set construction and twelve-tone analysis, where the syllabus outcomes from the musicianship overhaul are current
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Demonstrate understanding of the different genres, styles, and techniques of 20th and 21st century art music. 2. Analyze and evaluate post-tonal works in their technical, aesthetic, and historical contexts, supporting interpretive claims with evidence from the score. 3. Construct and manipulate post-tonal pitch collections, including pitch-class sets in normal and prime form, and analyze twelve-tone rows and their transformations. 4. Apply knowledge from earlier theory courses to extended post-tonal and contemporary works. 5. Situate works within the major compositional movements of the 20th and 21st centuries, including serialism, spectralism, minimalism, and extended techniques. 6. Implement the principles and concepts studied in class via performance on the student's area of emphasis.</t>
           </r>
         </is>
       </c>

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -1401,6 +1401,24 @@
               <color rgb="00B03A2E"/>
               <sz val="10"/>
             </rPr>
+            <t>prerequisite: MUS 108, or satisfactory score on the Music Theory Advisory Exam, or department consent</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+corequisite carries no equivalence or consent path
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
             <t>corequisite: MUS 115 and MUS 118, or equivalent, or department consent</t>
           </r>
         </is>
@@ -1547,17 +1565,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-strongly recommended preparation duplicates the proposed prerequisite
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>remove the strongly recommended preparation, now covered by the prerequisite</t>
+strongly recommended preparation duplicates the prerequisite
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>remove the strongly recommended preparation</t>
           </r>
         </is>
       </c>
@@ -1568,7 +1586,25 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">outcomes repeat the closing three of MUS 111 and MUS 211 and name no level-specific content, where the syllabus outcomes from the musicianship overhaul are current
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The second of three intensive courses that introduce students to the inner workings of European art music of the 18th and 19th centuries. This course completes diatonic harmony and introduces advanced part-writing, voice-leading, and harmonization techniques.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+outcomes repeat the closing three of MUS 111 and MUS 211 and name no level-specific content, where the syllabus outcomes from the musicianship overhaul are current
 </t>
           </r>
           <r>
@@ -2513,17 +2549,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-strongly recommended preparation duplicates the proposed prerequisite
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>remove the strongly recommended preparation, now covered by the prerequisite</t>
+strongly recommended preparation duplicates the prerequisite
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>remove the strongly recommended preparation</t>
           </r>
         </is>
       </c>
@@ -2651,17 +2687,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-corequisite carries no equivalence or consent path for transfer students
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>prerequisite: MUS 112 and MUS 116, or equivalent, or department consent</t>
+prerequisite and corequisite differ from the syllabus and carry no equivalence or consent path
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>prerequisite: MUS 116, or equivalent, or department consent</t>
           </r>
           <r>
             <rPr>
@@ -2679,7 +2715,7 @@
               <color rgb="00B03A2E"/>
               <sz val="10"/>
             </rPr>
-            <t>corequisite: MUS 211, or equivalent, or department consent</t>
+            <t>corequisite: MUS 211 and MUS 218, or equivalent, or department consent</t>
           </r>
         </is>
       </c>
@@ -5386,17 +5422,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-prerequisite misspells successful
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>correct to: MUS 211, or successful Theory and Musicianship Placement Exam</t>
+prerequisite misspells successful and names only MUS 211
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>prerequisite: MUS 211, MUS 215, and MUS 218, or successful Theory and Musicianship Placement Exam, or department consent</t>
           </r>
         </is>
       </c>

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -1401,7 +1401,7 @@
               <color rgb="00B03A2E"/>
               <sz val="10"/>
             </rPr>
-            <t>prerequisite: MUS 108, or satisfactory score on the Music Theory Advisory Exam, or department consent</t>
+            <t>prerequisite: MUS 108, or equivalent, or department consent</t>
           </r>
           <r>
             <rPr>

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -2026,7 +2026,25 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no corequisite published, though the guide runs the three tracks concurrently
+            <t xml:space="preserve">no requisites published, though the guide runs the three tracks concurrently and the handbook offers credit by exam
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>prerequisite: None; credit by exam available</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+corequisite carries no equivalence or consent path
 </t>
           </r>
           <r>

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -2026,25 +2026,7 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no requisites published, though the guide runs the three tracks concurrently and the handbook offers credit by exam
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>prerequisite: None; credit by exam available</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-corequisite carries no equivalence or consent path
+            <t xml:space="preserve">no corequisite published, though the guide runs the three tracks concurrently
 </t>
           </r>
           <r>
@@ -2192,7 +2174,7 @@
               <color rgb="00B03A2E"/>
               <sz val="10"/>
             </rPr>
-            <t>prerequisite: MUS 118, or equivalent, or credit by exam</t>
+            <t>prerequisite: MUS 118, or equivalent, or department consent</t>
           </r>
           <r>
             <rPr>
@@ -2871,7 +2853,7 @@
               <color rgb="00B03A2E"/>
               <sz val="10"/>
             </rPr>
-            <t>prerequisite: MUS 119, or equivalent, or credit by exam</t>
+            <t>prerequisite: MUS 119, or equivalent, or department consent</t>
           </r>
           <r>
             <rPr>

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -11813,24 +11813,6 @@
             </rPr>
             <t>review the full record on the current form</t>
           </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-units publish as 2 where the certificate roadmap and handbook give 1
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set units to 1</t>
-          </r>
         </is>
       </c>
       <c r="U101" s="3" t="inlineStr"/>

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -9259,24 +9259,21 @@
           <r>
             <rPr>
               <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">units publish as 3 where the record holds 2
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set units to 3</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">classification holds 2 units of C05 where the course publishes 3, a quarter-conversion artifact
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+            </rPr>
+            <t>set the classification to C05 3u</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
             </rPr>
             <t xml:space="preserve">
 last revised 2016-04-27, still on the 2016 conversion form
@@ -9287,27 +9284,8 @@
               <rFont val="Arial"/>
               <b val="1"/>
               <color rgb="00B03A2E"/>
-              <sz val="10"/>
             </rPr>
             <t>review the full record on the current form</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-units publish as 3 where the record holds 2
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>correct the record to 3</t>
           </r>
         </is>
       </c>
@@ -15864,8 +15842,5 @@
   </sheetData>
   <autoFilter ref="A1:U141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:U141" numberStoredAsText="1" twoDigitTextYear="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -15482,7 +15482,25 @@
       <c r="S138" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T138" s="3" t="inlineStr"/>
+      <c r="T138" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+            </rPr>
+            <t xml:space="preserve">classified C25, which is not a CSUEB course classification
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+            </rPr>
+            <t>set the classification to S25</t>
+          </r>
+        </is>
+      </c>
       <c r="U138" s="3" t="inlineStr"/>
     </row>
     <row r="139">

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -6319,24 +6319,21 @@
           <r>
             <rPr>
               <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">units publish as 3 where the record holds 2
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set units to 3</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">classification holds 2 units of C05 where the course publishes 3, a quarter-conversion artifact
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B03A2E"/>
+            </rPr>
+            <t>set the classification to C05 3u</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
             </rPr>
             <t xml:space="preserve">
 last revised 2016-04-26, still on the 2016 conversion form
@@ -6347,27 +6344,8 @@
               <rFont val="Arial"/>
               <b val="1"/>
               <color rgb="00B03A2E"/>
-              <sz val="10"/>
             </rPr>
             <t>review the full record on the current form</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-units publish as 3 where the record holds 2
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>correct the record to 3</t>
           </r>
         </is>
       </c>

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/inesthiebaut/Documents/music-curriculum/curriculum/catalog-audit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1EFBD89-FD0D-CE41-8D3D-5574742FD495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930B037F-66F8-AC42-AEC9-9DC4F399E752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5724,7 +5724,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5757,6 +5757,11 @@
       <color rgb="FFB03A2E"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -5783,7 +5788,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -5801,6 +5806,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8367,185 +8375,185 @@
         <v>316</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="182" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1" t="s">
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L46" s="1" t="s">
+      <c r="L46" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="M46" s="1" t="s">
+      <c r="M46" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1" t="s">
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1" t="s">
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-    </row>
-    <row r="47" spans="1:20" ht="168" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
+    </row>
+    <row r="47" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1" t="s">
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L47" s="1" t="s">
+      <c r="L47" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="M47" s="1" t="s">
+      <c r="M47" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1" t="s">
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="1" t="s">
+      <c r="Q47" s="4"/>
+      <c r="R47" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="S47" s="1"/>
-      <c r="T47" s="1"/>
-    </row>
-    <row r="48" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
+    </row>
+    <row r="48" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1" t="s">
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="K48" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L48" s="1" t="s">
+      <c r="L48" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1" t="s">
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="1" t="s">
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="S48" s="1"/>
-      <c r="T48" s="1"/>
-    </row>
-    <row r="49" spans="1:20" ht="98" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+    </row>
+    <row r="49" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1" t="s">
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L49" s="1" t="s">
+      <c r="L49" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="M49" s="1" t="s">
+      <c r="M49" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1" t="s">
+      <c r="N49" s="4"/>
+      <c r="O49" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="P49" s="1" t="s">
+      <c r="P49" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="Q49" s="1"/>
-      <c r="R49" s="1" t="s">
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="S49" s="2" t="s">
+      <c r="S49" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="T49" s="1"/>
+      <c r="T49" s="4"/>
     </row>
     <row r="50" spans="1:20" ht="70" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -8595,97 +8603,97 @@
         <v>345</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="210" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
+    <row r="51" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1" t="s">
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L51" s="1" t="s">
+      <c r="L51" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M51" s="1" t="s">
+      <c r="M51" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
-      <c r="P51" s="1" t="s">
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="Q51" s="1"/>
-      <c r="R51" s="1" t="s">
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="S51" s="2" t="s">
+      <c r="S51" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="T51" s="1"/>
-    </row>
-    <row r="52" spans="1:20" ht="140" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
+      <c r="T51" s="4"/>
+    </row>
+    <row r="52" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1" t="s">
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L52" s="1" t="s">
+      <c r="L52" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M52" s="1" t="s">
+      <c r="M52" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1" t="s">
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="Q52" s="1"/>
-      <c r="R52" s="1" t="s">
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="S52" s="2" t="s">
+      <c r="S52" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="T52" s="1"/>
+      <c r="T52" s="4"/>
     </row>
     <row r="53" spans="1:20" ht="126" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
@@ -8723,7 +8731,7 @@
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
-      <c r="P53" s="1" t="s">
+      <c r="P53" s="7" t="s">
         <v>364</v>
       </c>
       <c r="Q53" s="1"/>

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/inesthiebaut/Documents/music-curriculum/curriculum/catalog-audit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930B037F-66F8-AC42-AEC9-9DC4F399E752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7AFD327-A7EC-614C-926B-476EB9A3B3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5763,7 +5763,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5773,6 +5773,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEEAE2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -5788,7 +5800,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -5805,10 +5817,24 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6197,7 +6223,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>20</v>
       </c>
@@ -6243,7 +6269,7 @@
       </c>
       <c r="T2" s="4"/>
     </row>
-    <row r="3" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>32</v>
       </c>
@@ -6295,7 +6321,7 @@
       </c>
       <c r="T3" s="4"/>
     </row>
-    <row r="4" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
@@ -6343,7 +6369,7 @@
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
     </row>
-    <row r="5" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>50</v>
       </c>
@@ -6391,7 +6417,7 @@
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
     </row>
-    <row r="6" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>55</v>
       </c>
@@ -6439,7 +6465,7 @@
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
     </row>
-    <row r="7" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>59</v>
       </c>
@@ -6487,7 +6513,7 @@
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
     </row>
-    <row r="8" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>65</v>
       </c>
@@ -6535,7 +6561,7 @@
       </c>
       <c r="T8" s="4"/>
     </row>
-    <row r="9" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>75</v>
       </c>
@@ -6885,7 +6911,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>126</v>
       </c>
@@ -6933,7 +6959,7 @@
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
     </row>
-    <row r="17" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>131</v>
       </c>
@@ -7137,7 +7163,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="21" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>165</v>
       </c>
@@ -7181,7 +7207,7 @@
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
     </row>
-    <row r="22" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>171</v>
       </c>
@@ -7225,7 +7251,7 @@
       <c r="S22" s="4"/>
       <c r="T22" s="4"/>
     </row>
-    <row r="23" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>175</v>
       </c>
@@ -7269,7 +7295,7 @@
       <c r="S23" s="4"/>
       <c r="T23" s="4"/>
     </row>
-    <row r="24" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>179</v>
       </c>
@@ -7313,7 +7339,7 @@
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
     </row>
-    <row r="25" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>183</v>
       </c>
@@ -7359,7 +7385,7 @@
       </c>
       <c r="T25" s="4"/>
     </row>
-    <row r="26" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>189</v>
       </c>
@@ -7405,7 +7431,7 @@
       </c>
       <c r="T26" s="4"/>
     </row>
-    <row r="27" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>193</v>
       </c>
@@ -7453,59 +7479,59 @@
       <c r="S27" s="4"/>
       <c r="T27" s="4"/>
     </row>
-    <row r="28" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1" t="s">
+      <c r="G28" s="4"/>
+      <c r="H28" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1" t="s">
+      <c r="I28" s="4"/>
+      <c r="J28" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="K28" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="L28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="M28" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1" t="s">
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1" t="s">
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="S28" s="2" t="s">
+      <c r="S28" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="T28" s="2" t="s">
+      <c r="T28" s="5" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="29" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>210</v>
       </c>
@@ -7557,57 +7583,57 @@
       </c>
       <c r="T29" s="4"/>
     </row>
-    <row r="30" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1" t="s">
+      <c r="G30" s="4"/>
+      <c r="H30" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
+      <c r="I30" s="4"/>
+      <c r="J30" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="L30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="M30" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1" t="s">
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1" t="s">
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="S30" s="1"/>
-      <c r="T30" s="2" t="s">
+      <c r="S30" s="4"/>
+      <c r="T30" s="5" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="31" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>221</v>
       </c>
@@ -7657,59 +7683,59 @@
         <v>225</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="140" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1" t="s">
+      <c r="G32" s="4"/>
+      <c r="H32" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1" t="s">
+      <c r="I32" s="4"/>
+      <c r="J32" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L32" s="1" t="s">
+      <c r="L32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="M32" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1" t="s">
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1" t="s">
+      <c r="Q32" s="4"/>
+      <c r="R32" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="S32" s="2" t="s">
+      <c r="S32" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="T32" s="2" t="s">
+      <c r="T32" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="33" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>232</v>
       </c>
@@ -7757,207 +7783,207 @@
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
     </row>
-    <row r="34" spans="1:20" ht="140" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1" t="s">
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1" t="s">
+      <c r="I34" s="4"/>
+      <c r="J34" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="K34" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L34" s="1" t="s">
+      <c r="L34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M34" s="1" t="s">
+      <c r="M34" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1" t="s">
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1" t="s">
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="S34" s="2" t="s">
+      <c r="S34" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="T34" s="2" t="s">
+      <c r="T34" s="5" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1" t="s">
+      <c r="G35" s="4"/>
+      <c r="H35" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1" t="s">
+      <c r="I35" s="4"/>
+      <c r="J35" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="K35" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L35" s="1" t="s">
+      <c r="L35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="M35" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1" t="s">
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1" t="s">
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="S35" s="1"/>
-      <c r="T35" s="2" t="s">
+      <c r="S35" s="4"/>
+      <c r="T35" s="5" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1" t="s">
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1" t="s">
+      <c r="I36" s="4"/>
+      <c r="J36" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L36" s="1" t="s">
+      <c r="L36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="M36" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1" t="s">
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1" t="s">
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="S36" s="2" t="s">
+      <c r="S36" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="T36" s="2" t="s">
+      <c r="T36" s="5" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1" t="s">
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K37" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L37" s="1" t="s">
+      <c r="L37" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M37" s="1" t="s">
+      <c r="M37" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1" t="s">
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1" t="s">
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
+      <c r="S37" s="4"/>
+      <c r="T37" s="4"/>
     </row>
     <row r="38" spans="1:20" ht="182" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
@@ -8067,7 +8093,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="40" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>271</v>
       </c>
@@ -8119,7 +8145,7 @@
       <c r="S40" s="4"/>
       <c r="T40" s="4"/>
     </row>
-    <row r="41" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>280</v>
       </c>
@@ -8171,7 +8197,7 @@
       <c r="S41" s="4"/>
       <c r="T41" s="4"/>
     </row>
-    <row r="42" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>287</v>
       </c>
@@ -8223,7 +8249,7 @@
       <c r="S42" s="4"/>
       <c r="T42" s="4"/>
     </row>
-    <row r="43" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>293</v>
       </c>
@@ -8325,7 +8351,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="45" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>308</v>
       </c>
@@ -8375,7 +8401,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="46" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>317</v>
       </c>
@@ -8419,7 +8445,7 @@
       <c r="S46" s="4"/>
       <c r="T46" s="4"/>
     </row>
-    <row r="47" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>321</v>
       </c>
@@ -8463,7 +8489,7 @@
       <c r="S47" s="4"/>
       <c r="T47" s="4"/>
     </row>
-    <row r="48" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>326</v>
       </c>
@@ -8507,7 +8533,7 @@
       <c r="S48" s="4"/>
       <c r="T48" s="4"/>
     </row>
-    <row r="49" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>333</v>
       </c>
@@ -8603,7 +8629,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="51" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>346</v>
       </c>
@@ -8649,7 +8675,7 @@
       </c>
       <c r="T51" s="4"/>
     </row>
-    <row r="52" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>352</v>
       </c>
@@ -8731,7 +8757,7 @@
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
-      <c r="P53" s="7" t="s">
+      <c r="P53" s="6" t="s">
         <v>364</v>
       </c>
       <c r="Q53" s="1"/>
@@ -8743,891 +8769,891 @@
       </c>
       <c r="T53" s="1"/>
     </row>
-    <row r="54" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A54" s="1" t="s">
+    <row r="54" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1" t="s">
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="K54" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="L54" s="1" t="s">
+      <c r="L54" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="M54" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1" t="s">
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="Q54" s="1"/>
-      <c r="R54" s="1" t="s">
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="S54" s="2" t="s">
+      <c r="S54" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="T54" s="1"/>
-    </row>
-    <row r="55" spans="1:20" ht="168" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
+      <c r="T54" s="4"/>
+    </row>
+    <row r="55" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1" t="s">
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="K55" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L55" s="1" t="s">
+      <c r="L55" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M55" s="1" t="s">
+      <c r="M55" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1" t="s">
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="Q55" s="1"/>
-      <c r="R55" s="1" t="s">
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="S55" s="1"/>
-      <c r="T55" s="2" t="s">
+      <c r="S55" s="4"/>
+      <c r="T55" s="5" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="140" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
+    <row r="56" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1" t="s">
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="K56" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L56" s="1" t="s">
+      <c r="L56" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="M56" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1" t="s">
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="Q56" s="1"/>
-      <c r="R56" s="1" t="s">
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="S56" s="2" t="s">
+      <c r="S56" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="T56" s="2" t="s">
+      <c r="T56" s="5" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="98" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1" t="s">
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="K57" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L57" s="1" t="s">
+      <c r="L57" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M57" s="1" t="s">
+      <c r="M57" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1" t="s">
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="1" t="s">
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="S57" s="1"/>
-      <c r="T57" s="2" t="s">
+      <c r="S57" s="4"/>
+      <c r="T57" s="5" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="154" x14ac:dyDescent="0.2">
-      <c r="A58" s="1" t="s">
+    <row r="58" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1" t="s">
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="K58" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L58" s="1" t="s">
+      <c r="L58" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M58" s="1" t="s">
+      <c r="M58" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1" t="s">
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1" t="s">
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="S58" s="2" t="s">
+      <c r="S58" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="T58" s="2" t="s">
+      <c r="T58" s="5" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A59" s="1" t="s">
+    <row r="59" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1" t="s">
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="J59" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="K59" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="L59" s="1" t="s">
+      <c r="L59" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M59" s="1" t="s">
+      <c r="M59" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1" t="s">
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="Q59" s="1"/>
-      <c r="R59" s="1" t="s">
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="S59" s="2" t="s">
+      <c r="S59" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="T59" s="1"/>
-    </row>
-    <row r="60" spans="1:20" ht="98" x14ac:dyDescent="0.2">
-      <c r="A60" s="1" t="s">
+      <c r="T59" s="4"/>
+    </row>
+    <row r="60" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1" t="s">
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="K60" s="1" t="s">
+      <c r="K60" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L60" s="1" t="s">
+      <c r="L60" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M60" s="1" t="s">
+      <c r="M60" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1" t="s">
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1" t="s">
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="S60" s="2" t="s">
+      <c r="S60" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="T60" s="2" t="s">
+      <c r="T60" s="5" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="140" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
+    <row r="61" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1" t="s">
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="K61" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L61" s="1" t="s">
+      <c r="L61" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M61" s="1" t="s">
+      <c r="M61" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1" t="s">
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="Q61" s="1"/>
-      <c r="R61" s="1" t="s">
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="S61" s="2" t="s">
+      <c r="S61" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="T61" s="2" t="s">
+      <c r="T61" s="5" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
+    <row r="62" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1" t="s">
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="K62" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L62" s="1" t="s">
+      <c r="L62" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M62" s="1" t="s">
+      <c r="M62" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1" t="s">
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="1" t="s">
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S62" s="2" t="s">
+      <c r="S62" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="T62" s="2" t="s">
+      <c r="T62" s="5" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="98" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
+    <row r="63" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1" t="s">
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="K63" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L63" s="1" t="s">
+      <c r="L63" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M63" s="1" t="s">
+      <c r="M63" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1" t="s">
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="Q63" s="1"/>
-      <c r="R63" s="1" t="s">
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S63" s="2" t="s">
+      <c r="S63" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="T63" s="2" t="s">
+      <c r="T63" s="5" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
+    <row r="64" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1" t="s">
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K64" s="1" t="s">
+      <c r="K64" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L64" s="1" t="s">
+      <c r="L64" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M64" s="1" t="s">
+      <c r="M64" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1" t="s">
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="Q64" s="1"/>
-      <c r="R64" s="1" t="s">
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="S64" s="2" t="s">
+      <c r="S64" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="T64" s="2" t="s">
+      <c r="T64" s="5" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="154" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
+    <row r="65" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D65" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1" t="s">
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="K65" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L65" s="1" t="s">
+      <c r="L65" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M65" s="1" t="s">
+      <c r="M65" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
-      <c r="P65" s="1" t="s">
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="Q65" s="1"/>
-      <c r="R65" s="1" t="s">
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="S65" s="2" t="s">
+      <c r="S65" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="T65" s="2" t="s">
+      <c r="T65" s="5" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
+    <row r="66" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1" t="s">
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K66" s="1" t="s">
+      <c r="K66" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L66" s="1" t="s">
+      <c r="L66" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M66" s="1" t="s">
+      <c r="M66" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1" t="s">
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="Q66" s="1"/>
-      <c r="R66" s="1" t="s">
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="S66" s="2" t="s">
+      <c r="S66" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="T66" s="2" t="s">
+      <c r="T66" s="5" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
+    <row r="67" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E67" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1" t="s">
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K67" s="1" t="s">
+      <c r="K67" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L67" s="1" t="s">
+      <c r="L67" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M67" s="1" t="s">
+      <c r="M67" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1" t="s">
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="Q67" s="1"/>
-      <c r="R67" s="1" t="s">
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="S67" s="2" t="s">
+      <c r="S67" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="T67" s="2" t="s">
+      <c r="T67" s="5" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
+    <row r="68" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1" t="s">
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="K68" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="L68" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1" t="s">
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="Q68" s="1"/>
-      <c r="R68" s="1" t="s">
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="S68" s="2" t="s">
+      <c r="S68" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="T68" s="2" t="s">
+      <c r="T68" s="5" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="168" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
+    <row r="69" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1" t="s">
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="K69" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L69" s="1" t="s">
+      <c r="L69" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M69" s="1" t="s">
+      <c r="M69" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1" t="s">
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="Q69" s="1"/>
-      <c r="R69" s="1" t="s">
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="S69" s="1"/>
-      <c r="T69" s="2" t="s">
+      <c r="S69" s="4"/>
+      <c r="T69" s="5" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="98" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
+    <row r="70" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E70" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="G70" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="H70" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1" t="s">
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L70" s="1" t="s">
+      <c r="L70" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M70" s="1" t="s">
+      <c r="M70" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1" t="s">
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="Q70" s="1"/>
-      <c r="R70" s="1" t="s">
+      <c r="Q70" s="4"/>
+      <c r="R70" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="S70" s="1"/>
-      <c r="T70" s="1"/>
-    </row>
-    <row r="71" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
+      <c r="S70" s="4"/>
+      <c r="T70" s="4"/>
+    </row>
+    <row r="71" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E71" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="1" t="s">
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L71" s="1" t="s">
+      <c r="L71" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
-      <c r="P71" s="1" t="s">
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="Q71" s="1"/>
-      <c r="R71" s="1" t="s">
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="S71" s="2" t="s">
+      <c r="S71" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="T71" s="1"/>
+      <c r="T71" s="4"/>
     </row>
     <row r="72" spans="1:20" ht="293" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
@@ -9677,285 +9703,285 @@
         <v>484</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="98" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
+    <row r="73" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D73" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E73" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1" t="s">
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L73" s="1" t="s">
+      <c r="L73" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M73" s="1" t="s">
+      <c r="M73" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
-      <c r="P73" s="1" t="s">
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+      <c r="P73" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="Q73" s="1"/>
-      <c r="R73" s="1" t="s">
+      <c r="Q73" s="4"/>
+      <c r="R73" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="S73" s="1"/>
-      <c r="T73" s="1"/>
-    </row>
-    <row r="74" spans="1:20" ht="98" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
+      <c r="S73" s="4"/>
+      <c r="T73" s="4"/>
+    </row>
+    <row r="74" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E74" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1" t="s">
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L74" s="1" t="s">
+      <c r="L74" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M74" s="1" t="s">
+      <c r="M74" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="N74" s="1"/>
-      <c r="O74" s="1"/>
-      <c r="P74" s="1" t="s">
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="Q74" s="1"/>
-      <c r="R74" s="1" t="s">
+      <c r="Q74" s="4"/>
+      <c r="R74" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="S74" s="1"/>
-      <c r="T74" s="1"/>
-    </row>
-    <row r="75" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
+      <c r="S74" s="4"/>
+      <c r="T74" s="4"/>
+    </row>
+    <row r="75" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E75" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="G75" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="1" t="s">
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L75" s="1" t="s">
+      <c r="L75" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M75" s="1" t="s">
+      <c r="M75" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="N75" s="1"/>
-      <c r="O75" s="1"/>
-      <c r="P75" s="1" t="s">
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="Q75" s="1"/>
-      <c r="R75" s="1" t="s">
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="S75" s="1"/>
-      <c r="T75" s="1"/>
-    </row>
-    <row r="76" spans="1:20" ht="168" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
+      <c r="S75" s="4"/>
+      <c r="T75" s="4"/>
+    </row>
+    <row r="76" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E76" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="G76" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1" t="s">
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="K76" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L76" s="1" t="s">
+      <c r="L76" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M76" s="1" t="s">
+      <c r="M76" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1" t="s">
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="Q76" s="1"/>
-      <c r="R76" s="1" t="s">
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="S76" s="2" t="s">
+      <c r="S76" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="T76" s="1"/>
-    </row>
-    <row r="77" spans="1:20" ht="210" x14ac:dyDescent="0.2">
-      <c r="A77" s="1" t="s">
+      <c r="T76" s="4"/>
+    </row>
+    <row r="77" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D77" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="G77" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1" t="s">
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L77" s="1" t="s">
+      <c r="L77" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M77" s="1" t="s">
+      <c r="M77" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="N77" s="1"/>
-      <c r="O77" s="1"/>
-      <c r="P77" s="1" t="s">
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="Q77" s="1"/>
-      <c r="R77" s="1" t="s">
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="S77" s="2" t="s">
+      <c r="S77" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="T77" s="1"/>
-    </row>
-    <row r="78" spans="1:20" ht="154" x14ac:dyDescent="0.2">
-      <c r="A78" s="1" t="s">
+      <c r="T77" s="4"/>
+    </row>
+    <row r="78" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D78" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E78" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="G78" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-      <c r="K78" s="1" t="s">
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L78" s="1" t="s">
+      <c r="L78" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M78" s="1" t="s">
+      <c r="M78" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="N78" s="1"/>
-      <c r="O78" s="1"/>
-      <c r="P78" s="1" t="s">
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="Q78" s="1"/>
-      <c r="R78" s="1" t="s">
+      <c r="Q78" s="4"/>
+      <c r="R78" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="S78" s="2" t="s">
+      <c r="S78" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="T78" s="1"/>
+      <c r="T78" s="4"/>
     </row>
     <row r="79" spans="1:20" ht="126" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
@@ -10007,831 +10033,831 @@
       </c>
       <c r="T79" s="1"/>
     </row>
-    <row r="80" spans="1:20" ht="238" x14ac:dyDescent="0.2">
-      <c r="A80" s="1" t="s">
+    <row r="80" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D80" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E80" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F80" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1" t="s">
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="K80" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L80" s="1" t="s">
+      <c r="L80" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M80" s="1" t="s">
+      <c r="M80" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="N80" s="1"/>
-      <c r="O80" s="1"/>
-      <c r="P80" s="1" t="s">
+      <c r="N80" s="4"/>
+      <c r="O80" s="4"/>
+      <c r="P80" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="Q80" s="1"/>
-      <c r="R80" s="1" t="s">
+      <c r="Q80" s="4"/>
+      <c r="R80" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="S80" s="1"/>
-      <c r="T80" s="1"/>
-    </row>
-    <row r="81" spans="1:20" ht="196" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
+      <c r="S80" s="4"/>
+      <c r="T80" s="4"/>
+    </row>
+    <row r="81" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D81" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E81" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F81" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="G81" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1" t="s">
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K81" s="1" t="s">
+      <c r="K81" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L81" s="1" t="s">
+      <c r="L81" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="M81" s="1"/>
-      <c r="N81" s="1"/>
-      <c r="O81" s="1"/>
-      <c r="P81" s="1" t="s">
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="Q81" s="1"/>
-      <c r="R81" s="1" t="s">
+      <c r="Q81" s="4"/>
+      <c r="R81" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="S81" s="2" t="s">
+      <c r="S81" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="T81" s="1"/>
-    </row>
-    <row r="82" spans="1:20" ht="154" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
+      <c r="T81" s="4"/>
+    </row>
+    <row r="82" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D82" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E82" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F82" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="G82" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="H82" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1" t="s">
+      <c r="I82" s="4"/>
+      <c r="J82" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K82" s="1" t="s">
+      <c r="K82" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L82" s="1" t="s">
+      <c r="L82" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M82" s="1" t="s">
+      <c r="M82" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N82" s="1"/>
-      <c r="O82" s="1"/>
-      <c r="P82" s="1" t="s">
+      <c r="N82" s="4"/>
+      <c r="O82" s="4"/>
+      <c r="P82" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="Q82" s="1"/>
-      <c r="R82" s="1" t="s">
+      <c r="Q82" s="4"/>
+      <c r="R82" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S82" s="2" t="s">
+      <c r="S82" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="T82" s="2" t="s">
+      <c r="T82" s="5" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A83" s="1" t="s">
+    <row r="83" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D83" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E83" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="F83" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G83" s="1" t="s">
+      <c r="G83" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="H83" s="1" t="s">
+      <c r="H83" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1" t="s">
+      <c r="I83" s="4"/>
+      <c r="J83" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="K83" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L83" s="1" t="s">
+      <c r="L83" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M83" s="1" t="s">
+      <c r="M83" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N83" s="1"/>
-      <c r="O83" s="1"/>
-      <c r="P83" s="1" t="s">
+      <c r="N83" s="4"/>
+      <c r="O83" s="4"/>
+      <c r="P83" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="Q83" s="1"/>
-      <c r="R83" s="1" t="s">
+      <c r="Q83" s="4"/>
+      <c r="R83" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S83" s="1"/>
-      <c r="T83" s="2" t="s">
+      <c r="S83" s="4"/>
+      <c r="T83" s="5" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="154" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
+    <row r="84" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D84" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E84" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F84" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G84" s="1" t="s">
+      <c r="G84" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="H84" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1" t="s">
+      <c r="I84" s="4"/>
+      <c r="J84" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K84" s="1" t="s">
+      <c r="K84" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L84" s="1" t="s">
+      <c r="L84" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M84" s="1" t="s">
+      <c r="M84" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N84" s="1"/>
-      <c r="O84" s="1"/>
-      <c r="P84" s="1" t="s">
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
+      <c r="P84" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="Q84" s="1"/>
-      <c r="R84" s="1" t="s">
+      <c r="Q84" s="4"/>
+      <c r="R84" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S84" s="1"/>
-      <c r="T84" s="2" t="s">
+      <c r="S84" s="4"/>
+      <c r="T84" s="5" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
+    <row r="85" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E85" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="F85" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G85" s="1" t="s">
+      <c r="G85" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="H85" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1" t="s">
+      <c r="I85" s="4"/>
+      <c r="J85" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K85" s="1" t="s">
+      <c r="K85" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L85" s="1" t="s">
+      <c r="L85" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M85" s="1" t="s">
+      <c r="M85" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N85" s="1"/>
-      <c r="O85" s="1"/>
-      <c r="P85" s="1" t="s">
+      <c r="N85" s="4"/>
+      <c r="O85" s="4"/>
+      <c r="P85" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="Q85" s="1"/>
-      <c r="R85" s="1" t="s">
+      <c r="Q85" s="4"/>
+      <c r="R85" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S85" s="1"/>
-      <c r="T85" s="2" t="s">
+      <c r="S85" s="4"/>
+      <c r="T85" s="5" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
+    <row r="86" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D86" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E86" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="F86" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G86" s="1" t="s">
+      <c r="G86" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="H86" s="1" t="s">
+      <c r="H86" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1" t="s">
+      <c r="I86" s="4"/>
+      <c r="J86" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K86" s="1" t="s">
+      <c r="K86" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L86" s="1" t="s">
+      <c r="L86" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M86" s="1"/>
-      <c r="N86" s="1"/>
-      <c r="O86" s="1"/>
-      <c r="P86" s="1" t="s">
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4"/>
+      <c r="P86" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="Q86" s="1"/>
-      <c r="R86" s="1" t="s">
+      <c r="Q86" s="4"/>
+      <c r="R86" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S86" s="2" t="s">
+      <c r="S86" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="T86" s="2" t="s">
+      <c r="T86" s="5" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
+    <row r="87" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D87" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E87" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F87" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G87" s="1" t="s">
+      <c r="G87" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="H87" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1" t="s">
+      <c r="I87" s="4"/>
+      <c r="J87" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K87" s="1" t="s">
+      <c r="K87" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L87" s="1" t="s">
+      <c r="L87" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M87" s="1" t="s">
+      <c r="M87" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N87" s="1"/>
-      <c r="O87" s="1"/>
-      <c r="P87" s="1" t="s">
+      <c r="N87" s="4"/>
+      <c r="O87" s="4"/>
+      <c r="P87" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="Q87" s="1"/>
-      <c r="R87" s="1" t="s">
+      <c r="Q87" s="4"/>
+      <c r="R87" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S87" s="1"/>
-      <c r="T87" s="2" t="s">
+      <c r="S87" s="4"/>
+      <c r="T87" s="5" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
+    <row r="88" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D88" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E88" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="F88" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G88" s="1" t="s">
+      <c r="G88" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="H88" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1" t="s">
+      <c r="I88" s="4"/>
+      <c r="J88" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="K88" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L88" s="1" t="s">
+      <c r="L88" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M88" s="1" t="s">
+      <c r="M88" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N88" s="1"/>
-      <c r="O88" s="1"/>
-      <c r="P88" s="1" t="s">
+      <c r="N88" s="4"/>
+      <c r="O88" s="4"/>
+      <c r="P88" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="Q88" s="1"/>
-      <c r="R88" s="1" t="s">
+      <c r="Q88" s="4"/>
+      <c r="R88" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S88" s="1"/>
-      <c r="T88" s="2" t="s">
+      <c r="S88" s="4"/>
+      <c r="T88" s="5" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A89" s="1" t="s">
+    <row r="89" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D89" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E89" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F89" s="1" t="s">
+      <c r="F89" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G89" s="1" t="s">
+      <c r="G89" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="H89" s="1" t="s">
+      <c r="H89" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1" t="s">
+      <c r="I89" s="4"/>
+      <c r="J89" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K89" s="1" t="s">
+      <c r="K89" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L89" s="1" t="s">
+      <c r="L89" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M89" s="1" t="s">
+      <c r="M89" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N89" s="1"/>
-      <c r="O89" s="1"/>
-      <c r="P89" s="1" t="s">
+      <c r="N89" s="4"/>
+      <c r="O89" s="4"/>
+      <c r="P89" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="Q89" s="1"/>
-      <c r="R89" s="1" t="s">
+      <c r="Q89" s="4"/>
+      <c r="R89" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S89" s="1"/>
-      <c r="T89" s="2" t="s">
+      <c r="S89" s="4"/>
+      <c r="T89" s="5" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A90" s="1" t="s">
+    <row r="90" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D90" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="E90" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="F90" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G90" s="1" t="s">
+      <c r="G90" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="H90" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1" t="s">
+      <c r="I90" s="4"/>
+      <c r="J90" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K90" s="1" t="s">
+      <c r="K90" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L90" s="1" t="s">
+      <c r="L90" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M90" s="1"/>
-      <c r="N90" s="1"/>
-      <c r="O90" s="1"/>
-      <c r="P90" s="1" t="s">
+      <c r="M90" s="4"/>
+      <c r="N90" s="4"/>
+      <c r="O90" s="4"/>
+      <c r="P90" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="Q90" s="1"/>
-      <c r="R90" s="1" t="s">
+      <c r="Q90" s="4"/>
+      <c r="R90" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S90" s="1"/>
-      <c r="T90" s="2" t="s">
+      <c r="S90" s="4"/>
+      <c r="T90" s="5" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
+    <row r="91" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E91" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F91" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G91" s="1" t="s">
+      <c r="G91" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="H91" s="1" t="s">
+      <c r="H91" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1" t="s">
+      <c r="I91" s="4"/>
+      <c r="J91" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K91" s="1" t="s">
+      <c r="K91" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L91" s="1" t="s">
+      <c r="L91" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M91" s="1" t="s">
+      <c r="M91" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N91" s="1"/>
-      <c r="O91" s="1"/>
-      <c r="P91" s="1" t="s">
+      <c r="N91" s="4"/>
+      <c r="O91" s="4"/>
+      <c r="P91" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="Q91" s="1"/>
-      <c r="R91" s="1" t="s">
+      <c r="Q91" s="4"/>
+      <c r="R91" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S91" s="1"/>
-      <c r="T91" s="2" t="s">
+      <c r="S91" s="4"/>
+      <c r="T91" s="5" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
+    <row r="92" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D92" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E92" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="F92" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G92" s="1" t="s">
+      <c r="G92" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="H92" s="1" t="s">
+      <c r="H92" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1" t="s">
+      <c r="I92" s="4"/>
+      <c r="J92" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K92" s="1" t="s">
+      <c r="K92" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L92" s="1" t="s">
+      <c r="L92" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M92" s="1" t="s">
+      <c r="M92" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N92" s="1"/>
-      <c r="O92" s="1"/>
-      <c r="P92" s="1" t="s">
+      <c r="N92" s="4"/>
+      <c r="O92" s="4"/>
+      <c r="P92" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="Q92" s="1"/>
-      <c r="R92" s="1" t="s">
+      <c r="Q92" s="4"/>
+      <c r="R92" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S92" s="1"/>
-      <c r="T92" s="2" t="s">
+      <c r="S92" s="4"/>
+      <c r="T92" s="5" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A93" s="1" t="s">
+    <row r="93" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D93" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E93" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="F93" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G93" s="1" t="s">
+      <c r="G93" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="H93" s="1" t="s">
+      <c r="H93" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1" t="s">
+      <c r="I93" s="4"/>
+      <c r="J93" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="K93" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L93" s="1" t="s">
+      <c r="L93" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M93" s="1" t="s">
+      <c r="M93" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N93" s="1"/>
-      <c r="O93" s="1"/>
-      <c r="P93" s="1" t="s">
+      <c r="N93" s="4"/>
+      <c r="O93" s="4"/>
+      <c r="P93" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="Q93" s="1"/>
-      <c r="R93" s="1" t="s">
+      <c r="Q93" s="4"/>
+      <c r="R93" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S93" s="2" t="s">
+      <c r="S93" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="T93" s="2" t="s">
+      <c r="T93" s="5" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A94" s="1" t="s">
+    <row r="94" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D94" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E94" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="F94" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G94" s="1" t="s">
+      <c r="G94" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="H94" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1" t="s">
+      <c r="I94" s="4"/>
+      <c r="J94" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="K94" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L94" s="1" t="s">
+      <c r="L94" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M94" s="1" t="s">
+      <c r="M94" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N94" s="1"/>
-      <c r="O94" s="1"/>
-      <c r="P94" s="1" t="s">
+      <c r="N94" s="4"/>
+      <c r="O94" s="4"/>
+      <c r="P94" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="Q94" s="1"/>
-      <c r="R94" s="1" t="s">
+      <c r="Q94" s="4"/>
+      <c r="R94" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S94" s="2" t="s">
+      <c r="S94" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="T94" s="2" t="s">
+      <c r="T94" s="5" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A95" s="1" t="s">
+    <row r="95" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D95" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E95" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="F95" s="1" t="s">
+      <c r="F95" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="G95" s="1" t="s">
+      <c r="G95" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="H95" s="1" t="s">
+      <c r="H95" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1" t="s">
+      <c r="I95" s="4"/>
+      <c r="J95" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K95" s="1" t="s">
+      <c r="K95" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L95" s="1" t="s">
+      <c r="L95" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M95" s="1" t="s">
+      <c r="M95" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N95" s="1"/>
-      <c r="O95" s="1"/>
-      <c r="P95" s="1" t="s">
+      <c r="N95" s="4"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="Q95" s="1"/>
-      <c r="R95" s="1" t="s">
+      <c r="Q95" s="4"/>
+      <c r="R95" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="S95" s="2" t="s">
+      <c r="S95" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="T95" s="2" t="s">
+      <c r="T95" s="5" t="s">
         <v>541</v>
       </c>
     </row>
@@ -10943,245 +10969,245 @@
         <v>584</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="140" x14ac:dyDescent="0.2">
-      <c r="A98" s="1" t="s">
+    <row r="98" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D98" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E98" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="F98" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
-      <c r="I98" s="1" t="s">
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="J98" s="1"/>
-      <c r="K98" s="1" t="s">
+      <c r="J98" s="4"/>
+      <c r="K98" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L98" s="1" t="s">
+      <c r="L98" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M98" s="1" t="s">
+      <c r="M98" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="N98" s="1"/>
-      <c r="O98" s="1"/>
-      <c r="P98" s="1" t="s">
+      <c r="N98" s="4"/>
+      <c r="O98" s="4"/>
+      <c r="P98" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="Q98" s="1"/>
-      <c r="R98" s="1" t="s">
+      <c r="Q98" s="4"/>
+      <c r="R98" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="S98" s="1"/>
-      <c r="T98" s="1"/>
-    </row>
-    <row r="99" spans="1:20" ht="140" x14ac:dyDescent="0.2">
-      <c r="A99" s="1" t="s">
+      <c r="S98" s="4"/>
+      <c r="T98" s="4"/>
+    </row>
+    <row r="99" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D99" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E99" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="F99" s="1" t="s">
+      <c r="F99" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1" t="s">
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="J99" s="1"/>
-      <c r="K99" s="1" t="s">
+      <c r="J99" s="4"/>
+      <c r="K99" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L99" s="1" t="s">
+      <c r="L99" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M99" s="1" t="s">
+      <c r="M99" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="N99" s="1"/>
-      <c r="O99" s="1"/>
-      <c r="P99" s="1" t="s">
+      <c r="N99" s="4"/>
+      <c r="O99" s="4"/>
+      <c r="P99" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="Q99" s="1"/>
-      <c r="R99" s="1" t="s">
+      <c r="Q99" s="4"/>
+      <c r="R99" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="S99" s="1"/>
-      <c r="T99" s="1"/>
-    </row>
-    <row r="100" spans="1:20" ht="70" x14ac:dyDescent="0.2">
-      <c r="A100" s="1" t="s">
+      <c r="S99" s="4"/>
+      <c r="T99" s="4"/>
+    </row>
+    <row r="100" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="4" t="s">
         <v>597</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D100" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E100" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F100" s="1" t="s">
+      <c r="F100" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="G100" s="1" t="s">
+      <c r="G100" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1" t="s">
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="K100" s="1" t="s">
+      <c r="K100" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="L100" s="1" t="s">
+      <c r="L100" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M100" s="1" t="s">
+      <c r="M100" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N100" s="1" t="s">
+      <c r="N100" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="O100" s="1"/>
-      <c r="P100" s="1"/>
-      <c r="Q100" s="1"/>
-      <c r="R100" s="1" t="s">
+      <c r="O100" s="4"/>
+      <c r="P100" s="4"/>
+      <c r="Q100" s="4"/>
+      <c r="R100" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="S100" s="2" t="s">
+      <c r="S100" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="T100" s="2" t="s">
+      <c r="T100" s="5" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A101" s="1" t="s">
+    <row r="101" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D101" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E101" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="F101" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="G101" s="1" t="s">
+      <c r="G101" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1"/>
-      <c r="K101" s="1" t="s">
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L101" s="1" t="s">
+      <c r="L101" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M101" s="1" t="s">
+      <c r="M101" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="N101" s="1" t="s">
+      <c r="N101" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="O101" s="1"/>
-      <c r="P101" s="1" t="s">
+      <c r="O101" s="4"/>
+      <c r="P101" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="Q101" s="1"/>
-      <c r="R101" s="1" t="s">
+      <c r="Q101" s="4"/>
+      <c r="R101" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="S101" s="2" t="s">
+      <c r="S101" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="T101" s="1"/>
-    </row>
-    <row r="102" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A102" s="1" t="s">
+      <c r="T101" s="4"/>
+    </row>
+    <row r="102" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D102" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E102" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F102" s="1" t="s">
+      <c r="F102" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="G102" s="1"/>
-      <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="1" t="s">
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="K102" s="1" t="s">
+      <c r="K102" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L102" s="1" t="s">
+      <c r="L102" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M102" s="1"/>
-      <c r="N102" s="1"/>
-      <c r="O102" s="1"/>
-      <c r="P102" s="1" t="s">
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="Q102" s="1"/>
-      <c r="R102" s="1" t="s">
+      <c r="Q102" s="4"/>
+      <c r="R102" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="S102" s="2" t="s">
+      <c r="S102" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="T102" s="1"/>
+      <c r="T102" s="4"/>
     </row>
     <row r="103" spans="1:20" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
@@ -11241,141 +11267,141 @@
       </c>
       <c r="T103" s="1"/>
     </row>
-    <row r="104" spans="1:20" ht="182" x14ac:dyDescent="0.2">
-      <c r="A104" s="1" t="s">
+    <row r="104" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B104" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C104" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="D104" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E104" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F104" s="1" t="s">
+      <c r="F104" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="G104" s="1" t="s">
+      <c r="G104" s="4" t="s">
         <v>633</v>
       </c>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1" t="s">
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="K104" s="1" t="s">
+      <c r="K104" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L104" s="1" t="s">
+      <c r="L104" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M104" s="1"/>
-      <c r="N104" s="1"/>
-      <c r="O104" s="1"/>
-      <c r="P104" s="1" t="s">
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="Q104" s="1"/>
-      <c r="R104" s="1" t="s">
+      <c r="Q104" s="4"/>
+      <c r="R104" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="S104" s="2" t="s">
+      <c r="S104" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="T104" s="1"/>
-    </row>
-    <row r="105" spans="1:20" ht="266" x14ac:dyDescent="0.2">
-      <c r="A105" s="1" t="s">
+      <c r="T104" s="4"/>
+    </row>
+    <row r="105" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="4" t="s">
         <v>637</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B105" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D105" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E105" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F105" s="1" t="s">
+      <c r="F105" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
-      <c r="J105" s="1"/>
-      <c r="K105" s="1" t="s">
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L105" s="1" t="s">
+      <c r="L105" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="M105" s="1" t="s">
+      <c r="M105" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="N105" s="1"/>
-      <c r="O105" s="1"/>
-      <c r="P105" s="1" t="s">
+      <c r="N105" s="4"/>
+      <c r="O105" s="4"/>
+      <c r="P105" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="Q105" s="1"/>
-      <c r="R105" s="1" t="s">
+      <c r="Q105" s="4"/>
+      <c r="R105" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S105" s="1"/>
-      <c r="T105" s="1"/>
-    </row>
-    <row r="106" spans="1:20" ht="196" x14ac:dyDescent="0.2">
-      <c r="A106" s="1" t="s">
+      <c r="S105" s="4"/>
+      <c r="T105" s="4"/>
+    </row>
+    <row r="106" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B106" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C106" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D106" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E106" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F106" s="1" t="s">
+      <c r="F106" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="1"/>
-      <c r="K106" s="1" t="s">
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L106" s="1" t="s">
+      <c r="L106" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="M106" s="1" t="s">
+      <c r="M106" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="N106" s="1"/>
-      <c r="O106" s="1"/>
-      <c r="P106" s="1" t="s">
+      <c r="N106" s="4"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="Q106" s="1"/>
-      <c r="R106" s="1" t="s">
+      <c r="Q106" s="4"/>
+      <c r="R106" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S106" s="1"/>
-      <c r="T106" s="1"/>
+      <c r="S106" s="4"/>
+      <c r="T106" s="4"/>
     </row>
     <row r="107" spans="1:20" ht="182" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
@@ -11465,371 +11491,371 @@
       <c r="S108" s="1"/>
       <c r="T108" s="1"/>
     </row>
-    <row r="109" spans="1:20" ht="168" x14ac:dyDescent="0.2">
-      <c r="A109" s="1" t="s">
+    <row r="109" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B109" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C109" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="D109" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="E109" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F109" s="1" t="s">
+      <c r="F109" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="G109" s="1"/>
-      <c r="H109" s="1"/>
-      <c r="I109" s="1"/>
-      <c r="J109" s="1"/>
-      <c r="K109" s="1" t="s">
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L109" s="1" t="s">
+      <c r="L109" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M109" s="1" t="s">
+      <c r="M109" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="N109" s="1"/>
-      <c r="O109" s="1"/>
-      <c r="P109" s="1" t="s">
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4" t="s">
         <v>657</v>
       </c>
-      <c r="Q109" s="1"/>
-      <c r="R109" s="1" t="s">
+      <c r="Q109" s="4"/>
+      <c r="R109" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S109" s="1"/>
-      <c r="T109" s="1"/>
-    </row>
-    <row r="110" spans="1:20" ht="280" x14ac:dyDescent="0.2">
-      <c r="A110" s="1" t="s">
+      <c r="S109" s="4"/>
+      <c r="T109" s="4"/>
+    </row>
+    <row r="110" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B110" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C110" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D110" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E110" s="1" t="s">
+      <c r="E110" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="F110" s="1" t="s">
+      <c r="F110" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="G110" s="1"/>
-      <c r="H110" s="1"/>
-      <c r="I110" s="1"/>
-      <c r="J110" s="1"/>
-      <c r="K110" s="1" t="s">
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L110" s="1" t="s">
+      <c r="L110" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M110" s="1" t="s">
+      <c r="M110" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="N110" s="1"/>
-      <c r="O110" s="1"/>
-      <c r="P110" s="1" t="s">
+      <c r="N110" s="4"/>
+      <c r="O110" s="4"/>
+      <c r="P110" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="Q110" s="1"/>
-      <c r="R110" s="1" t="s">
+      <c r="Q110" s="4"/>
+      <c r="R110" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S110" s="1"/>
-      <c r="T110" s="1"/>
-    </row>
-    <row r="111" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A111" s="1" t="s">
+      <c r="S110" s="4"/>
+      <c r="T110" s="4"/>
+    </row>
+    <row r="111" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="4" t="s">
         <v>663</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B111" s="4" t="s">
         <v>664</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C111" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="D111" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="E111" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F111" s="1" t="s">
+      <c r="F111" s="4" t="s">
         <v>665</v>
       </c>
-      <c r="G111" s="1"/>
-      <c r="H111" s="1"/>
-      <c r="I111" s="1"/>
-      <c r="J111" s="1"/>
-      <c r="K111" s="1" t="s">
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L111" s="1" t="s">
+      <c r="L111" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M111" s="1" t="s">
+      <c r="M111" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="N111" s="1"/>
-      <c r="O111" s="1"/>
-      <c r="P111" s="1" t="s">
+      <c r="N111" s="4"/>
+      <c r="O111" s="4"/>
+      <c r="P111" s="4" t="s">
         <v>666</v>
       </c>
-      <c r="Q111" s="1"/>
-      <c r="R111" s="1" t="s">
+      <c r="Q111" s="4"/>
+      <c r="R111" s="4" t="s">
         <v>667</v>
       </c>
-      <c r="S111" s="1"/>
-      <c r="T111" s="1"/>
-    </row>
-    <row r="112" spans="1:20" ht="154" x14ac:dyDescent="0.2">
-      <c r="A112" s="1" t="s">
+      <c r="S111" s="4"/>
+      <c r="T111" s="4"/>
+    </row>
+    <row r="112" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B112" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C112" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="D112" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="E112" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F112" s="1" t="s">
+      <c r="F112" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="G112" s="1" t="s">
+      <c r="G112" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="H112" s="1"/>
-      <c r="I112" s="1"/>
-      <c r="J112" s="1"/>
-      <c r="K112" s="1" t="s">
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L112" s="1" t="s">
+      <c r="L112" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M112" s="1"/>
-      <c r="N112" s="1"/>
-      <c r="O112" s="1"/>
-      <c r="P112" s="1" t="s">
+      <c r="M112" s="4"/>
+      <c r="N112" s="4"/>
+      <c r="O112" s="4"/>
+      <c r="P112" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="Q112" s="1"/>
-      <c r="R112" s="1" t="s">
+      <c r="Q112" s="4"/>
+      <c r="R112" s="4" t="s">
         <v>673</v>
       </c>
-      <c r="S112" s="2" t="s">
+      <c r="S112" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="T112" s="1"/>
-    </row>
-    <row r="113" spans="1:20" ht="210" x14ac:dyDescent="0.2">
-      <c r="A113" s="1" t="s">
+      <c r="T112" s="4"/>
+    </row>
+    <row r="113" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B113" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C113" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="D113" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E113" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="F113" s="1" t="s">
+      <c r="F113" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="G113" s="1" t="s">
+      <c r="G113" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="H113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1" t="s">
+      <c r="H113" s="4"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K113" s="1" t="s">
+      <c r="K113" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L113" s="1" t="s">
+      <c r="L113" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M113" s="1" t="s">
+      <c r="M113" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="N113" s="1"/>
-      <c r="O113" s="1"/>
-      <c r="P113" s="1" t="s">
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
+      <c r="P113" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="Q113" s="1"/>
-      <c r="R113" s="1" t="s">
+      <c r="Q113" s="4"/>
+      <c r="R113" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S113" s="1"/>
-      <c r="T113" s="1"/>
-    </row>
-    <row r="114" spans="1:20" ht="140" x14ac:dyDescent="0.2">
-      <c r="A114" s="1" t="s">
+      <c r="S113" s="4"/>
+      <c r="T113" s="4"/>
+    </row>
+    <row r="114" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B114" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="D114" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E114" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F114" s="1" t="s">
+      <c r="F114" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="G114" s="1" t="s">
+      <c r="G114" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="H114" s="1"/>
-      <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
-      <c r="K114" s="1" t="s">
+      <c r="H114" s="4"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L114" s="1" t="s">
+      <c r="L114" s="4" t="s">
         <v>683</v>
       </c>
-      <c r="M114" s="1" t="s">
+      <c r="M114" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="N114" s="1"/>
-      <c r="O114" s="1"/>
-      <c r="P114" s="1" t="s">
+      <c r="N114" s="4"/>
+      <c r="O114" s="4"/>
+      <c r="P114" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="Q114" s="1"/>
-      <c r="R114" s="1" t="s">
+      <c r="Q114" s="4"/>
+      <c r="R114" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S114" s="1"/>
-      <c r="T114" s="1"/>
-    </row>
-    <row r="115" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A115" s="1" t="s">
+      <c r="S114" s="4"/>
+      <c r="T114" s="4"/>
+    </row>
+    <row r="115" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="D115" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E115" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F115" s="1" t="s">
+      <c r="F115" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="G115" s="1" t="s">
+      <c r="G115" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="H115" s="1"/>
-      <c r="I115" s="1" t="s">
+      <c r="H115" s="4"/>
+      <c r="I115" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="J115" s="1"/>
-      <c r="K115" s="1" t="s">
+      <c r="J115" s="4"/>
+      <c r="K115" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L115" s="1" t="s">
+      <c r="L115" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M115" s="1"/>
-      <c r="N115" s="1"/>
-      <c r="O115" s="1"/>
-      <c r="P115" s="1" t="s">
+      <c r="M115" s="4"/>
+      <c r="N115" s="4"/>
+      <c r="O115" s="4"/>
+      <c r="P115" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="Q115" s="1"/>
-      <c r="R115" s="1" t="s">
+      <c r="Q115" s="4"/>
+      <c r="R115" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="S115" s="2" t="s">
+      <c r="S115" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="T115" s="1"/>
-    </row>
-    <row r="116" spans="1:20" ht="210" x14ac:dyDescent="0.2">
-      <c r="A116" s="1" t="s">
+      <c r="T115" s="4"/>
+    </row>
+    <row r="116" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D116" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E116" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F116" s="1" t="s">
+      <c r="F116" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="G116" s="1" t="s">
+      <c r="G116" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="H116" s="1"/>
-      <c r="I116" s="1"/>
-      <c r="J116" s="1"/>
-      <c r="K116" s="1" t="s">
+      <c r="H116" s="4"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L116" s="1" t="s">
+      <c r="L116" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M116" s="1"/>
-      <c r="N116" s="1"/>
-      <c r="O116" s="1"/>
-      <c r="P116" s="1" t="s">
+      <c r="M116" s="4"/>
+      <c r="N116" s="4"/>
+      <c r="O116" s="4"/>
+      <c r="P116" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="Q116" s="1"/>
-      <c r="R116" s="1" t="s">
+      <c r="Q116" s="4"/>
+      <c r="R116" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="S116" s="2" t="s">
+      <c r="S116" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="T116" s="1"/>
+      <c r="T116" s="4"/>
     </row>
     <row r="117" spans="1:20" ht="196" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
@@ -11931,767 +11957,767 @@
       </c>
       <c r="T118" s="1"/>
     </row>
-    <row r="119" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A119" s="1" t="s">
+    <row r="119" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D119" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="E119" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="F119" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="G119" s="1" t="s">
+      <c r="G119" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="H119" s="1"/>
-      <c r="I119" s="1"/>
-      <c r="J119" s="1" t="s">
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K119" s="1" t="s">
+      <c r="K119" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L119" s="1" t="s">
+      <c r="L119" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M119" s="1" t="s">
+      <c r="M119" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N119" s="1"/>
-      <c r="O119" s="1"/>
-      <c r="P119" s="1" t="s">
+      <c r="N119" s="4"/>
+      <c r="O119" s="4"/>
+      <c r="P119" s="4" t="s">
         <v>709</v>
       </c>
-      <c r="Q119" s="1"/>
-      <c r="R119" s="1" t="s">
+      <c r="Q119" s="4"/>
+      <c r="R119" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S119" s="2" t="s">
+      <c r="S119" s="5" t="s">
         <v>699</v>
       </c>
-      <c r="T119" s="1"/>
-    </row>
-    <row r="120" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A120" s="1" t="s">
+      <c r="T119" s="4"/>
+    </row>
+    <row r="120" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B120" s="4" t="s">
         <v>711</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C120" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="D120" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E120" s="1" t="s">
+      <c r="E120" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F120" s="1" t="s">
+      <c r="F120" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="G120" s="1" t="s">
+      <c r="G120" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="H120" s="1"/>
-      <c r="I120" s="1"/>
-      <c r="J120" s="1" t="s">
+      <c r="H120" s="4"/>
+      <c r="I120" s="4"/>
+      <c r="J120" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K120" s="1" t="s">
+      <c r="K120" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L120" s="1" t="s">
+      <c r="L120" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M120" s="1" t="s">
+      <c r="M120" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N120" s="1"/>
-      <c r="O120" s="1"/>
-      <c r="P120" s="1" t="s">
+      <c r="N120" s="4"/>
+      <c r="O120" s="4"/>
+      <c r="P120" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="Q120" s="1"/>
-      <c r="R120" s="1" t="s">
+      <c r="Q120" s="4"/>
+      <c r="R120" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S120" s="2" t="s">
+      <c r="S120" s="5" t="s">
         <v>699</v>
       </c>
-      <c r="T120" s="1"/>
-    </row>
-    <row r="121" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A121" s="1" t="s">
+      <c r="T120" s="4"/>
+    </row>
+    <row r="121" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="D121" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="E121" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F121" s="1" t="s">
+      <c r="F121" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="G121" s="1"/>
-      <c r="H121" s="1"/>
-      <c r="I121" s="1"/>
-      <c r="J121" s="1" t="s">
+      <c r="G121" s="4"/>
+      <c r="H121" s="4"/>
+      <c r="I121" s="4"/>
+      <c r="J121" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K121" s="1" t="s">
+      <c r="K121" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L121" s="1" t="s">
+      <c r="L121" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M121" s="1" t="s">
+      <c r="M121" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N121" s="1"/>
-      <c r="O121" s="1"/>
-      <c r="P121" s="1" t="s">
+      <c r="N121" s="4"/>
+      <c r="O121" s="4"/>
+      <c r="P121" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="Q121" s="1"/>
-      <c r="R121" s="1" t="s">
+      <c r="Q121" s="4"/>
+      <c r="R121" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S121" s="2" t="s">
+      <c r="S121" s="5" t="s">
         <v>716</v>
       </c>
-      <c r="T121" s="2" t="s">
+      <c r="T121" s="5" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A122" s="1" t="s">
+    <row r="122" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D122" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="E122" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="F122" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="1" t="s">
+      <c r="G122" s="4"/>
+      <c r="H122" s="4"/>
+      <c r="I122" s="4"/>
+      <c r="J122" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K122" s="1" t="s">
+      <c r="K122" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L122" s="1" t="s">
+      <c r="L122" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M122" s="1"/>
-      <c r="N122" s="1"/>
-      <c r="O122" s="1"/>
-      <c r="P122" s="1" t="s">
+      <c r="M122" s="4"/>
+      <c r="N122" s="4"/>
+      <c r="O122" s="4"/>
+      <c r="P122" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="Q122" s="1"/>
-      <c r="R122" s="1" t="s">
+      <c r="Q122" s="4"/>
+      <c r="R122" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S122" s="1"/>
-      <c r="T122" s="1"/>
-    </row>
-    <row r="123" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A123" s="1" t="s">
+      <c r="S122" s="4"/>
+      <c r="T122" s="4"/>
+    </row>
+    <row r="123" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C123" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="D123" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="E123" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F123" s="1" t="s">
+      <c r="F123" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1" t="s">
+      <c r="G123" s="4"/>
+      <c r="H123" s="4"/>
+      <c r="I123" s="4"/>
+      <c r="J123" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K123" s="1" t="s">
+      <c r="K123" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L123" s="1" t="s">
+      <c r="L123" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M123" s="1" t="s">
+      <c r="M123" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N123" s="1"/>
-      <c r="O123" s="1"/>
-      <c r="P123" s="1" t="s">
+      <c r="N123" s="4"/>
+      <c r="O123" s="4"/>
+      <c r="P123" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="Q123" s="1"/>
-      <c r="R123" s="1" t="s">
+      <c r="Q123" s="4"/>
+      <c r="R123" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S123" s="1"/>
-      <c r="T123" s="1"/>
-    </row>
-    <row r="124" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A124" s="1" t="s">
+      <c r="S123" s="4"/>
+      <c r="T123" s="4"/>
+    </row>
+    <row r="124" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B124" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C124" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="D124" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="E124" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="F124" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="G124" s="1"/>
-      <c r="H124" s="1"/>
-      <c r="I124" s="1"/>
-      <c r="J124" s="1" t="s">
+      <c r="G124" s="4"/>
+      <c r="H124" s="4"/>
+      <c r="I124" s="4"/>
+      <c r="J124" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K124" s="1" t="s">
+      <c r="K124" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L124" s="1" t="s">
+      <c r="L124" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M124" s="1" t="s">
+      <c r="M124" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N124" s="1"/>
-      <c r="O124" s="1"/>
-      <c r="P124" s="1" t="s">
+      <c r="N124" s="4"/>
+      <c r="O124" s="4"/>
+      <c r="P124" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="Q124" s="1"/>
-      <c r="R124" s="1" t="s">
+      <c r="Q124" s="4"/>
+      <c r="R124" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S124" s="1"/>
-      <c r="T124" s="1"/>
-    </row>
-    <row r="125" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A125" s="1" t="s">
+      <c r="S124" s="4"/>
+      <c r="T124" s="4"/>
+    </row>
+    <row r="125" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B125" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D125" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E125" s="1" t="s">
+      <c r="E125" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="F125" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="G125" s="1"/>
-      <c r="H125" s="1"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="1" t="s">
+      <c r="G125" s="4"/>
+      <c r="H125" s="4"/>
+      <c r="I125" s="4"/>
+      <c r="J125" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K125" s="1" t="s">
+      <c r="K125" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L125" s="1" t="s">
+      <c r="L125" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M125" s="1" t="s">
+      <c r="M125" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N125" s="1"/>
-      <c r="O125" s="1"/>
-      <c r="P125" s="1" t="s">
+      <c r="N125" s="4"/>
+      <c r="O125" s="4"/>
+      <c r="P125" s="4" t="s">
         <v>709</v>
       </c>
-      <c r="Q125" s="1"/>
-      <c r="R125" s="1" t="s">
+      <c r="Q125" s="4"/>
+      <c r="R125" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S125" s="2" t="s">
+      <c r="S125" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="T125" s="1"/>
-    </row>
-    <row r="126" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A126" s="1" t="s">
+      <c r="T125" s="4"/>
+    </row>
+    <row r="126" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B126" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C126" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="D126" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E126" s="1" t="s">
+      <c r="E126" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="F126" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1" t="s">
+      <c r="G126" s="4"/>
+      <c r="H126" s="4"/>
+      <c r="I126" s="4"/>
+      <c r="J126" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K126" s="1" t="s">
+      <c r="K126" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L126" s="1" t="s">
+      <c r="L126" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M126" s="1" t="s">
+      <c r="M126" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N126" s="1"/>
-      <c r="O126" s="1"/>
-      <c r="P126" s="1" t="s">
+      <c r="N126" s="4"/>
+      <c r="O126" s="4"/>
+      <c r="P126" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="Q126" s="1"/>
-      <c r="R126" s="1" t="s">
+      <c r="Q126" s="4"/>
+      <c r="R126" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S126" s="1"/>
-      <c r="T126" s="1"/>
-    </row>
-    <row r="127" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A127" s="1" t="s">
+      <c r="S126" s="4"/>
+      <c r="T126" s="4"/>
+    </row>
+    <row r="127" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B127" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C127" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D127" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="E127" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="F127" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="G127" s="1"/>
-      <c r="H127" s="1"/>
-      <c r="I127" s="1"/>
-      <c r="J127" s="1" t="s">
+      <c r="G127" s="4"/>
+      <c r="H127" s="4"/>
+      <c r="I127" s="4"/>
+      <c r="J127" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K127" s="1" t="s">
+      <c r="K127" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L127" s="1" t="s">
+      <c r="L127" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M127" s="1" t="s">
+      <c r="M127" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N127" s="1"/>
-      <c r="O127" s="1"/>
-      <c r="P127" s="1" t="s">
+      <c r="N127" s="4"/>
+      <c r="O127" s="4"/>
+      <c r="P127" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="Q127" s="1"/>
-      <c r="R127" s="1" t="s">
+      <c r="Q127" s="4"/>
+      <c r="R127" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S127" s="1"/>
-      <c r="T127" s="1"/>
-    </row>
-    <row r="128" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A128" s="1" t="s">
+      <c r="S127" s="4"/>
+      <c r="T127" s="4"/>
+    </row>
+    <row r="128" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B128" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C128" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D128" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="E128" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="F128" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="G128" s="1"/>
-      <c r="H128" s="1"/>
-      <c r="I128" s="1"/>
-      <c r="J128" s="1" t="s">
+      <c r="G128" s="4"/>
+      <c r="H128" s="4"/>
+      <c r="I128" s="4"/>
+      <c r="J128" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K128" s="1" t="s">
+      <c r="K128" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L128" s="1" t="s">
+      <c r="L128" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M128" s="1" t="s">
+      <c r="M128" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N128" s="1"/>
-      <c r="O128" s="1"/>
-      <c r="P128" s="1" t="s">
+      <c r="N128" s="4"/>
+      <c r="O128" s="4"/>
+      <c r="P128" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="Q128" s="1"/>
-      <c r="R128" s="1" t="s">
+      <c r="Q128" s="4"/>
+      <c r="R128" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S128" s="1"/>
-      <c r="T128" s="1"/>
-    </row>
-    <row r="129" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A129" s="1" t="s">
+      <c r="S128" s="4"/>
+      <c r="T128" s="4"/>
+    </row>
+    <row r="129" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B129" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C129" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D129" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="E129" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="F129" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="G129" s="1" t="s">
+      <c r="G129" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="H129" s="1"/>
-      <c r="I129" s="1"/>
-      <c r="J129" s="1" t="s">
+      <c r="H129" s="4"/>
+      <c r="I129" s="4"/>
+      <c r="J129" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K129" s="1" t="s">
+      <c r="K129" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L129" s="1" t="s">
+      <c r="L129" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M129" s="1" t="s">
+      <c r="M129" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N129" s="1"/>
-      <c r="O129" s="1"/>
-      <c r="P129" s="1" t="s">
+      <c r="N129" s="4"/>
+      <c r="O129" s="4"/>
+      <c r="P129" s="4" t="s">
         <v>709</v>
       </c>
-      <c r="Q129" s="1"/>
-      <c r="R129" s="1" t="s">
+      <c r="Q129" s="4"/>
+      <c r="R129" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S129" s="2" t="s">
+      <c r="S129" s="5" t="s">
         <v>699</v>
       </c>
-      <c r="T129" s="1"/>
-    </row>
-    <row r="130" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A130" s="1" t="s">
+      <c r="T129" s="4"/>
+    </row>
+    <row r="130" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B130" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C130" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D130" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="E130" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F130" s="1" t="s">
+      <c r="F130" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="G130" s="1"/>
-      <c r="H130" s="1"/>
-      <c r="I130" s="1"/>
-      <c r="J130" s="1" t="s">
+      <c r="G130" s="4"/>
+      <c r="H130" s="4"/>
+      <c r="I130" s="4"/>
+      <c r="J130" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K130" s="1" t="s">
+      <c r="K130" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L130" s="1" t="s">
+      <c r="L130" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M130" s="1" t="s">
+      <c r="M130" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N130" s="1"/>
-      <c r="O130" s="1"/>
-      <c r="P130" s="1" t="s">
+      <c r="N130" s="4"/>
+      <c r="O130" s="4"/>
+      <c r="P130" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="Q130" s="1"/>
-      <c r="R130" s="1" t="s">
+      <c r="Q130" s="4"/>
+      <c r="R130" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S130" s="1"/>
-      <c r="T130" s="1"/>
-    </row>
-    <row r="131" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A131" s="1" t="s">
+      <c r="S130" s="4"/>
+      <c r="T130" s="4"/>
+    </row>
+    <row r="131" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B131" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C131" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D131" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E131" s="1" t="s">
+      <c r="E131" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="F131" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="G131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1" t="s">
+      <c r="G131" s="4"/>
+      <c r="H131" s="4"/>
+      <c r="I131" s="4"/>
+      <c r="J131" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K131" s="1" t="s">
+      <c r="K131" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L131" s="1" t="s">
+      <c r="L131" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M131" s="1" t="s">
+      <c r="M131" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N131" s="1"/>
-      <c r="O131" s="1"/>
-      <c r="P131" s="1" t="s">
+      <c r="N131" s="4"/>
+      <c r="O131" s="4"/>
+      <c r="P131" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="Q131" s="1"/>
-      <c r="R131" s="1" t="s">
+      <c r="Q131" s="4"/>
+      <c r="R131" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S131" s="1"/>
-      <c r="T131" s="1"/>
-    </row>
-    <row r="132" spans="1:20" ht="70" x14ac:dyDescent="0.2">
-      <c r="A132" s="1" t="s">
+      <c r="S131" s="4"/>
+      <c r="T131" s="4"/>
+    </row>
+    <row r="132" spans="1:20" s="13" customFormat="1" ht="70" x14ac:dyDescent="0.2">
+      <c r="A132" s="11" t="s">
         <v>739</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="B132" s="11" t="s">
         <v>740</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C132" s="11" t="s">
         <v>631</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D132" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E132" s="1" t="s">
+      <c r="E132" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="F132" s="1" t="s">
+      <c r="F132" s="11" t="s">
         <v>741</v>
       </c>
-      <c r="G132" s="1"/>
-      <c r="H132" s="1"/>
-      <c r="I132" s="1" t="s">
+      <c r="G132" s="11"/>
+      <c r="H132" s="11"/>
+      <c r="I132" s="11" t="s">
         <v>742</v>
       </c>
-      <c r="J132" s="1" t="s">
+      <c r="J132" s="11" t="s">
         <v>743</v>
       </c>
-      <c r="K132" s="1" t="s">
+      <c r="K132" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="L132" s="1" t="s">
+      <c r="L132" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="M132" s="1" t="s">
+      <c r="M132" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="N132" s="1"/>
-      <c r="O132" s="1"/>
-      <c r="P132" s="1"/>
-      <c r="Q132" s="1"/>
-      <c r="R132" s="1" t="s">
+      <c r="N132" s="11"/>
+      <c r="O132" s="11"/>
+      <c r="P132" s="11"/>
+      <c r="Q132" s="11"/>
+      <c r="R132" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="S132" s="2" t="s">
+      <c r="S132" s="12" t="s">
         <v>744</v>
       </c>
-      <c r="T132" s="2" t="s">
+      <c r="T132" s="12" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="133" spans="1:20" ht="140" x14ac:dyDescent="0.2">
-      <c r="A133" s="1" t="s">
+    <row r="133" spans="1:20" s="13" customFormat="1" ht="140" x14ac:dyDescent="0.2">
+      <c r="A133" s="11" t="s">
         <v>745</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B133" s="11" t="s">
         <v>746</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="C133" s="11" t="s">
         <v>631</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="D133" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E133" s="1" t="s">
+      <c r="E133" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="F133" s="1" t="s">
+      <c r="F133" s="11" t="s">
         <v>747</v>
       </c>
-      <c r="G133" s="1"/>
-      <c r="H133" s="1"/>
-      <c r="I133" s="1" t="s">
+      <c r="G133" s="11"/>
+      <c r="H133" s="11"/>
+      <c r="I133" s="11" t="s">
         <v>748</v>
       </c>
-      <c r="J133" s="1" t="s">
+      <c r="J133" s="11" t="s">
         <v>743</v>
       </c>
-      <c r="K133" s="1" t="s">
+      <c r="K133" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="L133" s="1" t="s">
+      <c r="L133" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="M133" s="1" t="s">
+      <c r="M133" s="11" t="s">
         <v>749</v>
       </c>
-      <c r="N133" s="1"/>
-      <c r="O133" s="1"/>
-      <c r="P133" s="1" t="s">
+      <c r="N133" s="11"/>
+      <c r="O133" s="11"/>
+      <c r="P133" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="Q133" s="1"/>
-      <c r="R133" s="1" t="s">
+      <c r="Q133" s="11"/>
+      <c r="R133" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="S133" s="2" t="s">
+      <c r="S133" s="12" t="s">
         <v>751</v>
       </c>
-      <c r="T133" s="1"/>
-    </row>
-    <row r="134" spans="1:20" ht="70" x14ac:dyDescent="0.2">
-      <c r="A134" s="1" t="s">
+      <c r="T133" s="11"/>
+    </row>
+    <row r="134" spans="1:20" s="13" customFormat="1" ht="70" x14ac:dyDescent="0.2">
+      <c r="A134" s="11" t="s">
         <v>752</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B134" s="11" t="s">
         <v>753</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="C134" s="11" t="s">
         <v>631</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D134" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="E134" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="F134" s="1" t="s">
+      <c r="F134" s="11" t="s">
         <v>754</v>
       </c>
-      <c r="G134" s="1"/>
-      <c r="H134" s="1"/>
-      <c r="I134" s="1" t="s">
+      <c r="G134" s="11"/>
+      <c r="H134" s="11"/>
+      <c r="I134" s="11" t="s">
         <v>755</v>
       </c>
-      <c r="J134" s="1" t="s">
+      <c r="J134" s="11" t="s">
         <v>743</v>
       </c>
-      <c r="K134" s="1" t="s">
+      <c r="K134" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="L134" s="1" t="s">
+      <c r="L134" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="M134" s="1" t="s">
+      <c r="M134" s="11" t="s">
         <v>749</v>
       </c>
-      <c r="N134" s="1"/>
-      <c r="O134" s="1"/>
-      <c r="P134" s="1"/>
-      <c r="Q134" s="1"/>
-      <c r="R134" s="1" t="s">
+      <c r="N134" s="11"/>
+      <c r="O134" s="11"/>
+      <c r="P134" s="11"/>
+      <c r="Q134" s="11"/>
+      <c r="R134" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="S134" s="2" t="s">
+      <c r="S134" s="12" t="s">
         <v>744</v>
       </c>
-      <c r="T134" s="2" t="s">
+      <c r="T134" s="12" t="s">
         <v>345</v>
       </c>
     </row>
@@ -12743,103 +12769,103 @@
         <v>345</v>
       </c>
     </row>
-    <row r="136" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A136" s="1" t="s">
+    <row r="136" spans="1:20" s="10" customFormat="1" ht="112" x14ac:dyDescent="0.2">
+      <c r="A136" s="8" t="s">
         <v>762</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="B136" s="8" t="s">
         <v>763</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="C136" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="D136" s="8" t="s">
         <v>764</v>
       </c>
-      <c r="E136" s="1" t="s">
+      <c r="E136" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F136" s="1" t="s">
+      <c r="F136" s="8" t="s">
         <v>765</v>
       </c>
-      <c r="G136" s="1" t="s">
+      <c r="G136" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="H136" s="1"/>
-      <c r="I136" s="1"/>
-      <c r="J136" s="1" t="s">
+      <c r="H136" s="8"/>
+      <c r="I136" s="8"/>
+      <c r="J136" s="8" t="s">
         <v>766</v>
       </c>
-      <c r="K136" s="1" t="s">
+      <c r="K136" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="L136" s="1" t="s">
+      <c r="L136" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M136" s="1"/>
-      <c r="N136" s="1"/>
-      <c r="O136" s="1"/>
-      <c r="P136" s="1" t="s">
+      <c r="M136" s="8"/>
+      <c r="N136" s="8"/>
+      <c r="O136" s="8"/>
+      <c r="P136" s="8" t="s">
         <v>767</v>
       </c>
-      <c r="Q136" s="1"/>
-      <c r="R136" s="1" t="s">
+      <c r="Q136" s="8"/>
+      <c r="R136" s="8" t="s">
         <v>760</v>
       </c>
-      <c r="S136" s="2" t="s">
+      <c r="S136" s="9" t="s">
         <v>768</v>
       </c>
-      <c r="T136" s="2" t="s">
+      <c r="T136" s="9" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="137" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A137" s="1" t="s">
+    <row r="137" spans="1:20" s="10" customFormat="1" ht="112" x14ac:dyDescent="0.2">
+      <c r="A137" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B137" s="8" t="s">
         <v>771</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="C137" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="D137" s="8" t="s">
         <v>772</v>
       </c>
-      <c r="E137" s="1" t="s">
+      <c r="E137" s="8" t="s">
         <v>773</v>
       </c>
-      <c r="F137" s="1" t="s">
+      <c r="F137" s="8" t="s">
         <v>774</v>
       </c>
-      <c r="G137" s="1" t="s">
+      <c r="G137" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="H137" s="1"/>
-      <c r="I137" s="1"/>
-      <c r="J137" s="1" t="s">
+      <c r="H137" s="8"/>
+      <c r="I137" s="8"/>
+      <c r="J137" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="K137" s="1" t="s">
+      <c r="K137" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="L137" s="1" t="s">
+      <c r="L137" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M137" s="1"/>
-      <c r="N137" s="1"/>
-      <c r="O137" s="1"/>
-      <c r="P137" s="1" t="s">
+      <c r="M137" s="8"/>
+      <c r="N137" s="8"/>
+      <c r="O137" s="8"/>
+      <c r="P137" s="8" t="s">
         <v>775</v>
       </c>
-      <c r="Q137" s="1"/>
-      <c r="R137" s="1" t="s">
+      <c r="Q137" s="8"/>
+      <c r="R137" s="8" t="s">
         <v>776</v>
       </c>
-      <c r="S137" s="2" t="s">
+      <c r="S137" s="9" t="s">
         <v>777</v>
       </c>
-      <c r="T137" s="1"/>
+      <c r="T137" s="8"/>
     </row>
     <row r="138" spans="1:20" ht="98" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
@@ -12889,149 +12915,149 @@
       </c>
       <c r="T138" s="1"/>
     </row>
-    <row r="139" spans="1:20" ht="84" x14ac:dyDescent="0.2">
-      <c r="A139" s="1" t="s">
+    <row r="139" spans="1:20" s="13" customFormat="1" ht="84" x14ac:dyDescent="0.2">
+      <c r="A139" s="11" t="s">
         <v>785</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B139" s="11" t="s">
         <v>786</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="C139" s="11" t="s">
         <v>631</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="D139" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="E139" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F139" s="1" t="s">
+      <c r="F139" s="11" t="s">
         <v>787</v>
       </c>
-      <c r="G139" s="1" t="s">
+      <c r="G139" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="H139" s="1"/>
-      <c r="I139" s="1"/>
-      <c r="J139" s="1" t="s">
+      <c r="H139" s="11"/>
+      <c r="I139" s="11"/>
+      <c r="J139" s="11" t="s">
         <v>788</v>
       </c>
-      <c r="K139" s="1" t="s">
+      <c r="K139" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="L139" s="1" t="s">
+      <c r="L139" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="M139" s="1"/>
-      <c r="N139" s="1"/>
-      <c r="O139" s="1"/>
-      <c r="P139" s="1" t="s">
+      <c r="M139" s="11"/>
+      <c r="N139" s="11"/>
+      <c r="O139" s="11"/>
+      <c r="P139" s="11" t="s">
         <v>789</v>
       </c>
-      <c r="Q139" s="1"/>
-      <c r="R139" s="1" t="s">
+      <c r="Q139" s="11"/>
+      <c r="R139" s="11" t="s">
         <v>760</v>
       </c>
-      <c r="S139" s="2" t="s">
+      <c r="S139" s="12" t="s">
         <v>790</v>
       </c>
-      <c r="T139" s="1"/>
-    </row>
-    <row r="140" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A140" s="1" t="s">
+      <c r="T139" s="11"/>
+    </row>
+    <row r="140" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B140" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="C140" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="D140" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="E140" s="1" t="s">
+      <c r="E140" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F140" s="1" t="s">
+      <c r="F140" s="4" t="s">
         <v>792</v>
       </c>
-      <c r="G140" s="1" t="s">
+      <c r="G140" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="H140" s="1"/>
-      <c r="I140" s="1"/>
-      <c r="J140" s="1" t="s">
+      <c r="H140" s="4"/>
+      <c r="I140" s="4"/>
+      <c r="J140" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="K140" s="1" t="s">
+      <c r="K140" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="L140" s="1" t="s">
+      <c r="L140" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M140" s="1"/>
-      <c r="N140" s="1" t="s">
+      <c r="M140" s="4"/>
+      <c r="N140" s="4" t="s">
         <v>793</v>
       </c>
-      <c r="O140" s="1"/>
-      <c r="P140" s="1"/>
-      <c r="Q140" s="1"/>
-      <c r="R140" s="1"/>
-      <c r="S140" s="2" t="s">
+      <c r="O140" s="4"/>
+      <c r="P140" s="4"/>
+      <c r="Q140" s="4"/>
+      <c r="R140" s="4"/>
+      <c r="S140" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="T140" s="2" t="s">
+      <c r="T140" s="5" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="141" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A141" s="1" t="s">
+    <row r="141" spans="1:20" s="10" customFormat="1" ht="112" x14ac:dyDescent="0.2">
+      <c r="A141" s="8" t="s">
         <v>795</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B141" s="8" t="s">
         <v>796</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="C141" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="D141" s="8" t="s">
         <v>772</v>
       </c>
-      <c r="E141" s="1" t="s">
+      <c r="E141" s="8" t="s">
         <v>773</v>
       </c>
-      <c r="F141" s="1" t="s">
+      <c r="F141" s="8" t="s">
         <v>797</v>
       </c>
-      <c r="G141" s="1" t="s">
+      <c r="G141" s="8" t="s">
         <v>798</v>
       </c>
-      <c r="H141" s="1"/>
-      <c r="I141" s="1"/>
-      <c r="J141" s="1" t="s">
+      <c r="H141" s="8"/>
+      <c r="I141" s="8"/>
+      <c r="J141" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="K141" s="1" t="s">
+      <c r="K141" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="L141" s="1" t="s">
+      <c r="L141" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M141" s="1"/>
-      <c r="N141" s="1"/>
-      <c r="O141" s="1"/>
-      <c r="P141" s="1" t="s">
+      <c r="M141" s="8"/>
+      <c r="N141" s="8"/>
+      <c r="O141" s="8"/>
+      <c r="P141" s="8" t="s">
         <v>799</v>
       </c>
-      <c r="Q141" s="1"/>
-      <c r="R141" s="1" t="s">
+      <c r="Q141" s="8"/>
+      <c r="R141" s="8" t="s">
         <v>776</v>
       </c>
-      <c r="S141" s="2" t="s">
+      <c r="S141" s="9" t="s">
         <v>777</v>
       </c>
-      <c r="T141" s="1"/>
+      <c r="T141" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T141" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -14,9 +14,11 @@
   </bookViews>
   <sheets>
     <sheet name="Course inventory" sheetId="1" r:id="rId1"/>
+    <sheet name="Applied study" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Course inventory'!$A$1:$T$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Course inventory'!$A$1:$T$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Applied study'!$A$1:$T$37</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -6137,7 +6139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T141"/>
+  <dimension ref="A1:T105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -7481,33 +7483,33 @@
     </row>
     <row r="28" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>200</v>
+        <v>251</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>202</v>
+        <v>253</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4" t="s">
-        <v>205</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4" t="s">
-        <v>197</v>
+        <v>26</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>28</v>
@@ -7518,810 +7520,772 @@
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
       <c r="P28" s="4" t="s">
-        <v>206</v>
+        <v>255</v>
       </c>
       <c r="Q28" s="4"/>
       <c r="R28" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="S28" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="T28" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D29" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+    </row>
+    <row r="29" spans="1:20" ht="182" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J29" s="4" t="s">
+      <c r="E29" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="K29" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L29" s="4" t="s">
+      <c r="K29" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M29" s="4" t="s">
+      <c r="M29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="S29" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="T29" s="4"/>
-    </row>
-    <row r="30" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="182" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K30" s="4" t="s">
+      <c r="E30" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L30" s="4" t="s">
+      <c r="L30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M30" s="4" t="s">
+      <c r="M30" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="S30" s="4"/>
-      <c r="T30" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>221</v>
+        <v>271</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>222</v>
+        <v>272</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>202</v>
+        <v>22</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="G31" s="4"/>
+        <v>273</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>197</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="J31" s="4"/>
       <c r="K31" s="4" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>45</v>
       </c>
       <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
+      <c r="O31" s="4" t="s">
+        <v>276</v>
+      </c>
       <c r="P31" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q31" s="4"/>
+        <v>277</v>
+      </c>
+      <c r="Q31" s="4" t="s">
+        <v>278</v>
+      </c>
       <c r="R31" s="4" t="s">
-        <v>207</v>
+        <v>279</v>
       </c>
       <c r="S31" s="4"/>
-      <c r="T31" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T31" s="4"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>226</v>
+        <v>280</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>227</v>
+        <v>281</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>202</v>
+        <v>133</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4" t="s">
-        <v>219</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="J32" s="4"/>
       <c r="K32" s="4" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>28</v>
+        <v>283</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
+      <c r="O32" s="4" t="s">
+        <v>284</v>
+      </c>
       <c r="P32" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q32" s="4"/>
+        <v>285</v>
+      </c>
+      <c r="Q32" s="4" t="s">
+        <v>286</v>
+      </c>
       <c r="R32" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="S32" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="T32" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+      <c r="S32" s="4"/>
+      <c r="T32" s="4"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>232</v>
+        <v>287</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>233</v>
+        <v>288</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>202</v>
+        <v>22</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="G33" s="4"/>
+        <v>289</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="H33" s="4"/>
       <c r="I33" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>197</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="J33" s="4"/>
       <c r="K33" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>28</v>
+        <v>290</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>45</v>
       </c>
       <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
+      <c r="O33" s="4" t="s">
+        <v>284</v>
+      </c>
       <c r="P33" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q33" s="4"/>
+        <v>291</v>
+      </c>
+      <c r="Q33" s="4" t="s">
+        <v>286</v>
+      </c>
       <c r="R33" s="4" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
     </row>
-    <row r="34" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>236</v>
+        <v>293</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>237</v>
+        <v>294</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>202</v>
+        <v>295</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4" t="s">
-        <v>219</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="J34" s="4"/>
       <c r="K34" s="4" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="M34" s="4" t="s">
         <v>45</v>
       </c>
       <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
+      <c r="O34" s="4" t="s">
+        <v>284</v>
+      </c>
       <c r="P34" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q34" s="4"/>
+        <v>297</v>
+      </c>
+      <c r="Q34" s="4" t="s">
+        <v>286</v>
+      </c>
       <c r="R34" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="S34" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="T34" s="5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L35" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="S34" s="4"/>
+      <c r="T34" s="4"/>
+    </row>
+    <row r="35" spans="1:20" ht="266" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L35" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M35" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="S35" s="4"/>
-      <c r="T35" s="5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="M35" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>247</v>
+        <v>308</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>248</v>
+        <v>309</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>202</v>
+        <v>310</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4" t="s">
-        <v>205</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4" t="s">
         <v>197</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="L36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M36" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="M36" s="4"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
       <c r="P36" s="4" t="s">
-        <v>250</v>
+        <v>313</v>
       </c>
       <c r="Q36" s="4"/>
       <c r="R36" s="4" t="s">
-        <v>207</v>
+        <v>314</v>
       </c>
       <c r="S36" s="5" t="s">
-        <v>208</v>
+        <v>315</v>
       </c>
       <c r="T36" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>251</v>
+        <v>317</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>252</v>
+        <v>318</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>253</v>
+        <v>295</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>213</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="J37" s="4"/>
       <c r="K37" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>45</v>
+        <v>304</v>
       </c>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
       <c r="P37" s="4" t="s">
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="Q37" s="4"/>
       <c r="R37" s="4" t="s">
-        <v>256</v>
+        <v>117</v>
       </c>
       <c r="S37" s="4"/>
       <c r="T37" s="4"/>
     </row>
-    <row r="38" spans="1:20" ht="182" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="182" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="S39" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="T39" s="2" t="s">
-        <v>267</v>
-      </c>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="S38" s="4"/>
+      <c r="T38" s="4"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>271</v>
+        <v>333</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>272</v>
+        <v>334</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>22</v>
+        <v>295</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>274</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="G40" s="4"/>
       <c r="H40" s="4"/>
-      <c r="I40" s="4" t="s">
-        <v>275</v>
-      </c>
+      <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>44</v>
+        <v>336</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>45</v>
       </c>
       <c r="N40" s="4"/>
       <c r="O40" s="4" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q40" s="4" t="s">
-        <v>278</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="Q40" s="4"/>
       <c r="R40" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="S40" s="4"/>
+        <v>143</v>
+      </c>
+      <c r="S40" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="T40" s="4"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D41" s="4" t="s">
+    <row r="41" spans="1:20" ht="70" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L41" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="M41" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="P41" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q41" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="R41" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
+      <c r="F41" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S41" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="T41" s="2" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>287</v>
+        <v>346</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>288</v>
+        <v>347</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>22</v>
+        <v>167</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>274</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="G42" s="4"/>
       <c r="H42" s="4"/>
-      <c r="I42" s="4" t="s">
-        <v>275</v>
-      </c>
+      <c r="I42" s="4"/>
       <c r="J42" s="4"/>
       <c r="K42" s="4" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>290</v>
+        <v>28</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="N42" s="4"/>
-      <c r="O42" s="4" t="s">
-        <v>284</v>
-      </c>
+      <c r="O42" s="4"/>
       <c r="P42" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q42" s="4" t="s">
-        <v>286</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="Q42" s="4"/>
       <c r="R42" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="S42" s="4"/>
+        <v>350</v>
+      </c>
+      <c r="S42" s="5" t="s">
+        <v>351</v>
+      </c>
       <c r="T42" s="4"/>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>293</v>
+        <v>352</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>294</v>
+        <v>353</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>295</v>
+        <v>167</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>128</v>
+        <v>354</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>274</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="G43" s="4"/>
       <c r="H43" s="4"/>
-      <c r="I43" s="4" t="s">
-        <v>275</v>
-      </c>
+      <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="N43" s="4"/>
-      <c r="O43" s="4" t="s">
-        <v>284</v>
-      </c>
+      <c r="O43" s="4"/>
       <c r="P43" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q43" s="4" t="s">
-        <v>286</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="Q43" s="4"/>
       <c r="R43" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="S43" s="4"/>
+        <v>357</v>
+      </c>
+      <c r="S43" s="5" t="s">
+        <v>358</v>
+      </c>
       <c r="T43" s="4"/>
     </row>
-    <row r="44" spans="1:20" ht="266" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:20" ht="126" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>67</v>
+        <v>167</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>301</v>
+        <v>361</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>302</v>
+        <v>362</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>303</v>
+        <v>363</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -8333,325 +8297,345 @@
         <v>28</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>304</v>
+        <v>96</v>
       </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
-      <c r="P44" s="1" t="s">
-        <v>305</v>
+      <c r="P44" s="6" t="s">
+        <v>364</v>
       </c>
       <c r="Q44" s="1"/>
       <c r="R44" s="1" t="s">
-        <v>117</v>
+        <v>365</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="T44" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
+        <v>366</v>
+      </c>
+      <c r="T44" s="1"/>
+    </row>
+    <row r="45" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>308</v>
+        <v>367</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>309</v>
+        <v>368</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>310</v>
+        <v>369</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>312</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="G45" s="4"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4" t="s">
-        <v>197</v>
+        <v>372</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>27</v>
+        <v>373</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M45" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
       <c r="P45" s="4" t="s">
-        <v>313</v>
+        <v>374</v>
       </c>
       <c r="Q45" s="4"/>
       <c r="R45" s="4" t="s">
-        <v>314</v>
+        <v>170</v>
       </c>
       <c r="S45" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="T45" s="5" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
+        <v>375</v>
+      </c>
+      <c r="T45" s="4"/>
+    </row>
+    <row r="46" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>317</v>
+        <v>376</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>318</v>
+        <v>377</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>295</v>
+        <v>369</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>128</v>
+        <v>370</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>319</v>
+        <v>378</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
+      <c r="J46" s="4" t="s">
+        <v>219</v>
+      </c>
       <c r="K46" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>304</v>
+        <v>45</v>
       </c>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
       <c r="P46" s="4" t="s">
-        <v>320</v>
+        <v>379</v>
       </c>
       <c r="Q46" s="4"/>
       <c r="R46" s="4" t="s">
-        <v>117</v>
+        <v>380</v>
       </c>
       <c r="S46" s="4"/>
-      <c r="T46" s="4"/>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T46" s="5" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>321</v>
+        <v>382</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>322</v>
+        <v>383</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>295</v>
+        <v>369</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>128</v>
+        <v>370</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="G47" s="4"/>
+        <v>384</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>262</v>
+      </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
+      <c r="J47" s="4" t="s">
+        <v>219</v>
+      </c>
       <c r="K47" s="4" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>324</v>
+        <v>45</v>
       </c>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
       <c r="P47" s="4" t="s">
-        <v>325</v>
+        <v>385</v>
       </c>
       <c r="Q47" s="4"/>
       <c r="R47" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="S47" s="4"/>
-      <c r="T47" s="4"/>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
+        <v>380</v>
+      </c>
+      <c r="S47" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="T47" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>326</v>
+        <v>388</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>327</v>
+        <v>389</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>295</v>
+        <v>369</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>128</v>
+        <v>370</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="G48" s="4"/>
+        <v>390</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>262</v>
+      </c>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4" t="s">
-        <v>329</v>
+        <v>219</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="M48" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
       <c r="P48" s="4" t="s">
-        <v>331</v>
+        <v>391</v>
       </c>
       <c r="Q48" s="4"/>
       <c r="R48" s="4" t="s">
-        <v>332</v>
+        <v>392</v>
       </c>
       <c r="S48" s="4"/>
-      <c r="T48" s="4"/>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T48" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>333</v>
+        <v>394</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>334</v>
+        <v>395</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>295</v>
+        <v>396</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>335</v>
+        <v>397</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
+      <c r="J49" s="4" t="s">
+        <v>372</v>
+      </c>
       <c r="K49" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="M49" s="4" t="s">
         <v>45</v>
       </c>
       <c r="N49" s="4"/>
-      <c r="O49" s="4" t="s">
-        <v>337</v>
-      </c>
+      <c r="O49" s="4"/>
       <c r="P49" s="4" t="s">
-        <v>338</v>
+        <v>398</v>
       </c>
       <c r="Q49" s="4"/>
       <c r="R49" s="4" t="s">
-        <v>143</v>
+        <v>256</v>
       </c>
       <c r="S49" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T49" s="4"/>
-    </row>
-    <row r="50" spans="1:20" ht="70" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="M50" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="T49" s="5" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M50" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
-      <c r="R50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S50" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="T50" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="S50" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="T50" s="4"/>
+    </row>
+    <row r="51" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>346</v>
+        <v>406</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>347</v>
+        <v>407</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>167</v>
+        <v>396</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>348</v>
+        <v>408</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
+      <c r="J51" s="4" t="s">
+        <v>409</v>
+      </c>
       <c r="K51" s="4" t="s">
         <v>138</v>
       </c>
@@ -8659,134 +8643,142 @@
         <v>28</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
       <c r="P51" s="4" t="s">
-        <v>349</v>
+        <v>410</v>
       </c>
       <c r="Q51" s="4"/>
       <c r="R51" s="4" t="s">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="S51" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="T51" s="4"/>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+      <c r="T51" s="5" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>352</v>
+        <v>413</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>353</v>
+        <v>414</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>167</v>
+        <v>396</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>354</v>
+        <v>77</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>355</v>
+        <v>415</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
+      <c r="J52" s="4" t="s">
+        <v>197</v>
+      </c>
       <c r="K52" s="4" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="L52" s="4" t="s">
         <v>28</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
       <c r="P52" s="4" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="Q52" s="4"/>
       <c r="R52" s="4" t="s">
-        <v>357</v>
+        <v>417</v>
       </c>
       <c r="S52" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="T52" s="4"/>
-    </row>
-    <row r="53" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L53" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="T52" s="5" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L53" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M53" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
-      <c r="P53" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="Q53" s="1"/>
-      <c r="R53" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="S53" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="T53" s="1"/>
+      <c r="M53" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S53" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="T53" s="5" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="54" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>367</v>
+        <v>426</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>368</v>
+        <v>427</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>370</v>
+        <v>77</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -8795,10 +8787,10 @@
         <v>372</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>373</v>
+        <v>27</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="M54" s="4" t="s">
         <v>45</v>
@@ -8806,41 +8798,43 @@
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
       <c r="P54" s="4" t="s">
-        <v>374</v>
+        <v>429</v>
       </c>
       <c r="Q54" s="4"/>
       <c r="R54" s="4" t="s">
-        <v>170</v>
+        <v>314</v>
       </c>
       <c r="S54" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="T54" s="4"/>
+        <v>430</v>
+      </c>
+      <c r="T54" s="5" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="55" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>376</v>
+        <v>432</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>377</v>
+        <v>433</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>370</v>
+        <v>77</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>378</v>
+        <v>434</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>27</v>
@@ -8854,43 +8848,43 @@
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
       <c r="P55" s="4" t="s">
-        <v>379</v>
+        <v>435</v>
       </c>
       <c r="Q55" s="4"/>
       <c r="R55" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="S55" s="4"/>
+        <v>417</v>
+      </c>
+      <c r="S55" s="5" t="s">
+        <v>436</v>
+      </c>
       <c r="T55" s="5" t="s">
-        <v>381</v>
+        <v>437</v>
       </c>
     </row>
     <row r="56" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>382</v>
+        <v>438</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>383</v>
+        <v>439</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>370</v>
+        <v>77</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>262</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="G56" s="4"/>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4" t="s">
-        <v>219</v>
+        <v>409</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>138</v>
@@ -8904,48 +8898,46 @@
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
       <c r="P56" s="4" t="s">
-        <v>385</v>
+        <v>441</v>
       </c>
       <c r="Q56" s="4"/>
       <c r="R56" s="4" t="s">
-        <v>380</v>
+        <v>256</v>
       </c>
       <c r="S56" s="5" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="T56" s="5" t="s">
-        <v>387</v>
+        <v>442</v>
       </c>
     </row>
     <row r="57" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>388</v>
+        <v>443</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>389</v>
+        <v>444</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>370</v>
+        <v>77</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>262</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="L57" s="4" t="s">
         <v>28</v>
@@ -8956,23 +8948,25 @@
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
       <c r="P57" s="4" t="s">
-        <v>391</v>
+        <v>446</v>
       </c>
       <c r="Q57" s="4"/>
       <c r="R57" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="S57" s="4"/>
+        <v>447</v>
+      </c>
+      <c r="S57" s="5" t="s">
+        <v>448</v>
+      </c>
       <c r="T57" s="5" t="s">
-        <v>393</v>
+        <v>449</v>
       </c>
     </row>
     <row r="58" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>394</v>
+        <v>450</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>395</v>
+        <v>451</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>396</v>
@@ -8984,13 +8978,13 @@
         <v>77</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>397</v>
+        <v>452</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4" t="s">
-        <v>372</v>
+        <v>197</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>27</v>
@@ -9004,25 +8998,25 @@
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
       <c r="P58" s="4" t="s">
-        <v>398</v>
+        <v>453</v>
       </c>
       <c r="Q58" s="4"/>
       <c r="R58" s="4" t="s">
-        <v>256</v>
+        <v>447</v>
       </c>
       <c r="S58" s="5" t="s">
-        <v>375</v>
+        <v>448</v>
       </c>
       <c r="T58" s="5" t="s">
-        <v>399</v>
+        <v>454</v>
       </c>
     </row>
     <row r="59" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>400</v>
+        <v>455</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>401</v>
+        <v>456</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>396</v>
@@ -9034,45 +9028,43 @@
         <v>77</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>402</v>
+        <v>457</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
-      <c r="I59" s="4" t="s">
-        <v>403</v>
-      </c>
+      <c r="I59" s="4"/>
       <c r="J59" s="4" t="s">
-        <v>372</v>
+        <v>197</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>373</v>
+        <v>27</v>
       </c>
       <c r="L59" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M59" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="M59" s="4"/>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
       <c r="P59" s="4" t="s">
-        <v>404</v>
+        <v>458</v>
       </c>
       <c r="Q59" s="4"/>
       <c r="R59" s="4" t="s">
-        <v>170</v>
+        <v>459</v>
       </c>
       <c r="S59" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="T59" s="4"/>
+        <v>460</v>
+      </c>
+      <c r="T59" s="5" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="60" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>406</v>
+        <v>462</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>407</v>
+        <v>463</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>396</v>
@@ -9084,16 +9076,16 @@
         <v>77</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>408</v>
+        <v>464</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4" t="s">
-        <v>409</v>
+        <v>465</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="L60" s="4" t="s">
         <v>28</v>
@@ -9104,44 +9096,44 @@
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
       <c r="P60" s="4" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="Q60" s="4"/>
       <c r="R60" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="S60" s="5" t="s">
-        <v>411</v>
-      </c>
+      <c r="S60" s="4"/>
       <c r="T60" s="5" t="s">
-        <v>412</v>
+        <v>466</v>
       </c>
     </row>
     <row r="61" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>413</v>
+        <v>467</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>414</v>
+        <v>468</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>396</v>
+        <v>259</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>77</v>
+        <v>469</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
+        <v>470</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>471</v>
+      </c>
       <c r="I61" s="4"/>
-      <c r="J61" s="4" t="s">
-        <v>197</v>
-      </c>
+      <c r="J61" s="4"/>
       <c r="K61" s="4" t="s">
         <v>138</v>
       </c>
@@ -9149,149 +9141,135 @@
         <v>28</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
       <c r="P61" s="4" t="s">
-        <v>416</v>
+        <v>472</v>
       </c>
       <c r="Q61" s="4"/>
       <c r="R61" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="S61" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="T61" s="5" t="s">
-        <v>419</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
     </row>
     <row r="62" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>420</v>
+        <v>474</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>421</v>
+        <v>475</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>396</v>
+        <v>253</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>422</v>
+        <v>476</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
-      <c r="J62" s="4" t="s">
-        <v>219</v>
-      </c>
+      <c r="J62" s="4"/>
       <c r="K62" s="4" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="L62" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M62" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
       <c r="P62" s="4" t="s">
-        <v>423</v>
+        <v>477</v>
       </c>
       <c r="Q62" s="4"/>
       <c r="R62" s="4" t="s">
-        <v>314</v>
+        <v>478</v>
       </c>
       <c r="S62" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="T62" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="K63" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="T62" s="4"/>
+    </row>
+    <row r="63" spans="1:20" ht="293" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L63" s="4" t="s">
+      <c r="L63" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M63" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="S63" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="T63" s="5" t="s">
-        <v>431</v>
+      <c r="M63" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="Q63" s="1"/>
+      <c r="R63" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="S63" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="T63" s="2" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="64" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>432</v>
+        <v>485</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>433</v>
+        <v>486</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>396</v>
+        <v>253</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>77</v>
+        <v>487</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>434</v>
+        <v>488</v>
       </c>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-      <c r="J64" s="4" t="s">
-        <v>197</v>
-      </c>
+      <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
         <v>27</v>
       </c>
@@ -9299,99 +9277,89 @@
         <v>28</v>
       </c>
       <c r="M64" s="4" t="s">
-        <v>45</v>
+        <v>304</v>
       </c>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
       <c r="P64" s="4" t="s">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="Q64" s="4"/>
       <c r="R64" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="S64" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="T64" s="5" t="s">
-        <v>437</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="S64" s="4"/>
+      <c r="T64" s="4"/>
     </row>
     <row r="65" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>438</v>
+        <v>490</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>439</v>
+        <v>491</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>396</v>
+        <v>253</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>77</v>
+        <v>487</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>440</v>
+        <v>492</v>
       </c>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
-      <c r="J65" s="4" t="s">
-        <v>409</v>
-      </c>
+      <c r="J65" s="4"/>
       <c r="K65" s="4" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="L65" s="4" t="s">
         <v>28</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>45</v>
+        <v>304</v>
       </c>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
       <c r="P65" s="4" t="s">
-        <v>441</v>
+        <v>493</v>
       </c>
       <c r="Q65" s="4"/>
       <c r="R65" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="S65" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="T65" s="5" t="s">
-        <v>442</v>
-      </c>
+      <c r="S65" s="4"/>
+      <c r="T65" s="4"/>
     </row>
     <row r="66" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>443</v>
+        <v>494</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>444</v>
+        <v>495</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>396</v>
+        <v>253</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>77</v>
+        <v>301</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="G66" s="4"/>
+        <v>496</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
-      <c r="J66" s="4" t="s">
-        <v>197</v>
-      </c>
+      <c r="J66" s="4"/>
       <c r="K66" s="4" t="s">
         <v>27</v>
       </c>
@@ -9399,48 +9367,46 @@
         <v>28</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
       <c r="P66" s="4" t="s">
-        <v>446</v>
+        <v>498</v>
       </c>
       <c r="Q66" s="4"/>
       <c r="R66" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="S66" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="T66" s="5" t="s">
-        <v>449</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="S66" s="4"/>
+      <c r="T66" s="4"/>
     </row>
     <row r="67" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>450</v>
+        <v>499</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>451</v>
+        <v>500</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>396</v>
+        <v>167</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="G67" s="4"/>
+        <v>501</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>363</v>
+      </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4" t="s">
-        <v>197</v>
+        <v>409</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>27</v>
@@ -9449,97 +9415,95 @@
         <v>28</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
       <c r="P67" s="4" t="s">
-        <v>453</v>
+        <v>502</v>
       </c>
       <c r="Q67" s="4"/>
       <c r="R67" s="4" t="s">
-        <v>447</v>
+        <v>357</v>
       </c>
       <c r="S67" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="T67" s="5" t="s">
-        <v>454</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="T67" s="4"/>
     </row>
     <row r="68" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>456</v>
+        <v>504</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>396</v>
+        <v>167</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="G68" s="4"/>
+        <v>505</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>506</v>
+      </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
-      <c r="J68" s="4" t="s">
-        <v>197</v>
-      </c>
+      <c r="J68" s="4"/>
       <c r="K68" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L68" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M68" s="4"/>
+      <c r="M68" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
       <c r="P68" s="4" t="s">
-        <v>458</v>
+        <v>507</v>
       </c>
       <c r="Q68" s="4"/>
       <c r="R68" s="4" t="s">
-        <v>459</v>
+        <v>357</v>
       </c>
       <c r="S68" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="T68" s="5" t="s">
-        <v>461</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="T68" s="4"/>
     </row>
     <row r="69" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>462</v>
+        <v>508</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>463</v>
+        <v>509</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>396</v>
+        <v>167</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="G69" s="4"/>
+        <v>510</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>506</v>
+      </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
-      <c r="J69" s="4" t="s">
-        <v>465</v>
-      </c>
+      <c r="J69" s="4"/>
       <c r="K69" s="4" t="s">
         <v>27</v>
       </c>
@@ -9547,256 +9511,280 @@
         <v>28</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
       <c r="P69" s="4" t="s">
-        <v>379</v>
+        <v>511</v>
       </c>
       <c r="Q69" s="4"/>
       <c r="R69" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="S69" s="4"/>
-      <c r="T69" s="5" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L70" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="S69" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="T69" s="4"/>
+    </row>
+    <row r="70" spans="1:20" ht="126" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L70" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M70" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4"/>
-      <c r="P70" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="Q70" s="4"/>
-      <c r="R70" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="S70" s="4"/>
-      <c r="T70" s="4"/>
+      <c r="M70" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q70" s="1"/>
+      <c r="R70" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="S70" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="T70" s="1"/>
     </row>
     <row r="71" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>474</v>
+        <v>518</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>475</v>
+        <v>519</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>253</v>
+        <v>167</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>24</v>
+        <v>520</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>476</v>
+        <v>521</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
+      <c r="J71" s="4" t="s">
+        <v>409</v>
+      </c>
       <c r="K71" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L71" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M71" s="4"/>
+      <c r="M71" s="4" t="s">
+        <v>304</v>
+      </c>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
       <c r="P71" s="4" t="s">
-        <v>477</v>
+        <v>522</v>
       </c>
       <c r="Q71" s="4"/>
       <c r="R71" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="S71" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="S71" s="4"/>
+      <c r="T71" s="4"/>
+    </row>
+    <row r="72" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="S72" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="T71" s="4"/>
-    </row>
-    <row r="72" spans="1:20" ht="293" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L72" s="1" t="s">
+      <c r="T72" s="4"/>
+    </row>
+    <row r="73" spans="1:20" ht="182" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L73" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M72" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="N72" s="1"/>
-      <c r="O72" s="1"/>
-      <c r="P72" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="Q72" s="1"/>
-      <c r="R72" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="S72" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="T72" s="2" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L73" s="4" t="s">
+      <c r="M73" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N73" s="1"/>
+      <c r="O73" s="1"/>
+      <c r="P73" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q73" s="1"/>
+      <c r="R73" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="T73" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" ht="182" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L74" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M73" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="N73" s="4"/>
-      <c r="O73" s="4"/>
-      <c r="P73" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="S73" s="4"/>
-      <c r="T73" s="4"/>
-    </row>
-    <row r="74" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L74" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M74" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="N74" s="4"/>
-      <c r="O74" s="4"/>
-      <c r="P74" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="S74" s="4"/>
-      <c r="T74" s="4"/>
+      <c r="M74" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N74" s="1"/>
+      <c r="O74" s="1"/>
+      <c r="P74" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q74" s="1"/>
+      <c r="R74" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="T74" s="2" t="s">
+        <v>584</v>
+      </c>
     </row>
     <row r="75" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>494</v>
+        <v>586</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>495</v>
+        <v>587</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>253</v>
@@ -9805,16 +9793,16 @@
         <v>41</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>301</v>
+        <v>588</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>497</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="G75" s="4"/>
       <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
+      <c r="I75" s="4" t="s">
+        <v>590</v>
+      </c>
       <c r="J75" s="4"/>
       <c r="K75" s="4" t="s">
         <v>27</v>
@@ -9823,47 +9811,45 @@
         <v>28</v>
       </c>
       <c r="M75" s="4" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
       <c r="P75" s="4" t="s">
-        <v>498</v>
+        <v>591</v>
       </c>
       <c r="Q75" s="4"/>
       <c r="R75" s="4" t="s">
-        <v>256</v>
+        <v>49</v>
       </c>
       <c r="S75" s="4"/>
       <c r="T75" s="4"/>
     </row>
     <row r="76" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>499</v>
+        <v>592</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>500</v>
+        <v>593</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>167</v>
+        <v>253</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>61</v>
+        <v>588</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>363</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="G76" s="4"/>
       <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4" t="s">
-        <v>409</v>
-      </c>
+      <c r="I76" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="J76" s="4"/>
       <c r="K76" s="4" t="s">
         <v>27</v>
       </c>
@@ -9871,47 +9857,47 @@
         <v>28</v>
       </c>
       <c r="M76" s="4" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
       <c r="P76" s="4" t="s">
-        <v>502</v>
+        <v>595</v>
       </c>
       <c r="Q76" s="4"/>
       <c r="R76" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="S76" s="5" t="s">
-        <v>358</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="S76" s="4"/>
       <c r="T76" s="4"/>
     </row>
     <row r="77" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>503</v>
+        <v>596</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>504</v>
+        <v>597</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>167</v>
+        <v>598</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>41</v>
+        <v>599</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>505</v>
+        <v>600</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>506</v>
+        <v>601</v>
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
+      <c r="J77" s="4" t="s">
+        <v>602</v>
+      </c>
       <c r="K77" s="4" t="s">
         <v>27</v>
       </c>
@@ -9919,49 +9905,51 @@
         <v>28</v>
       </c>
       <c r="M77" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="N77" s="4"/>
+        <v>45</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>603</v>
+      </c>
       <c r="O77" s="4"/>
-      <c r="P77" s="4" t="s">
-        <v>507</v>
-      </c>
+      <c r="P77" s="4"/>
       <c r="Q77" s="4"/>
       <c r="R77" s="4" t="s">
-        <v>357</v>
+        <v>73</v>
       </c>
       <c r="S77" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="T77" s="4"/>
+        <v>604</v>
+      </c>
+      <c r="T77" s="5" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="78" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>508</v>
+        <v>605</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>509</v>
+        <v>606</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>61</v>
+        <v>607</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>510</v>
+        <v>608</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>506</v>
+        <v>262</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
       <c r="K78" s="4" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="L78" s="4" t="s">
         <v>28</v>
@@ -9969,455 +9957,417 @@
       <c r="M78" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="N78" s="4"/>
+      <c r="N78" s="4" t="s">
+        <v>609</v>
+      </c>
       <c r="O78" s="4"/>
       <c r="P78" s="4" t="s">
-        <v>511</v>
+        <v>610</v>
       </c>
       <c r="Q78" s="4"/>
       <c r="R78" s="4" t="s">
-        <v>357</v>
+        <v>611</v>
       </c>
       <c r="S78" s="5" t="s">
-        <v>358</v>
+        <v>612</v>
       </c>
       <c r="T78" s="4"/>
     </row>
-    <row r="79" spans="1:20" ht="126" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C79" s="1" t="s">
+    <row r="79" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D79" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1" t="s">
+      <c r="E79" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="K79" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L79" s="1" t="s">
+      <c r="K79" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L79" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M79" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="N79" s="1"/>
-      <c r="O79" s="1"/>
-      <c r="P79" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="Q79" s="1"/>
-      <c r="R79" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="S79" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="T79" s="1"/>
-    </row>
-    <row r="80" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="K80" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L80" s="4" t="s">
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="S79" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="T79" s="4"/>
+    </row>
+    <row r="80" spans="1:20" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="L80" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M80" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="N80" s="4"/>
-      <c r="O80" s="4"/>
-      <c r="P80" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q80" s="4"/>
-      <c r="R80" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="S80" s="4"/>
-      <c r="T80" s="4"/>
+      <c r="M80" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="O80" s="1"/>
+      <c r="P80" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q80" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="R80" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="T80" s="1"/>
     </row>
     <row r="81" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>523</v>
+        <v>629</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>524</v>
+        <v>630</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>167</v>
+        <v>631</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>525</v>
+        <v>632</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>312</v>
+        <v>633</v>
       </c>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
       <c r="J81" s="4" t="s">
-        <v>197</v>
+        <v>409</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>290</v>
+        <v>28</v>
       </c>
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
       <c r="P81" s="4" t="s">
-        <v>526</v>
+        <v>634</v>
       </c>
       <c r="Q81" s="4"/>
       <c r="R81" s="4" t="s">
-        <v>527</v>
+        <v>635</v>
       </c>
       <c r="S81" s="5" t="s">
-        <v>31</v>
+        <v>636</v>
       </c>
       <c r="T81" s="4"/>
     </row>
     <row r="82" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>528</v>
+        <v>637</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>201</v>
+        <v>638</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>529</v>
+        <v>631</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>530</v>
+        <v>68</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>531</v>
+        <v>361</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>205</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
       <c r="I82" s="4"/>
-      <c r="J82" s="4" t="s">
-        <v>219</v>
-      </c>
+      <c r="J82" s="4"/>
       <c r="K82" s="4" t="s">
         <v>138</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>28</v>
+        <v>640</v>
       </c>
       <c r="M82" s="4" t="s">
-        <v>45</v>
+        <v>304</v>
       </c>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
       <c r="P82" s="4" t="s">
-        <v>534</v>
+        <v>641</v>
       </c>
       <c r="Q82" s="4"/>
       <c r="R82" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="S82" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="T82" s="5" t="s">
-        <v>536</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="S82" s="4"/>
+      <c r="T82" s="4"/>
     </row>
     <row r="83" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>537</v>
+        <v>643</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>538</v>
+        <v>644</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>529</v>
+        <v>631</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>530</v>
+        <v>68</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>531</v>
+        <v>361</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>205</v>
-      </c>
+        <v>645</v>
+      </c>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
       <c r="I83" s="4"/>
-      <c r="J83" s="4" t="s">
-        <v>219</v>
-      </c>
+      <c r="J83" s="4"/>
       <c r="K83" s="4" t="s">
         <v>138</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>28</v>
+        <v>640</v>
       </c>
       <c r="M83" s="4" t="s">
-        <v>45</v>
+        <v>304</v>
       </c>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
       <c r="P83" s="4" t="s">
-        <v>540</v>
+        <v>646</v>
       </c>
       <c r="Q83" s="4"/>
       <c r="R83" s="4" t="s">
-        <v>314</v>
+        <v>642</v>
       </c>
       <c r="S83" s="4"/>
-      <c r="T83" s="5" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>543</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K84" s="4" t="s">
+      <c r="T83" s="4"/>
+    </row>
+    <row r="84" spans="1:20" ht="182" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L84" s="4" t="s">
+      <c r="L84" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M84" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N84" s="4"/>
-      <c r="O84" s="4"/>
-      <c r="P84" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="Q84" s="4"/>
-      <c r="R84" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="S84" s="4"/>
-      <c r="T84" s="5" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K85" s="4" t="s">
+      <c r="M84" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="N84" s="1"/>
+      <c r="O84" s="1"/>
+      <c r="P84" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="Q84" s="1"/>
+      <c r="R84" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="S84" s="1"/>
+      <c r="T84" s="1"/>
+    </row>
+    <row r="85" spans="1:20" ht="210" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L85" s="4" t="s">
+      <c r="L85" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M85" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N85" s="4"/>
-      <c r="O85" s="4"/>
-      <c r="P85" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="Q85" s="4"/>
-      <c r="R85" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="S85" s="4"/>
-      <c r="T85" s="5" t="s">
-        <v>541</v>
-      </c>
+      <c r="M85" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="N85" s="1"/>
+      <c r="O85" s="1"/>
+      <c r="P85" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="Q85" s="1"/>
+      <c r="R85" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="S85" s="1"/>
+      <c r="T85" s="1"/>
     </row>
     <row r="86" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>547</v>
+        <v>654</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>548</v>
+        <v>655</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>529</v>
+        <v>631</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>530</v>
+        <v>68</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>531</v>
+        <v>361</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>205</v>
-      </c>
+        <v>656</v>
+      </c>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
       <c r="I86" s="4"/>
-      <c r="J86" s="4" t="s">
-        <v>219</v>
-      </c>
+      <c r="J86" s="4"/>
       <c r="K86" s="4" t="s">
         <v>138</v>
       </c>
       <c r="L86" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M86" s="4"/>
+      <c r="M86" s="4" t="s">
+        <v>324</v>
+      </c>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
       <c r="P86" s="4" t="s">
-        <v>550</v>
+        <v>657</v>
       </c>
       <c r="Q86" s="4"/>
       <c r="R86" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="S86" s="5" t="s">
-        <v>551</v>
-      </c>
-      <c r="T86" s="5" t="s">
-        <v>541</v>
-      </c>
+        <v>642</v>
+      </c>
+      <c r="S86" s="4"/>
+      <c r="T86" s="4"/>
     </row>
     <row r="87" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>552</v>
+        <v>658</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>237</v>
+        <v>659</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>529</v>
+        <v>631</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>530</v>
+        <v>68</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>531</v>
+        <v>660</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>205</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
       <c r="I87" s="4"/>
-      <c r="J87" s="4" t="s">
-        <v>219</v>
-      </c>
+      <c r="J87" s="4"/>
       <c r="K87" s="4" t="s">
         <v>138</v>
       </c>
@@ -10425,51 +10375,43 @@
         <v>28</v>
       </c>
       <c r="M87" s="4" t="s">
-        <v>45</v>
+        <v>304</v>
       </c>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
       <c r="P87" s="4" t="s">
-        <v>554</v>
+        <v>662</v>
       </c>
       <c r="Q87" s="4"/>
       <c r="R87" s="4" t="s">
-        <v>314</v>
+        <v>642</v>
       </c>
       <c r="S87" s="4"/>
-      <c r="T87" s="5" t="s">
-        <v>541</v>
-      </c>
+      <c r="T87" s="4"/>
     </row>
     <row r="88" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>555</v>
+        <v>663</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>556</v>
+        <v>664</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>529</v>
+        <v>631</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>530</v>
+        <v>41</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>531</v>
+        <v>61</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>205</v>
-      </c>
+        <v>665</v>
+      </c>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
       <c r="I88" s="4"/>
-      <c r="J88" s="4" t="s">
-        <v>219</v>
-      </c>
+      <c r="J88" s="4"/>
       <c r="K88" s="4" t="s">
         <v>138</v>
       </c>
@@ -10477,102 +10419,92 @@
         <v>28</v>
       </c>
       <c r="M88" s="4" t="s">
-        <v>45</v>
+        <v>324</v>
       </c>
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
       <c r="P88" s="4" t="s">
-        <v>546</v>
+        <v>666</v>
       </c>
       <c r="Q88" s="4"/>
       <c r="R88" s="4" t="s">
-        <v>314</v>
+        <v>667</v>
       </c>
       <c r="S88" s="4"/>
-      <c r="T88" s="5" t="s">
-        <v>541</v>
-      </c>
+      <c r="T88" s="4"/>
     </row>
     <row r="89" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>557</v>
+        <v>668</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>243</v>
+        <v>669</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>529</v>
+        <v>631</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>530</v>
+        <v>41</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>531</v>
+        <v>24</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>539</v>
+        <v>670</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>205</v>
-      </c>
+        <v>671</v>
+      </c>
+      <c r="H89" s="4"/>
       <c r="I89" s="4"/>
-      <c r="J89" s="4" t="s">
-        <v>219</v>
-      </c>
+      <c r="J89" s="4"/>
       <c r="K89" s="4" t="s">
         <v>138</v>
       </c>
       <c r="L89" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M89" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="M89" s="4"/>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
       <c r="P89" s="4" t="s">
-        <v>546</v>
+        <v>672</v>
       </c>
       <c r="Q89" s="4"/>
       <c r="R89" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="S89" s="4"/>
-      <c r="T89" s="5" t="s">
-        <v>541</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="S89" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="T89" s="4"/>
     </row>
     <row r="90" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
-        <v>559</v>
+        <v>675</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>560</v>
+        <v>676</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>529</v>
+        <v>631</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>530</v>
+        <v>68</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>531</v>
+        <v>660</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>539</v>
+        <v>677</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>205</v>
-      </c>
+        <v>678</v>
+      </c>
+      <c r="H90" s="4"/>
       <c r="I90" s="4"/>
       <c r="J90" s="4" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>138</v>
@@ -10580,2487 +10512,2651 @@
       <c r="L90" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M90" s="4"/>
+      <c r="M90" s="4" t="s">
+        <v>304</v>
+      </c>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
       <c r="P90" s="4" t="s">
-        <v>561</v>
+        <v>679</v>
       </c>
       <c r="Q90" s="4"/>
       <c r="R90" s="4" t="s">
-        <v>314</v>
+        <v>642</v>
       </c>
       <c r="S90" s="4"/>
-      <c r="T90" s="5" t="s">
-        <v>562</v>
-      </c>
+      <c r="T90" s="4"/>
     </row>
     <row r="91" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
-        <v>563</v>
+        <v>680</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>248</v>
+        <v>681</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>529</v>
+        <v>631</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>530</v>
+        <v>68</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>531</v>
+        <v>361</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>539</v>
+        <v>682</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>205</v>
-      </c>
+        <v>671</v>
+      </c>
+      <c r="H91" s="4"/>
       <c r="I91" s="4"/>
-      <c r="J91" s="4" t="s">
-        <v>219</v>
-      </c>
+      <c r="J91" s="4"/>
       <c r="K91" s="4" t="s">
         <v>138</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>28</v>
+        <v>683</v>
       </c>
       <c r="M91" s="4" t="s">
-        <v>45</v>
+        <v>324</v>
       </c>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
       <c r="P91" s="4" t="s">
-        <v>546</v>
+        <v>684</v>
       </c>
       <c r="Q91" s="4"/>
       <c r="R91" s="4" t="s">
-        <v>314</v>
+        <v>642</v>
       </c>
       <c r="S91" s="4"/>
-      <c r="T91" s="5" t="s">
-        <v>541</v>
-      </c>
+      <c r="T91" s="4"/>
     </row>
     <row r="92" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>565</v>
+        <v>685</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>566</v>
+        <v>686</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>529</v>
+        <v>631</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>530</v>
+        <v>41</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>531</v>
+        <v>24</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>539</v>
+        <v>687</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="I92" s="4"/>
-      <c r="J92" s="4" t="s">
-        <v>219</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="J92" s="4"/>
       <c r="K92" s="4" t="s">
         <v>138</v>
       </c>
       <c r="L92" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M92" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="M92" s="4"/>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
       <c r="P92" s="4" t="s">
-        <v>546</v>
+        <v>689</v>
       </c>
       <c r="Q92" s="4"/>
       <c r="R92" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="S92" s="4"/>
-      <c r="T92" s="5" t="s">
-        <v>541</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="S92" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="T92" s="4"/>
     </row>
     <row r="93" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>567</v>
+        <v>690</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>568</v>
+        <v>691</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>529</v>
+        <v>631</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>530</v>
+        <v>41</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>531</v>
+        <v>24</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>539</v>
+        <v>692</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>205</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="H93" s="4"/>
       <c r="I93" s="4"/>
-      <c r="J93" s="4" t="s">
-        <v>219</v>
-      </c>
+      <c r="J93" s="4"/>
       <c r="K93" s="4" t="s">
         <v>138</v>
       </c>
       <c r="L93" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M93" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="M93" s="4"/>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
       <c r="P93" s="4" t="s">
-        <v>570</v>
+        <v>693</v>
       </c>
       <c r="Q93" s="4"/>
       <c r="R93" s="4" t="s">
-        <v>314</v>
+        <v>30</v>
       </c>
       <c r="S93" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="T93" s="5" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="D94" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="T93" s="4"/>
+    </row>
+    <row r="94" spans="1:20" ht="196" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="E94" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4" t="s">
+      <c r="E94" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K94" s="4" t="s">
+      <c r="K94" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L94" s="4" t="s">
+      <c r="L94" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M94" s="4" t="s">
+      <c r="M94" s="1"/>
+      <c r="N94" s="1"/>
+      <c r="O94" s="1"/>
+      <c r="P94" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="Q94" s="1"/>
+      <c r="R94" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="S94" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="T94" s="1"/>
+    </row>
+    <row r="95" spans="1:20" ht="140" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M95" s="1"/>
+      <c r="N95" s="1"/>
+      <c r="O95" s="1"/>
+      <c r="P95" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q95" s="1"/>
+      <c r="R95" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="S95" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="T95" s="1"/>
+    </row>
+    <row r="96" spans="1:20" s="13" customFormat="1" ht="70" x14ac:dyDescent="0.2">
+      <c r="A96" s="11" t="s">
+        <v>739</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>740</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E96" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F96" s="11" t="s">
+        <v>741</v>
+      </c>
+      <c r="G96" s="11"/>
+      <c r="H96" s="11"/>
+      <c r="I96" s="11" t="s">
+        <v>742</v>
+      </c>
+      <c r="J96" s="11" t="s">
+        <v>743</v>
+      </c>
+      <c r="K96" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="L96" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M96" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="N96" s="11"/>
+      <c r="O96" s="11"/>
+      <c r="P96" s="11"/>
+      <c r="Q96" s="11"/>
+      <c r="R96" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="S96" s="12" t="s">
+        <v>744</v>
+      </c>
+      <c r="T96" s="12" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" s="13" customFormat="1" ht="140" x14ac:dyDescent="0.2">
+      <c r="A97" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E97" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F97" s="11" t="s">
+        <v>747</v>
+      </c>
+      <c r="G97" s="11"/>
+      <c r="H97" s="11"/>
+      <c r="I97" s="11" t="s">
+        <v>748</v>
+      </c>
+      <c r="J97" s="11" t="s">
+        <v>743</v>
+      </c>
+      <c r="K97" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="L97" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M97" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="N97" s="11"/>
+      <c r="O97" s="11"/>
+      <c r="P97" s="11" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q97" s="11"/>
+      <c r="R97" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="S97" s="12" t="s">
+        <v>751</v>
+      </c>
+      <c r="T97" s="11"/>
+    </row>
+    <row r="98" spans="1:20" s="13" customFormat="1" ht="70" x14ac:dyDescent="0.2">
+      <c r="A98" s="11" t="s">
+        <v>752</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>753</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E98" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F98" s="11" t="s">
+        <v>754</v>
+      </c>
+      <c r="G98" s="11"/>
+      <c r="H98" s="11"/>
+      <c r="I98" s="11" t="s">
+        <v>755</v>
+      </c>
+      <c r="J98" s="11" t="s">
+        <v>743</v>
+      </c>
+      <c r="K98" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="L98" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M98" s="11" t="s">
+        <v>749</v>
+      </c>
+      <c r="N98" s="11"/>
+      <c r="O98" s="11"/>
+      <c r="P98" s="11"/>
+      <c r="Q98" s="11"/>
+      <c r="R98" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="S98" s="12" t="s">
+        <v>744</v>
+      </c>
+      <c r="T98" s="12" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" ht="112" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M99" s="1"/>
+      <c r="N99" s="1"/>
+      <c r="O99" s="1"/>
+      <c r="P99" s="1"/>
+      <c r="Q99" s="1"/>
+      <c r="R99" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="S99" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="T99" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" s="10" customFormat="1" ht="112" x14ac:dyDescent="0.2">
+      <c r="A100" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="8" t="s">
+        <v>766</v>
+      </c>
+      <c r="K100" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="L100" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="M100" s="8"/>
+      <c r="N100" s="8"/>
+      <c r="O100" s="8"/>
+      <c r="P100" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="Q100" s="8"/>
+      <c r="R100" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="S100" s="9" t="s">
+        <v>768</v>
+      </c>
+      <c r="T100" s="9" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" s="10" customFormat="1" ht="112" x14ac:dyDescent="0.2">
+      <c r="A101" s="8" t="s">
+        <v>770</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>771</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="H101" s="8"/>
+      <c r="I101" s="8"/>
+      <c r="J101" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="K101" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="L101" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="M101" s="8"/>
+      <c r="N101" s="8"/>
+      <c r="O101" s="8"/>
+      <c r="P101" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="Q101" s="8"/>
+      <c r="R101" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="S101" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="T101" s="8"/>
+    </row>
+    <row r="102" spans="1:20" ht="98" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M102" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N94" s="4"/>
-      <c r="O94" s="4"/>
-      <c r="P94" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="Q94" s="4"/>
-      <c r="R94" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="S94" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="T94" s="5" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K95" s="4" t="s">
+      <c r="N102" s="1"/>
+      <c r="O102" s="1"/>
+      <c r="P102" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="Q102" s="1"/>
+      <c r="R102" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="S102" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="T102" s="1"/>
+    </row>
+    <row r="103" spans="1:20" s="13" customFormat="1" ht="84" x14ac:dyDescent="0.2">
+      <c r="A103" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>786</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E103" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F103" s="11" t="s">
+        <v>787</v>
+      </c>
+      <c r="G103" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="H103" s="11"/>
+      <c r="I103" s="11"/>
+      <c r="J103" s="11" t="s">
+        <v>788</v>
+      </c>
+      <c r="K103" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="L95" s="4" t="s">
+      <c r="L103" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="M95" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N95" s="4"/>
-      <c r="O95" s="4"/>
-      <c r="P95" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="Q95" s="4"/>
-      <c r="R95" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="S95" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="T95" s="5" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20" ht="182" x14ac:dyDescent="0.2">
-      <c r="A96" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L96" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M96" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N96" s="1"/>
-      <c r="O96" s="1"/>
-      <c r="P96" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q96" s="1"/>
-      <c r="R96" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="S96" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="T96" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" ht="182" x14ac:dyDescent="0.2">
-      <c r="A97" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="I97" s="1"/>
-      <c r="J97" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L97" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M97" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N97" s="1"/>
-      <c r="O97" s="1"/>
-      <c r="P97" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q97" s="1"/>
-      <c r="R97" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="S97" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="T97" s="2" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="J98" s="4"/>
-      <c r="K98" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L98" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M98" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="N98" s="4"/>
-      <c r="O98" s="4"/>
-      <c r="P98" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="Q98" s="4"/>
-      <c r="R98" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="S98" s="4"/>
-      <c r="T98" s="4"/>
-    </row>
-    <row r="99" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L99" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M99" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="N99" s="4"/>
-      <c r="O99" s="4"/>
-      <c r="P99" s="4" t="s">
-        <v>595</v>
-      </c>
-      <c r="Q99" s="4"/>
-      <c r="R99" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="S99" s="4"/>
-      <c r="T99" s="4"/>
-    </row>
-    <row r="100" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="K100" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L100" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M100" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N100" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="O100" s="4"/>
-      <c r="P100" s="4"/>
-      <c r="Q100" s="4"/>
-      <c r="R100" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="S100" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="T100" s="5" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="H101" s="4"/>
-      <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
-      <c r="K101" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L101" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M101" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="N101" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="O101" s="4"/>
-      <c r="P101" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="Q101" s="4"/>
-      <c r="R101" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="S101" s="5" t="s">
-        <v>612</v>
-      </c>
-      <c r="T101" s="4"/>
-    </row>
-    <row r="102" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E102" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F102" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
-      <c r="I102" s="4"/>
-      <c r="J102" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="K102" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L102" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M102" s="4"/>
-      <c r="N102" s="4"/>
-      <c r="O102" s="4"/>
-      <c r="P102" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q102" s="4"/>
-      <c r="R102" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="S102" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="T102" s="4"/>
-    </row>
-    <row r="103" spans="1:20" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A103" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="J103" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="L103" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M103" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N103" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="O103" s="1"/>
-      <c r="P103" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q103" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="R103" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="S103" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="T103" s="1"/>
+      <c r="M103" s="11"/>
+      <c r="N103" s="11"/>
+      <c r="O103" s="11"/>
+      <c r="P103" s="11" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q103" s="11"/>
+      <c r="R103" s="11" t="s">
+        <v>760</v>
+      </c>
+      <c r="S103" s="12" t="s">
+        <v>790</v>
+      </c>
+      <c r="T103" s="11"/>
     </row>
     <row r="104" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>629</v>
+        <v>791</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>631</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>41</v>
+        <v>599</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>632</v>
+        <v>792</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>633</v>
+        <v>601</v>
       </c>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
       <c r="J104" s="4" t="s">
-        <v>409</v>
+        <v>623</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>138</v>
+        <v>624</v>
       </c>
       <c r="L104" s="4" t="s">
         <v>28</v>
       </c>
       <c r="M104" s="4"/>
-      <c r="N104" s="4"/>
+      <c r="N104" s="4" t="s">
+        <v>793</v>
+      </c>
       <c r="O104" s="4"/>
-      <c r="P104" s="4" t="s">
-        <v>634</v>
-      </c>
+      <c r="P104" s="4"/>
       <c r="Q104" s="4"/>
-      <c r="R104" s="4" t="s">
-        <v>635</v>
-      </c>
+      <c r="R104" s="4"/>
       <c r="S104" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="T104" s="4"/>
-    </row>
-    <row r="105" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>638</v>
-      </c>
-      <c r="C105" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="T104" s="5" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20" s="10" customFormat="1" ht="112" x14ac:dyDescent="0.2">
+      <c r="A105" s="8" t="s">
+        <v>795</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="C105" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="D105" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="G105" s="4"/>
-      <c r="H105" s="4"/>
-      <c r="I105" s="4"/>
-      <c r="J105" s="4"/>
-      <c r="K105" s="4" t="s">
+      <c r="D105" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="H105" s="8"/>
+      <c r="I105" s="8"/>
+      <c r="J105" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="K105" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="L105" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="M105" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="N105" s="4"/>
-      <c r="O105" s="4"/>
-      <c r="P105" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="Q105" s="4"/>
-      <c r="R105" s="4" t="s">
+      <c r="L105" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="M105" s="8"/>
+      <c r="N105" s="8"/>
+      <c r="O105" s="8"/>
+      <c r="P105" s="8" t="s">
+        <v>799</v>
+      </c>
+      <c r="Q105" s="8"/>
+      <c r="R105" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="S105" s="9" t="s">
+        <v>777</v>
+      </c>
+      <c r="T105" s="8"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:T105" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:T37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="46" customWidth="1"/>
+    <col min="7" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="16" max="16" width="52" customWidth="1"/>
+    <col min="17" max="17" width="38" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
+    <col min="19" max="19" width="58.5" customWidth="1"/>
+    <col min="20" max="20" width="64" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="T3" s="4"/>
+    </row>
+    <row r="4" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="S4" s="4"/>
+      <c r="T4" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="S5" s="4"/>
+      <c r="T5" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="S6" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="T6" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+    </row>
+    <row r="8" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="S9" s="4"/>
+      <c r="T9" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="T11" s="5" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S12" s="4"/>
+      <c r="T12" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S13" s="4"/>
+      <c r="T13" s="5" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S14" s="4"/>
+      <c r="T14" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S15" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="T15" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S16" s="4"/>
+      <c r="T16" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S17" s="4"/>
+      <c r="T17" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S18" s="4"/>
+      <c r="T18" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S19" s="4"/>
+      <c r="T19" s="5" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S20" s="4"/>
+      <c r="T20" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S21" s="4"/>
+      <c r="T21" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S22" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="T22" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S23" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="T23" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="S24" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="T24" s="5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S105" s="4"/>
-      <c r="T105" s="4"/>
-    </row>
-    <row r="106" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="4" t="s">
-        <v>643</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>644</v>
-      </c>
-      <c r="C106" s="4" t="s">
+      <c r="S25" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="T25" s="4"/>
+    </row>
+    <row r="26" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D106" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
-      <c r="K106" s="4" t="s">
+      <c r="D26" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K26" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L106" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="M106" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="N106" s="4"/>
-      <c r="O106" s="4"/>
-      <c r="P106" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="Q106" s="4"/>
-      <c r="R106" s="4" t="s">
+      <c r="L26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S106" s="4"/>
-      <c r="T106" s="4"/>
-    </row>
-    <row r="107" spans="1:20" ht="182" x14ac:dyDescent="0.2">
-      <c r="A107" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C107" s="1" t="s">
+      <c r="S26" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="T26" s="4"/>
+    </row>
+    <row r="27" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1"/>
-      <c r="K107" s="1" t="s">
+      <c r="D27" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K27" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L107" s="1" t="s">
+      <c r="L27" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M107" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="N107" s="1"/>
-      <c r="O107" s="1"/>
-      <c r="P107" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="Q107" s="1"/>
-      <c r="R107" s="1" t="s">
+      <c r="M27" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S107" s="1"/>
-      <c r="T107" s="1"/>
-    </row>
-    <row r="108" spans="1:20" ht="210" x14ac:dyDescent="0.2">
-      <c r="A108" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="C108" s="1" t="s">
+      <c r="S27" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="T27" s="5" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D108" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="G108" s="1"/>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
-      <c r="J108" s="1"/>
-      <c r="K108" s="1" t="s">
+      <c r="D28" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L108" s="1" t="s">
+      <c r="L28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M108" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="N108" s="1"/>
-      <c r="O108" s="1"/>
-      <c r="P108" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="Q108" s="1"/>
-      <c r="R108" s="1" t="s">
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S108" s="1"/>
-      <c r="T108" s="1"/>
-    </row>
-    <row r="109" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>655</v>
-      </c>
-      <c r="C109" s="4" t="s">
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+    </row>
+    <row r="29" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D109" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E109" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>656</v>
-      </c>
-      <c r="G109" s="4"/>
-      <c r="H109" s="4"/>
-      <c r="I109" s="4"/>
-      <c r="J109" s="4"/>
-      <c r="K109" s="4" t="s">
+      <c r="D29" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K29" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L109" s="4" t="s">
+      <c r="L29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M109" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="N109" s="4"/>
-      <c r="O109" s="4"/>
-      <c r="P109" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="Q109" s="4"/>
-      <c r="R109" s="4" t="s">
+      <c r="M29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S109" s="4"/>
-      <c r="T109" s="4"/>
-    </row>
-    <row r="110" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>659</v>
-      </c>
-      <c r="C110" s="4" t="s">
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+    </row>
+    <row r="30" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D110" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="G110" s="4"/>
-      <c r="H110" s="4"/>
-      <c r="I110" s="4"/>
-      <c r="J110" s="4"/>
-      <c r="K110" s="4" t="s">
+      <c r="D30" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K30" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L110" s="4" t="s">
+      <c r="L30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M110" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="N110" s="4"/>
-      <c r="O110" s="4"/>
-      <c r="P110" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="Q110" s="4"/>
-      <c r="R110" s="4" t="s">
+      <c r="M30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S110" s="4"/>
-      <c r="T110" s="4"/>
-    </row>
-    <row r="111" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="4" t="s">
-        <v>663</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>664</v>
-      </c>
-      <c r="C111" s="4" t="s">
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+    </row>
+    <row r="31" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D111" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E111" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="G111" s="4"/>
-      <c r="H111" s="4"/>
-      <c r="I111" s="4"/>
-      <c r="J111" s="4"/>
-      <c r="K111" s="4" t="s">
+      <c r="D31" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K31" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L111" s="4" t="s">
+      <c r="L31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M111" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="N111" s="4"/>
-      <c r="O111" s="4"/>
-      <c r="P111" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="Q111" s="4"/>
-      <c r="R111" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="S111" s="4"/>
-      <c r="T111" s="4"/>
-    </row>
-    <row r="112" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>669</v>
-      </c>
-      <c r="C112" s="4" t="s">
+      <c r="M31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="S31" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="T31" s="4"/>
+    </row>
+    <row r="32" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D112" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="H112" s="4"/>
-      <c r="I112" s="4"/>
-      <c r="J112" s="4"/>
-      <c r="K112" s="4" t="s">
+      <c r="D32" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K32" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L112" s="4" t="s">
+      <c r="L32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M112" s="4"/>
-      <c r="N112" s="4"/>
-      <c r="O112" s="4"/>
-      <c r="P112" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q112" s="4"/>
-      <c r="R112" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="S112" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="T112" s="4"/>
-    </row>
-    <row r="113" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>676</v>
-      </c>
-      <c r="C113" s="4" t="s">
+      <c r="M32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="S32" s="4"/>
+      <c r="T32" s="4"/>
+    </row>
+    <row r="33" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D113" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E113" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="F113" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="H113" s="4"/>
-      <c r="I113" s="4"/>
-      <c r="J113" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="K113" s="4" t="s">
+      <c r="D33" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K33" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L113" s="4" t="s">
+      <c r="L33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M113" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="N113" s="4"/>
-      <c r="O113" s="4"/>
-      <c r="P113" s="4" t="s">
-        <v>679</v>
-      </c>
-      <c r="Q113" s="4"/>
-      <c r="R113" s="4" t="s">
+      <c r="M33" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S113" s="4"/>
-      <c r="T113" s="4"/>
-    </row>
-    <row r="114" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="4" t="s">
-        <v>680</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="C114" s="4" t="s">
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
+    </row>
+    <row r="34" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D114" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="H114" s="4"/>
-      <c r="I114" s="4"/>
-      <c r="J114" s="4"/>
-      <c r="K114" s="4" t="s">
+      <c r="D34" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K34" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L114" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="M114" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="N114" s="4"/>
-      <c r="O114" s="4"/>
-      <c r="P114" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="Q114" s="4"/>
-      <c r="R114" s="4" t="s">
+      <c r="L34" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S114" s="4"/>
-      <c r="T114" s="4"/>
-    </row>
-    <row r="115" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="C115" s="4" t="s">
+      <c r="S34" s="4"/>
+      <c r="T34" s="4"/>
+    </row>
+    <row r="35" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D115" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E115" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="G115" s="4" t="s">
+      <c r="D35" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="H115" s="4"/>
-      <c r="I115" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="J115" s="4"/>
-      <c r="K115" s="4" t="s">
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K35" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L115" s="4" t="s">
+      <c r="L35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M115" s="4"/>
-      <c r="N115" s="4"/>
-      <c r="O115" s="4"/>
-      <c r="P115" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="Q115" s="4"/>
-      <c r="R115" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="S115" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T115" s="4"/>
-    </row>
-    <row r="116" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="C116" s="4" t="s">
+      <c r="M35" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="S35" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="T35" s="4"/>
+    </row>
+    <row r="36" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D116" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E116" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="H116" s="4"/>
-      <c r="I116" s="4"/>
-      <c r="J116" s="4"/>
-      <c r="K116" s="4" t="s">
+      <c r="D36" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="K36" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L116" s="4" t="s">
+      <c r="L36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M116" s="4"/>
-      <c r="N116" s="4"/>
-      <c r="O116" s="4"/>
-      <c r="P116" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="Q116" s="4"/>
-      <c r="R116" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="S116" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T116" s="4"/>
-    </row>
-    <row r="117" spans="1:20" ht="196" x14ac:dyDescent="0.2">
-      <c r="A117" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="C117" s="1" t="s">
+      <c r="M36" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="S36" s="4"/>
+      <c r="T36" s="4"/>
+    </row>
+    <row r="37" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="D37" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E37" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F117" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="I117" s="1"/>
-      <c r="J117" s="1" t="s">
+      <c r="F37" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K117" s="1" t="s">
+      <c r="K37" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L117" s="1" t="s">
+      <c r="L37" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="M117" s="1"/>
-      <c r="N117" s="1"/>
-      <c r="O117" s="1"/>
-      <c r="P117" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="Q117" s="1"/>
-      <c r="R117" s="1" t="s">
+      <c r="M37" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="S117" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="T117" s="1"/>
-    </row>
-    <row r="118" spans="1:20" ht="140" x14ac:dyDescent="0.2">
-      <c r="A118" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="I118" s="1"/>
-      <c r="J118" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="K118" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L118" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M118" s="1"/>
-      <c r="N118" s="1"/>
-      <c r="O118" s="1"/>
-      <c r="P118" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="Q118" s="1"/>
-      <c r="R118" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="S118" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="T118" s="1"/>
-    </row>
-    <row r="119" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="4" t="s">
-        <v>706</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>707</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E119" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="G119" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="H119" s="4"/>
-      <c r="I119" s="4"/>
-      <c r="J119" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K119" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L119" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M119" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N119" s="4"/>
-      <c r="O119" s="4"/>
-      <c r="P119" s="4" t="s">
-        <v>709</v>
-      </c>
-      <c r="Q119" s="4"/>
-      <c r="R119" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="S119" s="5" t="s">
-        <v>699</v>
-      </c>
-      <c r="T119" s="4"/>
-    </row>
-    <row r="120" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="4" t="s">
-        <v>710</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>711</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D120" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E120" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="G120" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="H120" s="4"/>
-      <c r="I120" s="4"/>
-      <c r="J120" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K120" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L120" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M120" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N120" s="4"/>
-      <c r="O120" s="4"/>
-      <c r="P120" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="Q120" s="4"/>
-      <c r="R120" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="S120" s="5" t="s">
-        <v>699</v>
-      </c>
-      <c r="T120" s="4"/>
-    </row>
-    <row r="121" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="4" t="s">
-        <v>713</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>714</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E121" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="G121" s="4"/>
-      <c r="H121" s="4"/>
-      <c r="I121" s="4"/>
-      <c r="J121" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K121" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L121" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M121" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N121" s="4"/>
-      <c r="O121" s="4"/>
-      <c r="P121" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="Q121" s="4"/>
-      <c r="R121" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="S121" s="5" t="s">
-        <v>716</v>
-      </c>
-      <c r="T121" s="5" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="122" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E122" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
-      <c r="I122" s="4"/>
-      <c r="J122" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K122" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L122" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M122" s="4"/>
-      <c r="N122" s="4"/>
-      <c r="O122" s="4"/>
-      <c r="P122" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="Q122" s="4"/>
-      <c r="R122" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="S122" s="4"/>
-      <c r="T122" s="4"/>
-    </row>
-    <row r="123" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="B123" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E123" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="G123" s="4"/>
-      <c r="H123" s="4"/>
-      <c r="I123" s="4"/>
-      <c r="J123" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K123" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L123" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M123" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N123" s="4"/>
-      <c r="O123" s="4"/>
-      <c r="P123" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="Q123" s="4"/>
-      <c r="R123" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="S123" s="4"/>
-      <c r="T123" s="4"/>
-    </row>
-    <row r="124" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>723</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F124" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="G124" s="4"/>
-      <c r="H124" s="4"/>
-      <c r="I124" s="4"/>
-      <c r="J124" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K124" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L124" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M124" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N124" s="4"/>
-      <c r="O124" s="4"/>
-      <c r="P124" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="Q124" s="4"/>
-      <c r="R124" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="S124" s="4"/>
-      <c r="T124" s="4"/>
-    </row>
-    <row r="125" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>725</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E125" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F125" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="G125" s="4"/>
-      <c r="H125" s="4"/>
-      <c r="I125" s="4"/>
-      <c r="J125" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K125" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L125" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M125" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N125" s="4"/>
-      <c r="O125" s="4"/>
-      <c r="P125" s="4" t="s">
-        <v>709</v>
-      </c>
-      <c r="Q125" s="4"/>
-      <c r="R125" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="S125" s="5" t="s">
-        <v>726</v>
-      </c>
-      <c r="T125" s="4"/>
-    </row>
-    <row r="126" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="4" t="s">
-        <v>727</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E126" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F126" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="G126" s="4"/>
-      <c r="H126" s="4"/>
-      <c r="I126" s="4"/>
-      <c r="J126" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K126" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L126" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M126" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N126" s="4"/>
-      <c r="O126" s="4"/>
-      <c r="P126" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="Q126" s="4"/>
-      <c r="R126" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="S126" s="4"/>
-      <c r="T126" s="4"/>
-    </row>
-    <row r="127" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="4" t="s">
-        <v>729</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>730</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E127" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="G127" s="4"/>
-      <c r="H127" s="4"/>
-      <c r="I127" s="4"/>
-      <c r="J127" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K127" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L127" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M127" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N127" s="4"/>
-      <c r="O127" s="4"/>
-      <c r="P127" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="Q127" s="4"/>
-      <c r="R127" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="S127" s="4"/>
-      <c r="T127" s="4"/>
-    </row>
-    <row r="128" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="4" t="s">
-        <v>731</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>732</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E128" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F128" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="G128" s="4"/>
-      <c r="H128" s="4"/>
-      <c r="I128" s="4"/>
-      <c r="J128" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K128" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L128" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M128" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N128" s="4"/>
-      <c r="O128" s="4"/>
-      <c r="P128" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="Q128" s="4"/>
-      <c r="R128" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="S128" s="4"/>
-      <c r="T128" s="4"/>
-    </row>
-    <row r="129" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>734</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F129" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="G129" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="H129" s="4"/>
-      <c r="I129" s="4"/>
-      <c r="J129" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K129" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L129" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M129" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N129" s="4"/>
-      <c r="O129" s="4"/>
-      <c r="P129" s="4" t="s">
-        <v>709</v>
-      </c>
-      <c r="Q129" s="4"/>
-      <c r="R129" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="S129" s="5" t="s">
-        <v>699</v>
-      </c>
-      <c r="T129" s="4"/>
-    </row>
-    <row r="130" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="4" t="s">
-        <v>735</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="G130" s="4"/>
-      <c r="H130" s="4"/>
-      <c r="I130" s="4"/>
-      <c r="J130" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K130" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L130" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M130" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N130" s="4"/>
-      <c r="O130" s="4"/>
-      <c r="P130" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="Q130" s="4"/>
-      <c r="R130" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="S130" s="4"/>
-      <c r="T130" s="4"/>
-    </row>
-    <row r="131" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D131" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="G131" s="4"/>
-      <c r="H131" s="4"/>
-      <c r="I131" s="4"/>
-      <c r="J131" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="K131" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="L131" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M131" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N131" s="4"/>
-      <c r="O131" s="4"/>
-      <c r="P131" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="Q131" s="4"/>
-      <c r="R131" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="S131" s="4"/>
-      <c r="T131" s="4"/>
-    </row>
-    <row r="132" spans="1:20" s="13" customFormat="1" ht="70" x14ac:dyDescent="0.2">
-      <c r="A132" s="11" t="s">
-        <v>739</v>
-      </c>
-      <c r="B132" s="11" t="s">
-        <v>740</v>
-      </c>
-      <c r="C132" s="11" t="s">
-        <v>631</v>
-      </c>
-      <c r="D132" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E132" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F132" s="11" t="s">
-        <v>741</v>
-      </c>
-      <c r="G132" s="11"/>
-      <c r="H132" s="11"/>
-      <c r="I132" s="11" t="s">
-        <v>742</v>
-      </c>
-      <c r="J132" s="11" t="s">
-        <v>743</v>
-      </c>
-      <c r="K132" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="L132" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="M132" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="N132" s="11"/>
-      <c r="O132" s="11"/>
-      <c r="P132" s="11"/>
-      <c r="Q132" s="11"/>
-      <c r="R132" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="S132" s="12" t="s">
-        <v>744</v>
-      </c>
-      <c r="T132" s="12" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="133" spans="1:20" s="13" customFormat="1" ht="140" x14ac:dyDescent="0.2">
-      <c r="A133" s="11" t="s">
-        <v>745</v>
-      </c>
-      <c r="B133" s="11" t="s">
-        <v>746</v>
-      </c>
-      <c r="C133" s="11" t="s">
-        <v>631</v>
-      </c>
-      <c r="D133" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E133" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F133" s="11" t="s">
-        <v>747</v>
-      </c>
-      <c r="G133" s="11"/>
-      <c r="H133" s="11"/>
-      <c r="I133" s="11" t="s">
-        <v>748</v>
-      </c>
-      <c r="J133" s="11" t="s">
-        <v>743</v>
-      </c>
-      <c r="K133" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="L133" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="M133" s="11" t="s">
-        <v>749</v>
-      </c>
-      <c r="N133" s="11"/>
-      <c r="O133" s="11"/>
-      <c r="P133" s="11" t="s">
-        <v>750</v>
-      </c>
-      <c r="Q133" s="11"/>
-      <c r="R133" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="S133" s="12" t="s">
-        <v>751</v>
-      </c>
-      <c r="T133" s="11"/>
-    </row>
-    <row r="134" spans="1:20" s="13" customFormat="1" ht="70" x14ac:dyDescent="0.2">
-      <c r="A134" s="11" t="s">
-        <v>752</v>
-      </c>
-      <c r="B134" s="11" t="s">
-        <v>753</v>
-      </c>
-      <c r="C134" s="11" t="s">
-        <v>631</v>
-      </c>
-      <c r="D134" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E134" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F134" s="11" t="s">
-        <v>754</v>
-      </c>
-      <c r="G134" s="11"/>
-      <c r="H134" s="11"/>
-      <c r="I134" s="11" t="s">
-        <v>755</v>
-      </c>
-      <c r="J134" s="11" t="s">
-        <v>743</v>
-      </c>
-      <c r="K134" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="L134" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="M134" s="11" t="s">
-        <v>749</v>
-      </c>
-      <c r="N134" s="11"/>
-      <c r="O134" s="11"/>
-      <c r="P134" s="11"/>
-      <c r="Q134" s="11"/>
-      <c r="R134" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="S134" s="12" t="s">
-        <v>744</v>
-      </c>
-      <c r="T134" s="12" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="135" spans="1:20" ht="112" x14ac:dyDescent="0.2">
-      <c r="A135" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="H135" s="1"/>
-      <c r="I135" s="1"/>
-      <c r="J135" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="K135" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L135" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M135" s="1"/>
-      <c r="N135" s="1"/>
-      <c r="O135" s="1"/>
-      <c r="P135" s="1"/>
-      <c r="Q135" s="1"/>
-      <c r="R135" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="S135" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="T135" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="136" spans="1:20" s="10" customFormat="1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A136" s="8" t="s">
-        <v>762</v>
-      </c>
-      <c r="B136" s="8" t="s">
-        <v>763</v>
-      </c>
-      <c r="C136" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="D136" s="8" t="s">
-        <v>764</v>
-      </c>
-      <c r="E136" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F136" s="8" t="s">
-        <v>765</v>
-      </c>
-      <c r="G136" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="H136" s="8"/>
-      <c r="I136" s="8"/>
-      <c r="J136" s="8" t="s">
-        <v>766</v>
-      </c>
-      <c r="K136" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="L136" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="M136" s="8"/>
-      <c r="N136" s="8"/>
-      <c r="O136" s="8"/>
-      <c r="P136" s="8" t="s">
-        <v>767</v>
-      </c>
-      <c r="Q136" s="8"/>
-      <c r="R136" s="8" t="s">
-        <v>760</v>
-      </c>
-      <c r="S136" s="9" t="s">
-        <v>768</v>
-      </c>
-      <c r="T136" s="9" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="137" spans="1:20" s="10" customFormat="1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A137" s="8" t="s">
-        <v>770</v>
-      </c>
-      <c r="B137" s="8" t="s">
-        <v>771</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="D137" s="8" t="s">
-        <v>772</v>
-      </c>
-      <c r="E137" s="8" t="s">
-        <v>773</v>
-      </c>
-      <c r="F137" s="8" t="s">
-        <v>774</v>
-      </c>
-      <c r="G137" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="H137" s="8"/>
-      <c r="I137" s="8"/>
-      <c r="J137" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="K137" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="L137" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="M137" s="8"/>
-      <c r="N137" s="8"/>
-      <c r="O137" s="8"/>
-      <c r="P137" s="8" t="s">
-        <v>775</v>
-      </c>
-      <c r="Q137" s="8"/>
-      <c r="R137" s="8" t="s">
-        <v>776</v>
-      </c>
-      <c r="S137" s="9" t="s">
-        <v>777</v>
-      </c>
-      <c r="T137" s="8"/>
-    </row>
-    <row r="138" spans="1:20" ht="98" x14ac:dyDescent="0.2">
-      <c r="A138" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="G138" s="1"/>
-      <c r="H138" s="1"/>
-      <c r="I138" s="1"/>
-      <c r="J138" s="1" t="s">
-        <v>782</v>
-      </c>
-      <c r="K138" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L138" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M138" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N138" s="1"/>
-      <c r="O138" s="1"/>
-      <c r="P138" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="Q138" s="1"/>
-      <c r="R138" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="S138" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="T138" s="1"/>
-    </row>
-    <row r="139" spans="1:20" s="13" customFormat="1" ht="84" x14ac:dyDescent="0.2">
-      <c r="A139" s="11" t="s">
-        <v>785</v>
-      </c>
-      <c r="B139" s="11" t="s">
-        <v>786</v>
-      </c>
-      <c r="C139" s="11" t="s">
-        <v>631</v>
-      </c>
-      <c r="D139" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E139" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F139" s="11" t="s">
-        <v>787</v>
-      </c>
-      <c r="G139" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="H139" s="11"/>
-      <c r="I139" s="11"/>
-      <c r="J139" s="11" t="s">
-        <v>788</v>
-      </c>
-      <c r="K139" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="L139" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="M139" s="11"/>
-      <c r="N139" s="11"/>
-      <c r="O139" s="11"/>
-      <c r="P139" s="11" t="s">
-        <v>789</v>
-      </c>
-      <c r="Q139" s="11"/>
-      <c r="R139" s="11" t="s">
-        <v>760</v>
-      </c>
-      <c r="S139" s="12" t="s">
-        <v>790</v>
-      </c>
-      <c r="T139" s="11"/>
-    </row>
-    <row r="140" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="4" t="s">
-        <v>791</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="D140" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>792</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="H140" s="4"/>
-      <c r="I140" s="4"/>
-      <c r="J140" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="K140" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="L140" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M140" s="4"/>
-      <c r="N140" s="4" t="s">
-        <v>793</v>
-      </c>
-      <c r="O140" s="4"/>
-      <c r="P140" s="4"/>
-      <c r="Q140" s="4"/>
-      <c r="R140" s="4"/>
-      <c r="S140" s="5" t="s">
-        <v>794</v>
-      </c>
-      <c r="T140" s="5" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="141" spans="1:20" s="10" customFormat="1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A141" s="8" t="s">
-        <v>795</v>
-      </c>
-      <c r="B141" s="8" t="s">
-        <v>796</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="D141" s="8" t="s">
-        <v>772</v>
-      </c>
-      <c r="E141" s="8" t="s">
-        <v>773</v>
-      </c>
-      <c r="F141" s="8" t="s">
-        <v>797</v>
-      </c>
-      <c r="G141" s="8" t="s">
-        <v>798</v>
-      </c>
-      <c r="H141" s="8"/>
-      <c r="I141" s="8"/>
-      <c r="J141" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="K141" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="L141" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="M141" s="8"/>
-      <c r="N141" s="8"/>
-      <c r="O141" s="8"/>
-      <c r="P141" s="8" t="s">
-        <v>799</v>
-      </c>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="8" t="s">
-        <v>776</v>
-      </c>
-      <c r="S141" s="9" t="s">
-        <v>777</v>
-      </c>
-      <c r="T141" s="8"/>
+      <c r="S37" s="4"/>
+      <c r="T37" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T141" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T37" xr:uid="{00000000-0009-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -10,11 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Course inventory" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applied study" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ensembles" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music education" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Course inventory'!$A$1:$T$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Course inventory'!$A$1:$T$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Applied study'!$A$1:$T$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ensembles'!$A$1:$T$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Music education'!$A$1:$T$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -100,9 +102,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -113,6 +112,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -480,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T89"/>
+  <dimension ref="A1:T67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2850,17 +2852,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MUS 231</t>
+          <t>MUS 280</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Basic String Techniques</t>
+          <t>Composers Workshop</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Music: Music Education</t>
+          <t>Music: Composition</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2875,13 +2877,21 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Presents pedagogy and techniques for teaching violin, viola, cello, and bass in a school ensemble setting.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n"/>
+          <t>Weekly workshop that concentrates on a wide range of topics related to music creation. The topics, which include the performance of student works, will be guided both by contemporary concerns and by the interests of the group.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>MUS 111.</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>May be repeated for credit for a maximum of 2 units.</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice).</t>
@@ -2894,633 +2904,92 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Variable Intermittently</t>
+          <t>Fall &amp; Spring</t>
         </is>
       </c>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1. Learn the basic skills and mechanics involved with playing the violin, viola, cello, and double bass.
-2. Perform scales, studies, and solo material appropriate to elementary-level students.
-3. Implement pedagogical techniques and examine common issues/difficulties appropriate to beginning string students.
-4. Survey and analyze pedagogical materials, e.g. methods and solo literature, for elementary string students.</t>
+          <t>1. develop a better understanding of what it is to compose music, and its many possible processes.
+2. recognize the pivotal musical issues that have preoccupied art music composers since the common-practice period and how these issues are translated into new music being created today.
+3. compose music in several distinct styles, demonstrating creativity in using elements of music (pitch, rhythm, harmony, dynamics, timbre, texture, form) for expressive effect</t>
         </is>
       </c>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2023-02-14</t>
         </is>
       </c>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="2" t="n"/>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>MUS 232</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Basic Woodwind Techniques</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+    <row r="22" ht="182" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>MUS 281</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Vocal Coaching</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Music: Performance</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>C10 1u</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Presents pedagogy and techniques for developing performance ability on flute, clarinet, saxophone, oboe, and bassoon.</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>S36 1u</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Individual vocal coaching in collaborative music making for music majors or minors. Coaching times arranged according to degree recital expectations as outlined in the music major handbook.</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Department consent.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Minimum of one course from the MUS 261-269 series.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>May be repeated for credit for a maximum of 4 units.</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>A-F grading only.</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="n"/>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1. Learn the basic skills and mechanics involved with playing the flute, clarinet, saxophone, oboe, and bassoon.
-2. Perform scales, studies, and solo material appropriate to elementary-level students.
-3. Implement pedagogical techniques and examine common issues/difficulties appropriate to beginning woodwind students.
-4. Survey and analyze pedagogical materials, e.g. methods and solo literature, for elementary woodwind students.</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="n"/>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="n"/>
-      <c r="T22" s="2" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>MUS 233</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Basic Brass Techniques</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>C10 1u</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Presents pedagogy and techniques for developing performance ability on trumpet, French horn, trombone, and tuba.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2" t="n"/>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>1. Learn the basic skills and mechanics involved with playing the trumpet, French horn, trombone, and tuba.
-2. Perform scales, studies, and solo material appropriate to elementary-level brass students.
-3. Implement pedagogical techniques and examine common issues/difficulties appropriate to beginning brass students.
-4. Survey and analyze pedagogical materials, e.g. methods and solo literature, for elementary brass students.</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="n"/>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="n"/>
-      <c r="T23" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>MUS 234</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Basic Percussion Techniques</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>C10 1u</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Presents pedagogy and techniques for developing performance ability on percussion instruments.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>1. Learn the basic skills and mechanics involved with playing and teaching percussion instruments in a school setting.
-2. Perform scales, studies, and solo material appropriate to elementary-level students.
-3. Implement pedagogical techniques and examine common issues/difficulties appropriate to beginning percussion students.
-4. Survey and analyze pedagogical materials, e.g. methods and solo literature, for elementary percussion students.</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="n"/>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="n"/>
-      <c r="T24" s="2" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>MUS 235</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Basic Guitar Techniques</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>C10 1u</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Fundamentals of playing guitar with emphasis on developing competencies sufficient to employ the instrument in an educational setting.</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="n"/>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1. Learn the basic skills and mechanics involved with playing the guitar and using the guitar as an accompanying instrument.
-2. Perform scales, chords, and solo material appropriate for beginning guitar student.
-3. Implement pedagogical techniques and examine common issues/difficulties appropriate to beginning guitarists.
-4. Survey and analyze pedagogical materials, e.g. methods and solo literature, for beginning guitar students.</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="n"/>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>2016-05-01</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-05-01, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
-          </r>
-        </is>
-      </c>
-      <c r="T25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>MUS 236</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Basic Vocal Techniques</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>C10 1u</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Class instruction in fundamentals of singing.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1. Improve singing through regular practicing of vocal exercises and songs.
-2. Be come familiar with significant sources on vocal pedagogy and the art of singing.
-3. Demonstrate an understanding of the basics of breathing, posture, and good vocal tone production.
-4. Perform vocal music in solo and ensemble settings, demonstrating proper technique.
-5. Gain knowledge of vocal warm-ups and techniques for healthy vocal music as appropriate to a school setting.</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="n"/>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>2016-05-01</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-05-01, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
-          </r>
-        </is>
-      </c>
-      <c r="T26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>MUS 238</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Band: Concert Band Workshop</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>C10 1u</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Beginning Inclusive Collegiate Band that is open to all students with instrumental experience. Led by music education majors, the ensemble performs repertoire designed to foster musical growth, practical teaching skills, and collaborative performance.</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>1 year experience on a band instrument or successful completion of Basic</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>May be repeated for credit for a maximum of 4 units.</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="n"/>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>May not be used to satisfy chamber ensemble requirement for BA in music.</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>1. Demonstrate developing proficiency on an instrument through consistent participation in an ensemble setting.
-2. Perform elementary-level repertoire appropriate for K-12 school ensembles with accuracy, expression, and ensemble awareness.
-3. Apply fundamental conducting and rehearsal techniques in a live ensemble context.
-4. Integrate prior knowledge of instrumental techniques into a heterogeneous group performance setting.
-5. Collaborate effectively with peers to foster musical growth, ensemble cohesion, and inclusive musicianship.</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="n"/>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="n"/>
-      <c r="T27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>MUS 280</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Composers Workshop</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Music: Composition</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>C10 1u</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Weekly workshop that concentrates on a wide range of topics related to music creation. The topics, which include the performance of student works, will be guided both by contemporary concerns and by the interests of the group.</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>MUS 111.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>May be repeated for credit for a maximum of 2 units.</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Fall &amp; Spring</t>
         </is>
       </c>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="n"/>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1. develop a better understanding of what it is to compose music, and its many possible processes.
-2. recognize the pivotal musical issues that have preoccupied art music composers since the common-practice period and how these issues are translated into new music being created today.
-3. compose music in several distinct styles, demonstrating creativity in using elements of music (pitch, rhythm, harmony, dynamics, timbre, texture, form) for expressive effect</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="n"/>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="n"/>
-      <c r="T28" s="2" t="n"/>
-    </row>
-    <row r="29" ht="182" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>MUS 281</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Vocal Coaching</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Music: Performance</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>S36 1u</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Individual vocal coaching in collaborative music making for music majors or minors. Coaching times arranged according to degree recital expectations as outlined in the music major handbook.</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Department consent.</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Minimum of one course from the MUS 261-269 series.</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>May be repeated for credit for a maximum of 4 units.</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>A-F grading only.</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Fall &amp; Spring</t>
-        </is>
-      </c>
-      <c r="N29" s="4" t="n"/>
-      <c r="O29" s="4" t="n"/>
-      <c r="P29" s="4" t="inlineStr">
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>1. Quickly identify rhythms and pitches and maintain pitch accuracy for application in performance or composition;
 2. Bring an enriched tone production with improved technical skills to the performance of their primary instrument;
@@ -3528,13 +2997,13 @@
 4. Integrate musical ideas, methods, theory, and practice, and communicate them to others clearly and persuasively, in classroom and performance settings.</t>
         </is>
       </c>
-      <c r="Q29" s="4" t="n"/>
-      <c r="R29" s="4" t="inlineStr">
+      <c r="Q22" s="4" t="n"/>
+      <c r="R22" s="4" t="inlineStr">
         <is>
           <t>2016-05-09</t>
         </is>
       </c>
-      <c r="S29" s="5" t="inlineStr">
+      <c r="S22" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3609,7 +3078,7 @@
           </r>
         </is>
       </c>
-      <c r="T29" s="5" t="inlineStr">
+      <c r="T22" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3649,71 +3118,71 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="182" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="23" ht="182" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>MUS 282</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Instrumental Coaching</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Music: Performance</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>S36 1u</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Individual instrumental coaching in collaborative music making for music majors or minors. Coaching times arranged according to degree recital expectations as outlined in the music major handbook.</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Department consent.</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Minimum of one course from the MUS 261-269 series.</t>
         </is>
       </c>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>May be repeated for credit for a maximum of 4 units.</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Fall &amp; Spring</t>
         </is>
       </c>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="n"/>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>1. Quickly identify rhythms and pitches and maintain pitch accuracy for application in performance or composition;
 2. Bring an enriched tone production with improved technical skills to the performance of their primary instrument;
@@ -3721,13 +3190,13 @@
 4. Integrate musical ideas, methods, theory, and practice, and communicate them to others clearly and persuasively, in classroom and performance settings.</t>
         </is>
       </c>
-      <c r="Q30" s="4" t="n"/>
-      <c r="R30" s="4" t="inlineStr">
+      <c r="Q23" s="4" t="n"/>
+      <c r="R23" s="4" t="inlineStr">
         <is>
           <t>2016-05-09</t>
         </is>
       </c>
-      <c r="S30" s="5" t="inlineStr">
+      <c r="S23" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3802,7 +3271,7 @@
           </r>
         </is>
       </c>
-      <c r="T30" s="5" t="inlineStr">
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3842,71 +3311,71 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>MUS 302</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>What to Listen for in Music</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Music: Courses for Non-Music Majors</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>C02 3u</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Overview of America’s popular music, with roots in the music of immigrant populations. Includes study of history and traditions of cultural groups, and the role of music and artists as advocates for social awareness and progress.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Completion of GE Areas 1A, 1B, 1C and GE-2 with grade C- (CR) or better (GE Areas A1, A2, A3 and</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Upper division status (greater than 60 earned semester units) and completion</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Online-Asynchronous.</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>Fall &amp; Spring</t>
         </is>
       </c>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>GE-UD-3 - Upper Division Arts or Humanities, Overlay - Diversity</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>1. Express informed opinions and judgements about a variety of styles of popular music;
 2. Communicate critical thoughts, opinions, and judgements about the creative work of different artists and bands from the 1950s forward;
@@ -3917,7 +3386,7 @@
 7. Demonstrate how the perspectives of the arts or humanities are used by informed, engaged, and reflective citizens to benefit local and global communities.</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>Demonstrate an understanding of and ability to apply principles, methodologies, values systems, and thought processes employed in the arts and humanities.
 Analyze cultural production as an expression of, or reflection upon, what it means to be human.
@@ -3926,79 +3395,79 @@
 Examine the impact of their own identity on their experiences with and/or views of other cultural groups.</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="S31" s="2" t="n"/>
-      <c r="T31" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="2" t="n"/>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>MUS 303</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Entrepreneurship in the Arts</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Music: Business and Entrepreneurship</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>C02 3u</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Learn about arts careers and organizations by investigating artists, entrepreneurs, and administrators. Build skills in networking and personal branding and examine case studies of a variety of artistic ventures.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Completion of GE Areas 1A, 1B, 1C and GE-2 with grade C- (CR) or better (GE Areas A1, A2, A3 and</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Upper division status (greater than 60 earned semester units) and completion</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice).</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Online-Asynchronous or Online-Synchronous.</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>Spring ONLY</t>
         </is>
       </c>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>GE-UD-3 - Upper Division Arts or Humanities</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>1. Explain how issues of power and social identity has affected the career options for different cultural and economic groups in various arts disciplines in recent history;
 2. Describe various logistical and business aspects of arts industries and explain how important individuals and organizations in the arts have achieved success in spite of (or because of) issues of power and social identity;
@@ -4006,86 +3475,86 @@
 4. Through research, construct a personal marketing plan to achieve success on at least one possible career path.</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>Demonstrate an understanding of and ability to apply principles, methodologies, values systems, and thought processes employed in the arts and humanities.
 Analyze cultural production as an expression of, or reflection upon, what it means to be human.
 Demonstrate how the perspectives of the arts or humanities are used by informed, engaged, and reflective citizens to benefit local and global communities.</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>2023-09-14</t>
         </is>
       </c>
-      <c r="S32" s="2" t="n"/>
-      <c r="T32" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
+      <c r="T25" s="2" t="n"/>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>MUS 304</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>World Music &amp; Culture</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Music: Courses for Non-Music Majors</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>C02 3u</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Investigating various world music traditions, including those in Africa, South America, and Asia, with an emphasis on connections with culture and history. Previous musical experience welcome but not necessary.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Completion of GE Areas 1A, 1B, 1C and GE-2 with grade C- (CR) or better (GE Areas A1, A2, A3 and</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Upper division status (greater than 60 earned semester units) and completion</t>
         </is>
       </c>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice).</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>On-ground, or Hybrid, or Online-Asynchronous.</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>Fall &amp; Spring</t>
         </is>
       </c>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>GE-UD-3 - Upper Division Arts or Humanities</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>1. apply a range of general and specialized terms relating to the study of music and culture;
 2. demonstrate an in-depth familiarity with several major world music traditions, including the abilities to identify (aurally) and speak or write about specific examples of each;
@@ -4093,86 +3562,86 @@
 4. describe how, throughout the world, music is used by informed, engaged, and reflective citizens to both promote and challenge issues of cultural identity, political power, and social justice and equality.</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>Demonstrate an understanding of and ability to apply principles, methodologies, values systems, and thought processes employed in the arts and humanities.
 Analyze cultural production as an expression of, or reflection upon, what it means to be human.
 Demonstrate how the perspectives of the arts or humanities are used by informed, engaged, and reflective citizens to benefit local and global communities.</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="S33" s="2" t="n"/>
-      <c r="T33" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n"/>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>MUS 305</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Global Hip-Hop</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Music: Musicology and Ethnomusicology</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>C02 3u</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Rooted in the U.S., hip hop is now a global phenomenon. We explore examples of hip hop music and culture in various points around the world, examining how artists are adapting the art form to respond to their local conditions.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Completion of GE Areas 1A, 1B, 1C and GE-2 with grade C- (CR) or better (GE Areas A1, A2, A3 and</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Upper division status (greater than 60 earned semester units) and completion</t>
         </is>
       </c>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice).</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Online-Asynchronous.</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>Fall &amp; Spring</t>
         </is>
       </c>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>GE-UD-3 - Upper Division Arts or Humanities</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>1. Apply a range of general and specialized terms relating to the study of music;
 2. Demonstrate an in-depth familiarity with several varieties of hip hop and explain ways in which they relate to the historical, social, political, and economic contexts in which they were created, consumed, and valued;
@@ -4180,78 +3649,78 @@
 4. Complete a final project that investigates a form of hip hop of their choice and communicate their discoveries through a variety of methods.</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>Demonstrate an understanding of and ability to apply principles, methodologies, values systems, and thought processes employed in the arts and humanities.
 Analyze cultural production as an expression of, or reflection upon, what it means to be human.
 Demonstrate how the perspectives of the arts or humanities are used by informed, engaged, and reflective citizens to benefit local and global communities.</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>2022-09-23</t>
         </is>
       </c>
-      <c r="S34" s="2" t="n"/>
-      <c r="T34" s="2" t="n"/>
+      <c r="S27" s="2" t="n"/>
+      <c r="T27" s="2" t="n"/>
     </row>
-    <row r="35" ht="266" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="28" ht="266" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>MUS 312</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Form and Analysis</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Music: Theory and Musicianship</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>C02 2u + C10 1u</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>The exploration and analysis of music styles and structural forms of the European art music of the 18th and 19th C. Topics include phrase and sentence structures; thematic organization; binary and ternary forms; variation and rondo forms; slow movement forms; and sonata forms.</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>MUS 211, or Sucessful Theory &amp; Musicianship Placement Exam.</t>
         </is>
       </c>
-      <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="n"/>
-      <c r="J35" s="4" t="n"/>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice).</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>Fall Alternate Years</t>
         </is>
       </c>
-      <c r="N35" s="4" t="n"/>
-      <c r="O35" s="4" t="n"/>
-      <c r="P35" s="4" t="inlineStr">
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n"/>
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>1. Demonstrate understanding of the forms used in tonal music.
 2. Analyze and evaluate works of music in various forms in their technical, aesthetic, and historical contexts.
@@ -4259,13 +3728,13 @@
 4. Implement the principles and concepts studied in class via performance on your major instrument or voice</t>
         </is>
       </c>
-      <c r="Q35" s="4" t="n"/>
-      <c r="R35" s="4" t="inlineStr">
+      <c r="Q28" s="4" t="n"/>
+      <c r="R28" s="4" t="inlineStr">
         <is>
           <t>2023-02-13</t>
         </is>
       </c>
-      <c r="S35" s="5" t="inlineStr">
+      <c r="S28" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4322,7 +3791,7 @@
           </r>
         </is>
       </c>
-      <c r="T35" s="5" t="inlineStr">
+      <c r="T28" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4362,63 +3831,63 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>MUS 317</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Improvisation Techniques</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Music: Jazz Studies</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>C10 1u</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>A course focusing on developing soloing techniques idiomatic to the bebop and post-bop traditions. Includes jazz theory, analysis and performance of key transcriptions of bebop and post-bop masters as well as in-class application of the fundamental devices employed in modern jazz improvisation.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>MUS 112, MUS 116.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>May be repeated for credit for a maximum of 4 units.</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice).</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2" t="n"/>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>1. introduce instrumentalists and vocalists to the fundamentals of jazz improvisation
 2. The study and application of jazz theory
@@ -4428,13 +3897,13 @@
 6. Develop an audible comprehension of jazz harmony through ear-training exercises</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="n"/>
-      <c r="R36" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="n"/>
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>2023-09-15</t>
         </is>
       </c>
-      <c r="S36" s="3" t="inlineStr">
+      <c r="S29" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4455,7 +3924,7 @@
           </r>
         </is>
       </c>
-      <c r="T36" s="3" t="inlineStr">
+      <c r="T29" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4477,59 +3946,59 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>MUS 321</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Western Music History I</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Music: Musicology and Ethnomusicology</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>C02 3u</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Investigating the stylistic development of music of western civilization; focus on the social, cultural, and historical contexts of the music of each style period. (I.) Music from the Medieval to Baroque periods.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice).</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Hybrid.</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>Fall Alternate Years</t>
         </is>
       </c>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2" t="n"/>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>1. Develop a vocabulary of general and specialized musical terms of these periods;
 2. Become familiar with the musical traditions that dominated western Europe in the Medieval, Renaissance and Baroque periods;
@@ -4539,68 +4008,68 @@
 6. Employ critical thinking in the process of undertaking short research assignments</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="n"/>
-      <c r="R37" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>2023-02-13</t>
         </is>
       </c>
-      <c r="S37" s="2" t="n"/>
-      <c r="T37" s="2" t="n"/>
+      <c r="S30" s="2" t="n"/>
+      <c r="T30" s="2" t="n"/>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>MUS 322</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Western Music History II</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Music: Musicology and Ethnomusicology</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>C02 3u</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Investigating the stylistic development of music of western civilization; focus on the social, cultural, and historical contexts of the music of each style period. (II.) Music from the Classical to contemporary periods.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice).</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>Hybrid.</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>Spring Alternate Years</t>
         </is>
       </c>
-      <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2" t="n"/>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>1. Develop a vocabulary of general and specialized musical terms of these periods;
 2. Become familiar with the musical traditions that dominated western Europe in the Baroque period to the present;
@@ -4610,10 +4079,632 @@
 6. Employ critical thinking in the process of undertaking short research assignments.</t>
         </is>
       </c>
+      <c r="Q31" s="2" t="n"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2023-02-13</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>MUS 323</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Topics in Western Music History</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Music: Musicology and Ethnomusicology</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>C02 3u</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Special topics in Western music history, with changing content that highlights fresh, niche, or experimental areas of study. Each version offers new perspectives and may be repeated for credit when themes differ.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>May be repeated for credit for a maximum of 12 units.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>On-ground, or Hybrid, or Online-Asynchronous, or Online-Synchronous.</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1. Identify musicians who played key roles in shaping these musical traditions;
+2. Learn to see connections between musical practices and the societies that create and sustain them;
+3. Learn to analyze (or “deconstruct”) musical scores for different types of information; and
+4. Employ critical thinking in the process of undertaking short research assignments.</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="n"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="n"/>
+      <c r="T32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>MUS 324</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>History of American Music</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Music: Musicology and Ethnomusicology</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to the musical styles, composers, and institutions that have shaped American music through history. Special emphasis will be given to the contributions of Black Americans to the foundation and development of American music.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid or Online-Asynchronous.</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>Overlay - Diversity</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>1. Describe the histories, experiences or views of one or more cultural groups.
+2. Analyze the overlap or intersection of social identities of oneself and/or other cultural groups (e.g., culture, gender, class, sexuality, religion, disability, immigration status, and/or age).
+3. Examine the impact of their own identity on their experiences with and/or views of other cultural groups.</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="n"/>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="n"/>
+      <c r="T33" s="2" t="n"/>
+    </row>
+    <row r="34" ht="70" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MUS 326</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Topics in Global Music</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Music: Musicology and Ethnomusicology</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>C02 3u</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>A rotating-topics course introducing students to the diversity of global musical traditions. Emphasis is placed on listening, analysis, and discussion of music in cultural context. Topics vary by semester and may include Africa, the Americas, Asia, or the diaspora.</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Repeatable for credit up to 9 units.</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>A-F grading only.</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>A rotating-topics course introducing students to the diversity of global musical traditions.</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Fall &amp; Spring</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="n"/>
+      <c r="P34" s="4" t="n"/>
+      <c r="Q34" s="4" t="n"/>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">no learning outcomes published
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>add learning outcomes</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+repeatability uses non-standard phrasing
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>reword to may be repeated for credit for a maximum of 9 units</t>
+          </r>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">no outcomes published
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>to be drafted by area faculty</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>MUS 380</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Recital Class</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Music: Performance</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>C05 1u</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>This class is designed to guide students through every aspect of the preparation for their degree recitals. Topics include creating the program, strategizing personal practice, addressing the logistics of performing a recital, musician wellness and the mental aspects of performance.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Minimum of one course from the MUS 261-269 series.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Minimum of one course from the MUS 361-370 series.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>A-F grading only.</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Fall ONLY</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>1. Develop a well-balanced and inclusive program with the appropriate format;
+2. Develop long- and short-term practice strategies;
+3. Explore musician wellness, mindfulness, and techniques to deal with performance anxiety;
+4. Practice stage etiquette, audience interaction, and critique performances of peers.</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="n"/>
+      <c r="T35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>MUS 381</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Essentials of Music Technology</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Music: Composition</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>An introduction to the fundamental concepts of music technology, including acoustics and the elements of sound, audio recording, sample editing and overall sound mixing. The course will also briefly overview advanced topics in the field, such as DSP and synthesis.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>1. Discuss and evaluate the place of music technology in the music industry
+2. Identify and discuss the fundamental concepts of acoustics and digital audio
+3. Identify and explain the basic elements of MIDI
+4. Use basic recording and sound reinforcement equipment for musical projects
+5. Use music software for digital audio, synthesis, sequencing, and music notation</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="n"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2020-10-14</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="n"/>
+      <c r="T36" s="2" t="n"/>
+    </row>
+    <row r="37" ht="293" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>MUS 410</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>20th and 21st C Styles and Techniques</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Music: Theory and Musicianship</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>C02 3u</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Intensive course that introduces students to the inner workings of European and American art music of the 20th and 21st centuries.</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Spring Alternate Years</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n"/>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>1. Demonstrate understanding of the different genres and styles within 20th and 21st art music.
+2. Analyze and evaluate works of music in various forms in their technical, aesthetic, and historical contexts.
+3. Apply the knowledge learned in earlier theory courses to extended musical works.
+4. Implement the principles and concepts studied in class via performance on your area of emphasis.</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="n"/>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="S37" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">reclassification pending per the theory and musicianship guide, effective fall 2027
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set 2 units C05 plus 1 unit C10</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+no prerequisite published, though the guide states MUS 312
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>prerequisite: MUS 312, or equivalent, or department consent</t>
+          </r>
+        </is>
+      </c>
+      <c r="T37" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Analytical and compositional techniques of the 20th and 21st centuries: post-tonal collections, pitch-class sets, centricity, twelve-tone serialism, form in post-tonal music, and the movements that follow 1945, including spectralism and minimalism.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+four outcomes where the syllabus carries six, omitting pitch-class set construction and twelve-tone analysis, where the syllabus outcomes from the musicianship overhaul are current
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Demonstrate understanding of the different genres, styles, and techniques of 20th and 21st century art music. 2. Analyze and evaluate post-tonal works in their technical, aesthetic, and historical contexts, supporting interpretive claims with evidence from the score. 3. Construct and manipulate post-tonal pitch collections, including pitch-class sets in normal and prime form, and analyze twelve-tone rows and their transformations. 4. Apply knowledge from earlier theory courses to extended post-tonal and contemporary works. 5. Situate works within the major compositional movements of the 20th and 21st centuries, including serialism, spectralism, minimalism, and extended techniques. 6. Implement the principles and concepts studied in class via performance on the student's area of emphasis.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>MUS 412</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Contrapuntal Techniques</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Music: Composition</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>C04 3u</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Contrapuntal procedures from the High Renaissance and its impact on modern use of modal melodic writing in contemporary non-classical music styles.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Fall Alternate Years</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>1. Develop skills in the composition and analysis of 16th &amp; early 17th century modal polyphonic music
+2. Mastery and understanding of the principles of modal counterpoint
+3. Develop historical and technical insight into modal melodic writing
+4. Demonstrate skill in combining musical lines</t>
+        </is>
+      </c>
       <c r="Q38" s="2" t="n"/>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2023-02-14</t>
         </is>
       </c>
       <c r="S38" s="2" t="n"/>
@@ -4622,17 +4713,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MUS 323</t>
+          <t>MUS 414</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Topics in Western Music History</t>
+          <t>Contemporary Orchestration and Arranging</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Music: Musicology and Ethnomusicology</t>
+          <t>Music: Composition</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4642,22 +4733,18 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>C02 3u</t>
+          <t>C04 3u</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Special topics in Western music history, with changing content that highlights fresh, niche, or experimental areas of study. Each version offers new perspectives and may be repeated for credit when themes differ.</t>
+          <t>Course devoted to fundamentals of instrumentation and arranging for contemporary band and orchestral instruments. The study of basic elements (range, transposition, timbre) of each instrument will be followed by examination and analysis of orchestration ‘problems’ and solutions from repertoire.</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>May be repeated for credit for a maximum of 12 units.</t>
-        </is>
-      </c>
+      <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice).</t>
@@ -4665,24 +4752,29 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>On-ground, or Hybrid, or Online-Asynchronous, or Online-Synchronous.</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="n"/>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Fall Alternate Years</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1. Identify musicians who played key roles in shaping these musical traditions;
-2. Learn to see connections between musical practices and the societies that create and sustain them;
-3. Learn to analyze (or “deconstruct”) musical scores for different types of information; and
-4. Employ critical thinking in the process of undertaking short research assignments.</t>
+          <t>1. gain all necessary skills to arrange or compose for any ensemble
+2. develop intimate knowledge of the characteristics of every orchestral instrument
+3. recognize and recreate standard scoring patterns
+4. develop a concept of arranging as composition
+5. strengthen the inner ear and auditory ideation</t>
         </is>
       </c>
       <c r="Q39" s="2" t="n"/>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2023-02-14</t>
         </is>
       </c>
       <c r="S39" s="2" t="n"/>
@@ -4691,17 +4783,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MUS 324</t>
+          <t>MUS 415</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>History of American Music</t>
+          <t>MIDI Orchestration</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Music: Musicology and Ethnomusicology</t>
+          <t>Music: Composition</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4711,15 +4803,19 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>C02 2u + C10 1u</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Introduction to the musical styles, composers, and institutions that have shaped American music through history. Special emphasis will be given to the contributions of Black Americans to the foundation and development of American music.</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n"/>
+          <t>This course is devoted to students interested in writing orchestration projects for visual media, or contemporary arrangements to support other musical styles. It will cover basic techniques of creating a full orchestral sound through sequencing and sampling libraries.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>MUS 381.</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
@@ -4730,936 +4826,17 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Hybrid or Online-Asynchronous.</t>
+          <t>On-ground.</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Fall &amp; Spring</t>
+          <t>Variable Intermittently</t>
         </is>
       </c>
       <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>Overlay - Diversity</t>
-        </is>
-      </c>
+      <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>1. Describe the histories, experiences or views of one or more cultural groups.
-2. Analyze the overlap or intersection of social identities of oneself and/or other cultural groups (e.g., culture, gender, class, sexuality, religion, disability, immigration status, and/or age).
-3. Examine the impact of their own identity on their experiences with and/or views of other cultural groups.</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="n"/>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="n"/>
-      <c r="T40" s="2" t="n"/>
-    </row>
-    <row r="41" ht="70" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>MUS 326</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Topics in Global Music</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Music: Musicology and Ethnomusicology</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>C02 3u</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>A rotating-topics course introducing students to the diversity of global musical traditions. Emphasis is placed on listening, analysis, and discussion of music in cultural context. Topics vary by semester and may include Africa, the Americas, Asia, or the diaspora.</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Repeatable for credit up to 9 units.</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>A-F grading only.</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>A rotating-topics course introducing students to the diversity of global musical traditions.</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>Fall &amp; Spring</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="n"/>
-      <c r="O41" s="4" t="n"/>
-      <c r="P41" s="4" t="n"/>
-      <c r="Q41" s="4" t="n"/>
-      <c r="R41" s="4" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="S41" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no learning outcomes published
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>add learning outcomes</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-repeatability uses non-standard phrasing
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reword to may be repeated for credit for a maximum of 9 units</t>
-          </r>
-        </is>
-      </c>
-      <c r="T41" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no outcomes published
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>to be drafted by area faculty</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>MUS 331</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Foundations of Music Education</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Overview of music education for prospective music educators, with a focus on K-12 music education. Topics include philosophy of music education, K-12 music pedagogy, and the history, economics, and policy of music education. Field trips may be required.</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>A-F grading only.</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="n"/>
-      <c r="O42" s="2" t="n"/>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>1. Reflect, analyze, and discuss the student’s own music education experiences,
-2. Demonstrate knowledge of the primary forms of both traditional and non-traditional music education in the contemporary United States,
-3. Observe and reflect on music education in a variety of K-12 school settings,
-4. Demonstrate understanding of major theories and approaches to music teaching and learning, including knowledge of major events in the history of American music education,
-5. Demonstrate knowledge of the California State and National Standards in music education,
-6. Demonstrate knowledge of the roles and issues of cultural diversity and special learners in today’s schools.</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="n"/>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>2016-02-18</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-02-18, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
-          </r>
-        </is>
-      </c>
-      <c r="T42" s="2" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>MUS 335</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Technology for Music Educators</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>C05 1u + C13</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Instruction in uses of audio software, and software for desktop, interactive, and music publishing to aid in the development of music education curricula, programs, and lessons. Seminar Units: 2; Activity Units: 1.</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="n"/>
-      <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>1. Mastery of live sound knowledge as it applies to k-12 environments, including microphones, PA setup and; usage, and logistically planning for amplifying ensembles.
-2. Ability to edit and master digital audio using a DAW.
-3. Advocate for music technology needs in the classroom through the drafting of grant proposals.
-4. Utilize music notation software with rehearsal software in order to create lessons and lesson plans otherwise not possible.
-5. Create learning modules in teams using video and audio editing software.</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="n"/>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>2016-04-27</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
-          </r>
-        </is>
-      </c>
-      <c r="T43" s="2" t="n"/>
-    </row>
-    <row r="44" ht="126" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>MUS 341</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Basic Conducting</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>C05 2u</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Basic techniques of conducting including simple, compound and asymmetrical meters, expression and interpretation through observation and laboratory experience.</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>Junior, senior or post-baccalaureate standing.</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M44" s="4" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N44" s="4" t="n"/>
-      <c r="O44" s="4" t="n"/>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>1. Develop the skills needed by conductors with an emphasis on physical gesture, score study, and expression.
-2. Develop inner hearing and interpretation skills.
-3. Have knowledge of noteworthy conducting scholarship and materials.
-4. Demonstrate understanding via in-class conducting presentations Page: 1 &lt;- Back 10 … 12 | 13 | 14 | 15 | 16 | 17 | 18 | 19 | 20 | 21 | 22 … Forward 10 -&gt; 28 Contract All Courses | Print this Page</t>
-        </is>
-      </c>
-      <c r="Q44" s="4" t="n"/>
-      <c r="R44" s="4" t="inlineStr">
-        <is>
-          <t>2016-04-26</t>
-        </is>
-      </c>
-      <c r="S44" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">classification holds 2 units of C05 where the course publishes 3, a quarter-conversion artifact
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>set the classification to C05 3u</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-last revised 2016-04-26, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>review the full record on the current form</t>
-          </r>
-        </is>
-      </c>
-      <c r="T44" s="4" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>MUS 380</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Recital Class</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Music: Performance</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>C05 1u</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>This class is designed to guide students through every aspect of the preparation for their degree recitals. Topics include creating the program, strategizing personal practice, addressing the logistics of performing a recital, musician wellness and the mental aspects of performance.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Minimum of one course from the MUS 261-269 series.</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Minimum of one course from the MUS 361-370 series.</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>A-F grading only.</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>Fall ONLY</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="n"/>
-      <c r="O45" s="2" t="n"/>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>1. Develop a well-balanced and inclusive program with the appropriate format;
-2. Develop long- and short-term practice strategies;
-3. Explore musician wellness, mindfulness, and techniques to deal with performance anxiety;
-4. Practice stage etiquette, audience interaction, and critique performances of peers.</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="n"/>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="n"/>
-      <c r="T45" s="2" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>MUS 381</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Essentials of Music Technology</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Music: Composition</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>An introduction to the fundamental concepts of music technology, including acoustics and the elements of sound, audio recording, sample editing and overall sound mixing. The course will also briefly overview advanced topics in the field, such as DSP and synthesis.</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>1. Discuss and evaluate the place of music technology in the music industry
-2. Identify and discuss the fundamental concepts of acoustics and digital audio
-3. Identify and explain the basic elements of MIDI
-4. Use basic recording and sound reinforcement equipment for musical projects
-5. Use music software for digital audio, synthesis, sequencing, and music notation</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="n"/>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="293" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>MUS 410</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>20th and 21st C Styles and Techniques</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Music: Theory and Musicianship</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>C02 3u</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Intensive course that introduces students to the inner workings of European and American art music of the 20th and 21st centuries.</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M47" s="4" t="inlineStr">
-        <is>
-          <t>Spring Alternate Years</t>
-        </is>
-      </c>
-      <c r="N47" s="4" t="n"/>
-      <c r="O47" s="4" t="n"/>
-      <c r="P47" s="4" t="inlineStr">
-        <is>
-          <t>1. Demonstrate understanding of the different genres and styles within 20th and 21st art music.
-2. Analyze and evaluate works of music in various forms in their technical, aesthetic, and historical contexts.
-3. Apply the knowledge learned in earlier theory courses to extended musical works.
-4. Implement the principles and concepts studied in class via performance on your area of emphasis.</t>
-        </is>
-      </c>
-      <c r="Q47" s="4" t="n"/>
-      <c r="R47" s="4" t="inlineStr">
-        <is>
-          <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="S47" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">reclassification pending per the theory and musicianship guide, effective fall 2027
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set 2 units C05 plus 1 unit C10</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-no prerequisite published, though the guide states MUS 312
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>prerequisite: MUS 312, or equivalent, or department consent</t>
-          </r>
-        </is>
-      </c>
-      <c r="T47" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">description
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Analytical and compositional techniques of the 20th and 21st centuries: post-tonal collections, pitch-class sets, centricity, twelve-tone serialism, form in post-tonal music, and the movements that follow 1945, including spectralism and minimalism.</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-four outcomes where the syllabus carries six, omitting pitch-class set construction and twelve-tone analysis, where the syllabus outcomes from the musicianship overhaul are current
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Demonstrate understanding of the different genres, styles, and techniques of 20th and 21st century art music. 2. Analyze and evaluate post-tonal works in their technical, aesthetic, and historical contexts, supporting interpretive claims with evidence from the score. 3. Construct and manipulate post-tonal pitch collections, including pitch-class sets in normal and prime form, and analyze twelve-tone rows and their transformations. 4. Apply knowledge from earlier theory courses to extended post-tonal and contemporary works. 5. Situate works within the major compositional movements of the 20th and 21st centuries, including serialism, spectralism, minimalism, and extended techniques. 6. Implement the principles and concepts studied in class via performance on the student's area of emphasis.</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>MUS 412</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Contrapuntal Techniques</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Music: Composition</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>C04 3u</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Contrapuntal procedures from the High Renaissance and its impact on modern use of modal melodic writing in contemporary non-classical music styles.</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="n"/>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>Fall Alternate Years</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="n"/>
-      <c r="O48" s="2" t="n"/>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>1. Develop skills in the composition and analysis of 16th &amp; early 17th century modal polyphonic music
-2. Mastery and understanding of the principles of modal counterpoint
-3. Develop historical and technical insight into modal melodic writing
-4. Demonstrate skill in combining musical lines</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="n"/>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="n"/>
-      <c r="T48" s="2" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>MUS 414</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Contemporary Orchestration and Arranging</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Music: Composition</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>C04 3u</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Course devoted to fundamentals of instrumentation and arranging for contemporary band and orchestral instruments. The study of basic elements (range, transposition, timbre) of each instrument will be followed by examination and analysis of orchestration ‘problems’ and solutions from repertoire.</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="n"/>
-      <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>Fall Alternate Years</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="n"/>
-      <c r="O49" s="2" t="n"/>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>1. gain all necessary skills to arrange or compose for any ensemble
-2. develop intimate knowledge of the characteristics of every orchestral instrument
-3. recognize and recreate standard scoring patterns
-4. develop a concept of arranging as composition
-5. strengthen the inner ear and auditory ideation</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="n"/>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="n"/>
-      <c r="T49" s="2" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>MUS 415</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>MIDI Orchestration</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Music: Composition</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>C02 2u + C10 1u</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>This course is devoted to students interested in writing orchestration projects for visual media, or contemporary arrangements to support other musical styles. It will cover basic techniques of creating a full orchestral sound through sequencing and sampling libraries.</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>MUS 381.</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="2" t="n"/>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="n"/>
-      <c r="O50" s="2" t="n"/>
-      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>1. Understand the basic aesthetics of synthestration
 2. familiarize oneself with project studio requirements and considerations, such as computer choices, sequencing software and sample libraries
@@ -5667,637 +4844,80 @@
 4. produce “musical” facsimiles of acoustic instrument performances</t>
         </is>
       </c>
-      <c r="Q50" s="2" t="n"/>
-      <c r="R50" s="2" t="inlineStr">
+      <c r="Q40" s="2" t="n"/>
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="S50" s="2" t="n"/>
-      <c r="T50" s="2" t="n"/>
+      <c r="S40" s="2" t="n"/>
+      <c r="T40" s="2" t="n"/>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>MUS 431</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Elementary Music Teaching Methods</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>C05 3u</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Designed for prospective school music educators. Development of methods, techniques, and knowledge appropriate for teaching elementary general music classes. Study and exploration of elementary music instructional materials and topics. Field trips may be required.</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Junior, senior or post-baccalaureate standing.</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="n"/>
-      <c r="I51" s="2" t="n"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>May be repeated for credit for a maximum of 6 units.</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
+    <row r="41" ht="182" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>MUS 481</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Vocal Coaching</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Music: Performance</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>1–2</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>C36 1-2u</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Individual vocal coaching in collaborative music making for music majors or minors. Coaching times arranged according to degree recital expectations as outlined in the music major handbook.</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Department consent.</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Minimum of one course from the MUS 461-469 series.</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>May be repeated for credit for a maximum of 8 units.</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>A-F grading only.</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="n"/>
-      <c r="O51" s="2" t="n"/>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>1. To study and implement a variety of diverse approaches to teaching music to elementary level students.
-2. To become familiar with the methodologies of Orff, Kodály, Dalcroze, and Gordon (Music Learning Theory).
-3. To write lesson plans in a variety of formats, including the use of state and national standards for elementary general music.
-4. To plan, participate in, and reflect on several peer teaching episodes.
-5. To observe elementary general music teachers (Field Trips May Be Required).
-6. To become familiar with a wide variety of resources for teaching elementary music</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="n"/>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>2016-04-27</t>
-        </is>
-      </c>
-      <c r="S51" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
-          </r>
-        </is>
-      </c>
-      <c r="T51" s="2" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>MUS 432</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Instrumental Music Teaching Methods</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>C05 3u</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Provides opportunity for students intending to become music teachers to develop rehearsal techniques, organizational procedures related to public school band and orchestra programs; become familiar with public school teaching materials; further develop conducting techniques; and improve secondary instruments skills.</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>MUS 341.</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="n"/>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="n"/>
-      <c r="O52" s="2" t="n"/>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>1. To understand a variety of theories regarding the teaching of instrumental music,
-2. To familiarize the student with the National and State standards for instrumental music education and to apply them to instruction,
-3. To become familiar with and evaluate resources,
-4. To further develop score study, transposition, and conducting skills,
-5. To develop rehearsal planning and classroom management skills
-6. To perform on a secondary instrument in an ensemble,
-7. To develop a library of resources for future use as an instrumental music educator,
-8. To observe excellent elementary and secondary school instrumental music teachers. Field Trips May Be Required</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="n"/>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>2016-04-27</t>
-        </is>
-      </c>
-      <c r="S52" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
-          </r>
-        </is>
-      </c>
-      <c r="T52" s="2" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>MUS 433</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Choral Music Teaching Methods</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>C05 3u</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Development of rehearsal techniques and organizational procedures related to choirs and vocal ensembles in the elementary and secondary schools. Teaching materials and appropriate literature from various stylistic periods. Field trips may be required.</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>MUS 341.</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="n"/>
-      <c r="O53" s="2" t="n"/>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>1. Develop musical, curricular, and organizational skills necessary to lead a choral program at the elementary and secondary level
-2. Refine choral conducting skills, building on the fundamental topics of conducting including inner hearing, breathing, scholarship and expressive interpretation.
-3. Develop knowledge of instructional materials and score-reading ability.
-4. Demonstrate the ability to conduct and teach choral music during in-class experiences.
-5. Develop familiarity with choral music education materials</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="n"/>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>2016-04-27</t>
-        </is>
-      </c>
-      <c r="S53" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
-          </r>
-        </is>
-      </c>
-      <c r="T53" s="2" t="n"/>
-    </row>
-    <row r="54" ht="126" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>MUS 441</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Intermediate Conducting</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>C05 2u</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>Special techniques of choral conducting including vocal and score reading and analysis, interpretation, and rehearsal through observation and laboratory experience.</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>MUS 341 and junior, senior or post-baccalaureate standing.</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>May be repeated for credit for a maximum of 6 units.</t>
-        </is>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M54" s="4" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N54" s="4" t="n"/>
-      <c r="O54" s="4" t="n"/>
-      <c r="P54" s="4" t="inlineStr">
-        <is>
-          <t>1. Demonstrate the ability to analyze and read vocal and instrumental scores
-2. Independently conduct student choral and instrumental groups.
-3. Demonstrate mastery of standard conducting patterns and gestures.
-4. Conduct music in an interpretive and expressive manner.
-5. Demonstrate knowledge of notable conductors and conducting scholarship</t>
-        </is>
-      </c>
-      <c r="Q54" s="4" t="n"/>
-      <c r="R54" s="4" t="inlineStr">
-        <is>
-          <t>2016-04-27</t>
-        </is>
-      </c>
-      <c r="S54" s="5" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">classification holds 2 units of C05 where the course publishes 3, a quarter-conversion artifact
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>set the classification to C05 3u</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-last revised 2016-04-27, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="11"/>
-            </rPr>
-            <t>review the full record on the current form</t>
-          </r>
-        </is>
-      </c>
-      <c r="T54" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>MUS 445</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Piano Pedagogy</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>C02 2u</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>A comparison and analysis of current pedagogical approaches to the teaching of piano with attention to specific problems of the literature and technique, including appropriate studies in anatomy, physiology, and acoustics; particular emphasis upon the teaching of the younger student.</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="n"/>
-      <c r="H55" s="2" t="n"/>
-      <c r="I55" s="2" t="n"/>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>May be repeated for credit for a maximum of 6 units.</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>Fall Alternate Years</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="n"/>
-      <c r="O55" s="2" t="n"/>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>1. To establish an understanding of the layering of pedagogical concepts and skills in increasing levels of complexity
-2. To provide a structured and critical study of the most popular of the current beginning methods books and supplementary materials
-3. To study how learning takes place through an introductory survey of learning theories
-4. To make an in-depth study of the history and development of thought on piano technique, and its application to healthy practice techniques
-5. To cultivate awareness of effective teaching fundamentals of making music at the piano, including stylistic and expressive repertoire performance, and providing a solid technical foundation
-6. To prepare well-balanced and well-sequenced lesson plans and longer-term programs of study for students of various advancement levels</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="n"/>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="n"/>
-      <c r="T55" s="2" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>MUS 446</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Vocal Pedagogy</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to professional voice teaching. Examines methods, materials, resources, and techniques for teaching beginning voice students. Students will learn vocal anatomy, observe vocal instruction, and survey beginning and intermediate vocal repertoire.</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>MUS 112, MUS 116.</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>May be repeated for credit for a maximum of 4 units.</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice).</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>On-ground, or Hybrid, or Online-Asynchronous.</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="n"/>
-      <c r="N56" s="2" t="n"/>
-      <c r="O56" s="2" t="n"/>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>1. Develop pedagogical skills for teaching the beginning voice student
-2. Evaluate methods and materials available to the voice teacher
-3. Observe and analyze university-level secondary group voice classes
-4. Develop the ability to plan private lessons for peer and instructor feedback
-5. Explore the business aspects of operating an independent vocal studio
-6. Articulate a studio policy and marketing strategy
-7. Evaluate online and print resources relating to professional voice teaching including journals, magazines, books and conferences proceedings</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="n"/>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>2019-02-17</t>
-        </is>
-      </c>
-      <c r="S56" s="3" t="n"/>
-      <c r="T56" s="2" t="n"/>
-    </row>
-    <row r="57" ht="182" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>MUS 481</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Vocal Coaching</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Music: Performance</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>1–2</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>C36 1-2u</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>Individual vocal coaching in collaborative music making for music majors or minors. Coaching times arranged according to degree recital expectations as outlined in the music major handbook.</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>Department consent.</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>Minimum of one course from the MUS 461-469 series.</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="n"/>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>May be repeated for credit for a maximum of 8 units.</t>
-        </is>
-      </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>A-F grading only.</t>
-        </is>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>Fall &amp; Spring</t>
         </is>
       </c>
-      <c r="N57" s="4" t="n"/>
-      <c r="O57" s="4" t="n"/>
-      <c r="P57" s="4" t="inlineStr">
+      <c r="N41" s="4" t="n"/>
+      <c r="O41" s="4" t="n"/>
+      <c r="P41" s="4" t="inlineStr">
         <is>
           <t>1. Quickly identify rhythms and pitches and maintain pitch accuracy for application in performance or composition;
 2. Bring an enriched tone production with improved technical skills to the performance of their primary instrument;
@@ -6305,13 +4925,13 @@
 4. Integrate musical ideas, methods, theory, and practice, and communicate them to others clearly and persuasively, in classroom and performance settings.</t>
         </is>
       </c>
-      <c r="Q57" s="4" t="n"/>
-      <c r="R57" s="4" t="inlineStr">
+      <c r="Q41" s="4" t="n"/>
+      <c r="R41" s="4" t="inlineStr">
         <is>
           <t>2023-09-15</t>
         </is>
       </c>
-      <c r="S57" s="5" t="inlineStr">
+      <c r="S41" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6332,7 +4952,7 @@
           </r>
         </is>
       </c>
-      <c r="T57" s="5" t="inlineStr">
+      <c r="T41" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6372,71 +4992,71 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="182" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="42" ht="182" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>MUS 482</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Instrumental Coaching</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Music: Performance</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>1–2</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>C36 1-2u</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>Individual instrumental coaching in collaborative music making for music majors or minors. Coaching times arranged according to degree recital expectations as outlined in the music major handbook.</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>Department consent.</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>Minimum of one course from the MUS 461-469 series.</t>
         </is>
       </c>
-      <c r="I58" s="4" t="n"/>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>May be repeated for credit for a maximum of 8 units.</t>
         </is>
       </c>
-      <c r="K58" s="4" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L58" s="4" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M58" s="4" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>Fall &amp; Spring</t>
         </is>
       </c>
-      <c r="N58" s="4" t="n"/>
-      <c r="O58" s="4" t="n"/>
-      <c r="P58" s="4" t="inlineStr">
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="4" t="inlineStr">
         <is>
           <t>1. Quickly identify rhythms and pitches and maintain pitch accuracy for application in performance or composition;
 2. Bring an enriched tone production with improved technical skills to the performance of their primary instrument;
@@ -6444,13 +5064,13 @@
 4. Integrate musical ideas, methods, theory, and practice, and communicate them to others clearly and persuasively, in classroom and performance settings.</t>
         </is>
       </c>
-      <c r="Q58" s="4" t="n"/>
-      <c r="R58" s="4" t="inlineStr">
+      <c r="Q42" s="4" t="n"/>
+      <c r="R42" s="4" t="inlineStr">
         <is>
           <t>2023-09-15</t>
         </is>
       </c>
-      <c r="S58" s="5" t="inlineStr">
+      <c r="S42" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6471,7 +5091,7 @@
           </r>
         </is>
       </c>
-      <c r="T58" s="5" t="inlineStr">
+      <c r="T42" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6511,63 +5131,63 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>MUS 485</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Advanced Sound Design I: Sampling, Editing, and Mixing</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Music: Composition</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>C02 2u + C13 1u</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Advanced Sound Design 1: Sampling, Editing, and Mixing focuses on creative music production with sampling. Students develop advanced recording, editing, and processing techniques while building practical workflows for music, sound design, and multimedia applications through hands-on projects and critical listening.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n"/>
-      <c r="H59" s="2" t="n"/>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>Students enrolling in Advanced Sound Design are strongly encouraged to</t>
         </is>
       </c>
-      <c r="J59" s="2" t="n"/>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice).</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>Spring ONLY</t>
         </is>
       </c>
-      <c r="N59" s="2" t="n"/>
-      <c r="O59" s="2" t="n"/>
-      <c r="P59" s="2" t="inlineStr">
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="inlineStr">
         <is>
           <t>1. Understand Sound Design as both an artistic and technical process, and know the artistic and technical vocabulary with which a Sound Designer communicates.
 2. Examine the principles and techniques associated with sampling and samplers, including recording, editing, and programming
@@ -6575,72 +5195,72 @@
 4. Create an audio project based on the use of sampling and samplers</t>
         </is>
       </c>
-      <c r="Q59" s="2" t="n"/>
-      <c r="R59" s="2" t="inlineStr">
+      <c r="Q43" s="2" t="n"/>
+      <c r="R43" s="2" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="S59" s="2" t="n"/>
-      <c r="T59" s="2" t="n"/>
+      <c r="S43" s="2" t="n"/>
+      <c r="T43" s="2" t="n"/>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>MUS 486</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Advanced Sound Design II: Synthesis, Modulation &amp; Creative Digital</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Music: Composition</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>C02 2u + C13 1u</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Synthesis, Modulation &amp; Creative Digital Signal Processing serves advanced students interested in creating stand- alone electronic compositions. The course emphasizes synthesis programming, modulation, and computer-based composition techniques, developing skills in sound design, signal processing, and innovative digital workflows.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2" t="n"/>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>Students enrolling in Advanced Sound Design are strongly encouraged to</t>
         </is>
       </c>
-      <c r="J60" s="2" t="n"/>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice).</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>Fall ONLY</t>
         </is>
       </c>
-      <c r="N60" s="2" t="n"/>
-      <c r="O60" s="2" t="n"/>
-      <c r="P60" s="2" t="inlineStr">
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>1. Students will master the fundamentals of sound, acoustics, and electronics with an emphasis on developing the basic knowledge and skills to create original sounds via audio synthesis.
 2. Reflect upon and analyze everyday sonic experiences and articulate them to others.
@@ -6648,87 +5268,87 @@
 4. Identify suitable synthesis techniques to develop a design strategy for a specific sound design problem.</t>
         </is>
       </c>
-      <c r="Q60" s="2" t="n"/>
-      <c r="R60" s="2" t="inlineStr">
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="S60" s="2" t="n"/>
-      <c r="T60" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
+      <c r="T44" s="2" t="n"/>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>MUS 490</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Independent Study</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Music: Undergraduate Research</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>1–3</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Independent study (research or project) under the supervision a department faculty member.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Department consent and minimum 2.0 GPA.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="n"/>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>May be repeated for credit, with department consent, for a total of 6 units.</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice).</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>Fall &amp; Spring</t>
         </is>
       </c>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>No more than 6 units of independent study may count towards electives units within the major.</t>
         </is>
       </c>
-      <c r="O61" s="2" t="n"/>
-      <c r="P61" s="2" t="n"/>
-      <c r="Q61" s="2" t="n"/>
-      <c r="R61" s="2" t="inlineStr">
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="n"/>
+      <c r="Q45" s="2" t="n"/>
+      <c r="R45" s="2" t="inlineStr">
         <is>
           <t>2023-09-14</t>
         </is>
       </c>
-      <c r="S61" s="3" t="inlineStr">
+      <c r="S45" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6749,7 +5369,7 @@
           </r>
         </is>
       </c>
-      <c r="T61" s="3" t="inlineStr">
+      <c r="T45" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6771,284 +5391,79 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>MUS 495</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Music Education Practicum</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>C04 1u + C08</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Practicum experience in K-12 public school class and rehearsal settings, involving observation and teaching under the supervision of music faculty. Focus on practical skills. Regularly scheduled seminars. Field trips required.</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Department consent.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="n"/>
-      <c r="I62" s="2" t="n"/>
-      <c r="J62" s="2" t="n"/>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>A-F grading only.</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
+    <row r="46" ht="409.6" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>MUS 498</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Music: Undergraduate Research</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>C78 1u</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Formal work opportunities integrating the academic program with their career aspirations. Integral hands-on experience enhancing education and preparing for professional and personal success.</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Department consent and minimum 2.0 GPA.</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>NURS</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>May be repeated with department consent for a maximum of 6 units.</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>CR/NC grading only.</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>Only open for credit to music education majors participating in the music single subject matter</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="n"/>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>1. Observe outstanding music teachers in authentic K-12 school based classroom and rehearsal settings.
-2. Observe a variety of age levels and disciplines.
-3. Experience periodic, supervised teaching experiences.
-4. Participate in regular seminars.
-5. Relate experiences to current, relevant issues, such as cultural and other forms of diversity, significant national and global events, etc</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="n"/>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>2016-05-13</t>
-        </is>
-      </c>
-      <c r="S62" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">units publish as 1 where the record holds 2
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set units to 1</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-last revised 2016-05-13, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
-          </r>
-        </is>
-      </c>
-      <c r="T62" s="2" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>MUS 497</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Contemporary Issues in Music Education</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Music: Music Education</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>C05 3u</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Examination, discussion, and analysis of topics of consequence related to contemporary music teaching and learning.</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>May be repeated for credit for a maximum of 6 units.</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>A-F grading only.</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="n"/>
-      <c r="N63" s="2" t="n"/>
-      <c r="O63" s="2" t="n"/>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>1. Examine, discuss, and analyze topics of consequence in contemporary music education.
-2. Present original views and conclusions related to contemporary music education.
-3. Relate contemporary events to prior events/developments in the field music education.
-4. Relate current issues to their implementation in contemporary school-based music education.</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="n"/>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>2016-05-01</t>
-        </is>
-      </c>
-      <c r="S63" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-05-01, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
-          </r>
-        </is>
-      </c>
-      <c r="T63" s="2" t="n"/>
-    </row>
-    <row r="64" ht="409.6" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>MUS 498</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Music: Undergraduate Research</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>1–3</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>C78 1u</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>Formal work opportunities integrating the academic program with their career aspirations. Integral hands-on experience enhancing education and preparing for professional and personal success.</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>Department consent and minimum 2.0 GPA.</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>NURS</t>
-        </is>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>May be repeated with department consent for a maximum of 6 units.</t>
-        </is>
-      </c>
-      <c r="K64" s="4" t="inlineStr">
-        <is>
-          <t>CR/NC grading only.</t>
-        </is>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M64" s="4" t="inlineStr">
+      <c r="M46" s="4" t="inlineStr">
         <is>
           <t>Fall &amp; Spring</t>
         </is>
       </c>
-      <c r="N64" s="4" t="inlineStr">
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>Units may not be used towards the Music major or Minor.</t>
         </is>
       </c>
-      <c r="O64" s="4" t="n"/>
-      <c r="P64" s="4" t="inlineStr">
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4" t="inlineStr">
         <is>
           <t>1. Analyze connections and distinctions between individual health, public health, collective health, population health, and how these connect people, place, and health
 2. Contrast mechanisms for change within governmental institutions, non-profit organizations, grassroots organizations, and social movements
@@ -7113,7 +5528,7 @@
 61. Demonstrate how the perspectives of the arts or humanities are used by informed, engaged, and reflective citizens to benefit local and global communities.</t>
         </is>
       </c>
-      <c r="Q64" s="4" t="inlineStr">
+      <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>- Upon successful completion of this course students will be able to:
 Describe concepts of community engagement and culturally relevant community-based healthcare.
@@ -7267,12 +5682,12 @@
 Develop communication techniques for optimal interdisciplinary team co</t>
         </is>
       </c>
-      <c r="R64" s="4" t="inlineStr">
+      <c r="R46" s="4" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="S64" s="5" t="inlineStr">
+      <c r="S46" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7311,65 +5726,65 @@
           </r>
         </is>
       </c>
-      <c r="T64" s="4" t="n"/>
+      <c r="T46" s="4" t="n"/>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>MUS 600</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Seminar in Research Methodology</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Tools and resources available to conduct research in music. Organize and undertake a thesis-directed research project investigating important and relevant questions in music, and communicate findings in an academic manner. Required for Advancement to Candidacy.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Post-baccalaureate standing.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="n"/>
-      <c r="I65" s="2" t="n"/>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>May be repeated for credit for a maximum of 6 units.</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M65" s="2" t="n"/>
-      <c r="N65" s="2" t="n"/>
-      <c r="O65" s="2" t="n"/>
-      <c r="P65" s="2" t="inlineStr">
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
+      <c r="P47" s="2" t="inlineStr">
         <is>
           <t>1. Actively participate in seminar discussions focused on important and relevant issues in the analysis of music.
 2. Develop a thesis-based research project that addresses complex and challenging questions related to music through the application of critical thinking, analytical reasoning, and research methodology.
@@ -7378,13 +5793,13 @@
 5. Work cooperatively and respectfully with classmates on classroom, research, and presentation projects.</t>
         </is>
       </c>
-      <c r="Q65" s="2" t="n"/>
-      <c r="R65" s="2" t="inlineStr">
+      <c r="Q47" s="2" t="n"/>
+      <c r="R47" s="2" t="inlineStr">
         <is>
           <t>2016-02-05</t>
         </is>
       </c>
-      <c r="S65" s="3" t="inlineStr">
+      <c r="S47" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7405,61 +5820,61 @@
           </r>
         </is>
       </c>
-      <c r="T65" s="2" t="n"/>
+      <c r="T47" s="2" t="n"/>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>MUS 601</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Analysis of Musical Styles: Birth and Death of Tonality</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>C05 2u</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Examine the evolution of tonality from the Renaissance to Romantic eras. Develop research proficiency and analytical skills through comparative analysis of selected works. Explore the rich history of music styles and their impact.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n"/>
-      <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="n"/>
-      <c r="J66" s="2" t="n"/>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>On-ground or Online-Synchronous.</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>Fall Alternate Years</t>
         </is>
       </c>
-      <c r="N66" s="2" t="n"/>
-      <c r="O66" s="2" t="n"/>
-      <c r="P66" s="2" t="inlineStr">
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>1. demonstrate proficiency in musicological research methodologies, including the ability to critically evaluate scholarly sources, formulate research questions, and utilize appropriate bibliographic tools.
 2. develop effective communication skills through written analysis. They will be able to articulate complex musical concepts, tonal structures, and historical contexts coherently and concisely in a scholarly format adhering to proper citation styles.
@@ -7467,68 +5882,68 @@
 4. develop critical thinking skills in interpreting and evaluating musical works. They will demonstrate the ability to connect historical and theoretical knowledge to their analyses, offering insightful perspectives on the birth and death of tonality within the broader context of music history.</t>
         </is>
       </c>
-      <c r="Q66" s="2" t="n"/>
-      <c r="R66" s="2" t="inlineStr">
+      <c r="Q48" s="2" t="n"/>
+      <c r="R48" s="2" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="S66" s="2" t="n"/>
-      <c r="T66" s="2" t="n"/>
+      <c r="S48" s="2" t="n"/>
+      <c r="T48" s="2" t="n"/>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>MUS 602</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Analysis of Musical Styles: Post-Tonality and Beyond</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>C05 2u</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Embark on a research and analytical seminar exploring music from the turn-of-the-century to World War II. Investigate diverse musical landscapes, honing critical analysis and research skills within an evolving theoretical framework.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n"/>
-      <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="n"/>
-      <c r="J67" s="2" t="n"/>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>On-ground or Online-Synchronous.</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>Fall Alternate Years</t>
         </is>
       </c>
-      <c r="N67" s="2" t="n"/>
-      <c r="O67" s="2" t="n"/>
-      <c r="P67" s="2" t="inlineStr">
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
+      <c r="P49" s="2" t="inlineStr">
         <is>
           <t>1. develop advanced analytical skills, demonstrating a nuanced understanding of music from the 20th Century through the examination of diverse compositions and styles.
 2. engage in comprehensive research methodologies, acquiring the ability to investigate and analyze various musical topics, apply theoretical frameworks, and present findings in structured research papers.
@@ -7536,68 +5951,68 @@
 4. enhance communication skills through the synthesis and presentation of research findings, fostering effective expression and engagement within a scholarly community.</t>
         </is>
       </c>
-      <c r="Q67" s="2" t="n"/>
-      <c r="R67" s="2" t="inlineStr">
+      <c r="Q49" s="2" t="n"/>
+      <c r="R49" s="2" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="S67" s="2" t="n"/>
-      <c r="T67" s="2" t="n"/>
+      <c r="S49" s="2" t="n"/>
+      <c r="T49" s="2" t="n"/>
     </row>
-    <row r="68" ht="182" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="50" ht="182" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>MUS 603</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Entrepreneurship in the Arts</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>C05 3u</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>Graduate-level course explores entrepreneurship in the arts and music industry. Analyze power dynamics, business aspects, and craft personal branding. Develop a comprehensive marketing plan, reflecting on arts’ broader societal impact.</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n"/>
-      <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="n"/>
-      <c r="J68" s="4" t="n"/>
-      <c r="K68" s="4" t="inlineStr">
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L68" s="4" t="inlineStr">
+      <c r="L50" s="4" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M68" s="4" t="inlineStr">
+      <c r="M50" s="4" t="inlineStr">
         <is>
           <t>Fall Alternate Years</t>
         </is>
       </c>
-      <c r="N68" s="4" t="n"/>
-      <c r="O68" s="4" t="n"/>
-      <c r="P68" s="4" t="inlineStr">
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
+      <c r="P50" s="4" t="inlineStr">
         <is>
           <t>1. Analyze the impact of power and social identity on career options in various arts disciplines.
 2. Navigate the logistical and business aspects of arts industries, drawing inspiration from historical and contemporary perspectives.
@@ -7606,68 +6021,68 @@
 5. Demonstrate an understanding of the societal impact of arts and humanities perspectives, using this knowledge for the benefit of local and global communities.</t>
         </is>
       </c>
-      <c r="Q68" s="4" t="n"/>
-      <c r="R68" s="4" t="inlineStr">
+      <c r="Q50" s="4" t="n"/>
+      <c r="R50" s="4" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="S68" s="4" t="n"/>
-      <c r="T68" s="4" t="n"/>
+      <c r="S50" s="4" t="n"/>
+      <c r="T50" s="4" t="n"/>
     </row>
-    <row r="69" ht="210" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="51" ht="210" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>MUS 604</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Sounding Justice: Unveiling the Ecological and Social Dimensions of</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>C05 2u</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>Explore the transformative nexus of music, environment, and social justice in “Sounding Justice.” Dive into critical analyses, ethical reflections, and applied projects to harness the power of music for positive change.</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n"/>
-      <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="n"/>
-      <c r="J69" s="4" t="n"/>
-      <c r="K69" s="4" t="inlineStr">
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L69" s="4" t="inlineStr">
+      <c r="L51" s="4" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M69" s="4" t="inlineStr">
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>Spring Alternate Years</t>
         </is>
       </c>
-      <c r="N69" s="4" t="n"/>
-      <c r="O69" s="4" t="n"/>
-      <c r="P69" s="4" t="inlineStr">
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
+      <c r="P51" s="4" t="inlineStr">
         <is>
           <t>1. Demonstrate a comprehensive understanding of the intricate relationships between music, the environment, and social justice.
 2. Develop critical analytical skills to assess the impact of music on environmental sustainability and its role in advocating for social change.
@@ -7676,68 +6091,68 @@
 5. Enhance communication proficiency in articulating the relationships between music, the environment, and social justice, both in written and oral formats.</t>
         </is>
       </c>
-      <c r="Q69" s="4" t="n"/>
-      <c r="R69" s="4" t="inlineStr">
+      <c r="Q51" s="4" t="n"/>
+      <c r="R51" s="4" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="S69" s="4" t="n"/>
-      <c r="T69" s="4" t="n"/>
+      <c r="S51" s="4" t="n"/>
+      <c r="T51" s="4" t="n"/>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>MUS 605</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>History and Theory of Jazz</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>C05 2u</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>This graduate seminar offers an in-depth exploration of jazz, unraveling its historical narratives and theoretical underpinnings. Dive into the evolution of jazz, dissecting key movements, influential figures, and the cultural forces that have shaped this dynamic and enduring genre.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="n"/>
-      <c r="I70" s="2" t="n"/>
-      <c r="J70" s="2" t="n"/>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>Spring Alternate Years</t>
         </is>
       </c>
-      <c r="N70" s="2" t="n"/>
-      <c r="O70" s="2" t="n"/>
-      <c r="P70" s="2" t="inlineStr">
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>1. Evaluate the historical development of jazz, recognizing key movements, styles, and influential figures.
 2. Analyze the theoretical frameworks underpinning jazz, including harmonic structures, improvisation techniques, and stylistic nuances.
@@ -7746,68 +6161,68 @@
 5. Synthesize knowledge through research projects, presentations, and discussions, demonstrating a comprehensive understanding of jazz history and theory.</t>
         </is>
       </c>
-      <c r="Q70" s="2" t="n"/>
-      <c r="R70" s="2" t="inlineStr">
+      <c r="Q52" s="2" t="n"/>
+      <c r="R52" s="2" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="S70" s="2" t="n"/>
-      <c r="T70" s="2" t="n"/>
+      <c r="S52" s="2" t="n"/>
+      <c r="T52" s="2" t="n"/>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>MUS 606</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Interdisciplinary Collaboration in Music</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>C05 1u + C10 1u</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Explore the dynamic fusion of music with diverse arts in “Interdisciplinary Collaboration in Music Performance.” Composers, conductors, and performers engage in collaborative projects, adapting traditional practices for innovative, multidimensional performances. Thrive in the evolving landscape of interdisciplinary arts.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n"/>
-      <c r="H71" s="2" t="n"/>
-      <c r="I71" s="2" t="n"/>
-      <c r="J71" s="2" t="n"/>
-      <c r="K71" s="2" t="inlineStr">
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L71" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr">
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>Fall Alternate Years</t>
         </is>
       </c>
-      <c r="N71" s="2" t="n"/>
-      <c r="O71" s="2" t="n"/>
-      <c r="P71" s="2" t="inlineStr">
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="2" t="n"/>
+      <c r="P53" s="2" t="inlineStr">
         <is>
           <t>1. Create original compositions that seamlessly integrate music with diverse artistic disciplines, demonstrating a mastery of collaborative composition techniques and fostering interdisciplinary creativity.
 2. Refine their skills in leading ensembles that incorporate unconventional staging, multimedia elements, and collaborative artistic elements, showcasing adaptability and effective leadership in interdisciplinary settings.
@@ -7816,68 +6231,68 @@
 5. Gain an understanding of career opportunities and challenges in interdisciplinary arts, developing the skills necessary to navigate and contribute to the evolving landscape of collaborative projects beyond academic contexts.</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="n"/>
-      <c r="R71" s="2" t="inlineStr">
+      <c r="Q53" s="2" t="n"/>
+      <c r="R53" s="2" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="S71" s="2" t="n"/>
-      <c r="T71" s="2" t="n"/>
+      <c r="S53" s="2" t="n"/>
+      <c r="T53" s="2" t="n"/>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>MUS 610</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Seminar in Music of the 20th (post-1945) &amp; 21st Centuries</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>C05 3u</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Musical styles, forms and performance practice from 1945 to the present, with detailed analyses of representative works and close reading of historical writings.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="n"/>
-      <c r="H72" s="2" t="n"/>
-      <c r="I72" s="2" t="n"/>
-      <c r="J72" s="2" t="n"/>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>Spring Alternate Years</t>
         </is>
       </c>
-      <c r="N72" s="2" t="n"/>
-      <c r="O72" s="2" t="n"/>
-      <c r="P72" s="2" t="inlineStr">
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>1. Actively participate in seminar discussions focused on important and relevant issues in the analysis of music.
 2. Address complex and challenging questions related to music theory and musical analysis through the application of critical thinking, analytical reasoning, and research methodology.
@@ -7885,81 +6300,81 @@
 4. Work cooperatively and respectfully with classmates on classroom, research, and presentation projects.</t>
         </is>
       </c>
-      <c r="Q72" s="2" t="n"/>
-      <c r="R72" s="2" t="inlineStr">
+      <c r="Q54" s="2" t="n"/>
+      <c r="R54" s="2" t="inlineStr">
         <is>
           <t>2021-09-22</t>
         </is>
       </c>
-      <c r="S72" s="2" t="n"/>
-      <c r="T72" s="2" t="n"/>
+      <c r="S54" s="2" t="n"/>
+      <c r="T54" s="2" t="n"/>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>MUS 622</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Seminar in Asian Music and Culture</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Music and culture of selected parts of Asia and the Asian diaspora. Issues of identity, politics, modernization, and globalization will be studied from an ethnomusicological perspective.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>M.A. Music major.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="n"/>
-      <c r="I73" s="2" t="n"/>
-      <c r="J73" s="2" t="n"/>
-      <c r="K73" s="2" t="inlineStr">
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M73" s="2" t="n"/>
-      <c r="N73" s="2" t="n"/>
-      <c r="O73" s="2" t="n"/>
-      <c r="P73" s="2" t="inlineStr">
+      <c r="M55" s="2" t="n"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
+      <c r="P55" s="2" t="inlineStr">
         <is>
           <t>1. To learn to understand and appreciate selected music of Asia from an ethnomusicological perspective, that is, as developing through the unique conditions of the historical and cultural processes that gave rise to them.
 2. To understand how these musical traditions continuously develop and transform in a contemporary world defined by large-scale processes such as globalization, mass mediation, and electronic communications.
 3. Through the application of critical and creative thinking, communicate your understanding of how music in the culture you select answers or fulfills a particular problem or need.</t>
         </is>
       </c>
-      <c r="Q73" s="2" t="n"/>
-      <c r="R73" s="2" t="inlineStr">
+      <c r="Q55" s="2" t="n"/>
+      <c r="R55" s="2" t="inlineStr">
         <is>
           <t>2016-02-24</t>
         </is>
       </c>
-      <c r="S73" s="3" t="inlineStr">
+      <c r="S55" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7980,69 +6395,69 @@
           </r>
         </is>
       </c>
-      <c r="T73" s="2" t="n"/>
+      <c r="T55" s="2" t="n"/>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>MUS 630</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Advanced Conducting</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>C05 1u + C10 1u</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Ensemble conducting techniques including stylistic, pedagogical, and physical studies in gesture. Score analysis and ear training through the study of music from all genres and historical periods. Advanced rehearsal techniques and program building, including the development of ensemble.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Student enrolled in the M.A. in Music or MUS 441 or Instructor Permission</t>
         </is>
       </c>
-      <c r="H74" s="2" t="n"/>
-      <c r="I74" s="2" t="n"/>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>May be repeated for credit for a maximum of 4 units.</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>Fall Alternate Years</t>
         </is>
       </c>
-      <c r="N74" s="2" t="n"/>
-      <c r="O74" s="2" t="n"/>
-      <c r="P74" s="2" t="inlineStr">
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
+      <c r="P56" s="2" t="inlineStr">
         <is>
           <t>1. Read at sight with fluency, demonstrate keyboard competency, and sing in tune (alone and with others).
 2. Demonstrate the knowledge and sufficient skills to work as a leader and in collaboration on matters of musical interpretation.
@@ -8053,293 +6468,76 @@
 7. Solve problems using quality reference, research, and pedagogical materials including technology.</t>
         </is>
       </c>
-      <c r="Q74" s="2" t="n"/>
-      <c r="R74" s="2" t="inlineStr">
+      <c r="Q56" s="2" t="n"/>
+      <c r="R56" s="2" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="S74" s="2" t="n"/>
-      <c r="T74" s="2" t="n"/>
+      <c r="S56" s="2" t="n"/>
+      <c r="T56" s="2" t="n"/>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>MUS 631</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Teaching Music in Higher Education</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
+    <row r="57" ht="196" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>MUS 660A</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Graduate Vocal Coaching</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>C05 2u</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Preparation for careers in post-secondary education. Study of learning theories, curriculum development, assessment, and materials for teaching music in higher education.</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>M.A. Music major.</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="n"/>
-      <c r="I75" s="2" t="n"/>
-      <c r="J75" s="2" t="n"/>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>1–2</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>C36 1u</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Individual coaching in collaborative music making for music majors with Graduate-level performance ability. Coaching times arranged according to graduate degree recital expectations as outlined in the music major handbook.</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Department consent.</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>MUS 662.</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>May be repeated for credit for a maximum of 8 units.</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>On-ground or Hybrid.</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>Spring Alternate Years</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="n"/>
-      <c r="O75" s="2" t="n"/>
-      <c r="P75" s="2" t="inlineStr">
-        <is>
-          <t>1. Become familiar with a variety of teaching techniques/situations, such as lectures, small groups, individual lessons, and small/large ensemble rehearsals.
-2. Create curricular materials such as lesson/rehearsal plans and syllabi.
-3. Participate in peer teaching situations.
-4. Survey current resources/practices in higher education, i.e. textbooks, online/hybrid options, etc.
-5. Create a CV and participate in a mock job interview for a college/university position.</t>
-        </is>
-      </c>
-      <c r="Q75" s="2" t="n"/>
-      <c r="R75" s="2" t="inlineStr">
-        <is>
-          <t>2024-01-31</t>
-        </is>
-      </c>
-      <c r="S75" s="2" t="n"/>
-      <c r="T75" s="2" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>MUS 633</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Pedagogy of Music Theory</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Music: Graduate Studies</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>Materials, organization, techniques, and problems of the first two years of collegiate theory and musicianship teaching. Bibliographical survey of texts and materials, sample teaching, and observation of collegiate theory classes.</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Department consent.</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="n"/>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>Baccalaureate degree in music.</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="n"/>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>A-F grading only.</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="L57" s="4" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M76" s="2" t="n"/>
-      <c r="N76" s="2" t="n"/>
-      <c r="O76" s="2" t="n"/>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>1. Demonstrate familiarity with a variety of developmentally appropriate strategies for teaching collegiate music theory.
-2. Design instruction using a variety of modalities, accounting for learner differences.
-3. Demonstrate familiarity with and ability to evaluate curricular materials for music theory and musicianship (i.e. aural skills).
-4. Demonstrate familiarity with a variety of systems for rhythm (i.e Cheve, Gordon, takadimi), melody (solfegge), and overall approach (i.e. Kodaly).</t>
-        </is>
-      </c>
-      <c r="Q76" s="2" t="n"/>
-      <c r="R76" s="2" t="inlineStr">
-        <is>
-          <t>2019-02-15</t>
-        </is>
-      </c>
-      <c r="S76" s="3" t="n"/>
-      <c r="T76" s="2" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>MUS 638</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>History and Philosophy of Music Education</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Music: Graduate Studies</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>blank</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Study of historical and philosophical trends in music education, with an emphasis on their application to current practices, scholarship, and policy in music teaching and learning.</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Department consent.</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="n"/>
-      <c r="I77" s="2" t="n"/>
-      <c r="J77" s="2" t="n"/>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>A-F grading only.</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="n"/>
-      <c r="N77" s="2" t="n"/>
-      <c r="O77" s="2" t="n"/>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>1. Read complex texts, create original arguments, analyze the arguments of others, and express these criticisms orally and in writing.
-2. Demonstrate knowledge of major philosophers in music and music education, their relevant concepts, theories, methods, and historical contexts.
-3. Relate significant significant topic in the history and philosophy of music education to current events in K-12 music education.
-4. Demonstrate knowledge of major historical movements and events in music education and relate them to modern movements and events in music education.
-5. Cultivate an appreciation for a diversity of ideas and values across time and for human difference in areas such as: religion, culture, ethnicity, race, class, sexuality, and gender.</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="n"/>
-      <c r="R77" s="2" t="inlineStr">
-        <is>
-          <t>2019-02-15</t>
-        </is>
-      </c>
-      <c r="S77" s="3" t="n"/>
-      <c r="T77" s="2" t="n"/>
-    </row>
-    <row r="78" ht="196" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>MUS 660A</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Graduate Vocal Coaching</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>Music: Graduate Studies</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>1–2</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>C36 1u</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>Individual coaching in collaborative music making for music majors with Graduate-level performance ability. Coaching times arranged according to graduate degree recital expectations as outlined in the music major handbook.</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>Department consent.</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>MUS 662.</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="n"/>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>May be repeated for credit for a maximum of 8 units.</t>
-        </is>
-      </c>
-      <c r="K78" s="4" t="inlineStr">
-        <is>
-          <t>A-F grading only.</t>
-        </is>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M78" s="4" t="n"/>
-      <c r="N78" s="4" t="n"/>
-      <c r="O78" s="4" t="n"/>
-      <c r="P78" s="4" t="inlineStr">
+      <c r="M57" s="4" t="n"/>
+      <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="n"/>
+      <c r="P57" s="4" t="inlineStr">
         <is>
           <t>1. To develop the musical skills required to collaborate effectively with an accompanist, including but not limited to identifying and articulating musical ideas and understanding their relationship to the text, and listening to the musical elements of the accompaniment part and responding to them flexibly and musically.
 2. To develop language skills related to singing, including but not limited to diction, translation, poetic delivery and interpretation, and character development.
@@ -8347,13 +6545,13 @@
 4. To develop and improve performance skills to a level consistent with the student’s degree level.</t>
         </is>
       </c>
-      <c r="Q78" s="4" t="n"/>
-      <c r="R78" s="4" t="inlineStr">
+      <c r="Q57" s="4" t="n"/>
+      <c r="R57" s="4" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="S78" s="5" t="inlineStr">
+      <c r="S57" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8374,82 +6572,82 @@
           </r>
         </is>
       </c>
-      <c r="T78" s="4" t="n"/>
+      <c r="T57" s="4" t="n"/>
     </row>
-    <row r="79" ht="140" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
+    <row r="58" ht="140" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>MUS 660B</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Graduate Instrumental Coaching</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>1–2</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>C36 1u</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>Individual coaching in collaborative music making for music majors with Graduate-level performance ability. Coaching times are arranged according to graduate degree recital expectations as outlined in the music major handbook.</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>Department consent.</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>Minimum of one course from: MUS 661, MUS 661A, MUS 663 - MUS 669.</t>
         </is>
       </c>
-      <c r="I79" s="4" t="n"/>
-      <c r="J79" s="4" t="inlineStr">
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="4" t="inlineStr">
         <is>
           <t>May be repeated for credit for a maximum of 8 units.</t>
         </is>
       </c>
-      <c r="K79" s="4" t="inlineStr">
+      <c r="K58" s="4" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L79" s="4" t="inlineStr">
+      <c r="L58" s="4" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M79" s="4" t="n"/>
-      <c r="N79" s="4" t="n"/>
-      <c r="O79" s="4" t="n"/>
-      <c r="P79" s="4" t="inlineStr">
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4" t="n"/>
+      <c r="O58" s="4" t="n"/>
+      <c r="P58" s="4" t="inlineStr">
         <is>
           <t>1. To develop the musical skills required to collaborate effectively with an accompanist, including but not limited to identifying and articulating musical ideas, and listening to the musical elements of the accompaniment part and responding to them flexibly and musically.
 2. To develop an understanding of musical styles, interpretation, and performance practice to a level consistent with the student’s degree level.
 3. To develop and improve performance skills to a level consistent with the student’s degree level.</t>
         </is>
       </c>
-      <c r="Q79" s="4" t="n"/>
-      <c r="R79" s="4" t="inlineStr">
+      <c r="Q58" s="4" t="n"/>
+      <c r="R58" s="4" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="S79" s="5" t="inlineStr">
+      <c r="S58" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8488,197 +6686,69 @@
           </r>
         </is>
       </c>
-      <c r="T79" s="4" t="n"/>
+      <c r="T58" s="4" t="n"/>
     </row>
-    <row r="80" ht="70" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>MUS 671</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Kodály Pedagogy</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
+    <row r="59" ht="140" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>MUS 676</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to Orff Schulwerk</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>C10 1u</t>
         </is>
       </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>An introduction to the philosophy and practice of the Kodály-based curriculum of music teaching and learning. Curriculum development, teaching techniques, lesson planning and supportive song literature including singing games and dances.</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="n"/>
-      <c r="H80" s="7" t="n"/>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Baccalaureate degree in music; School teaching experience in music</t>
-        </is>
-      </c>
-      <c r="J80" s="7" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>Exploration of the Orff Schulwerk approach to music education. Focus on elementary music, improvisation, movement, and instruments. Includes curriculum development, lesson design, teaching methods, and supportive song, speech, and dance literature.</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="6" t="n"/>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>Baccalaureate degree in music; 1+ years of K-12 music teaching experience</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
         <is>
           <t>Repeatable for credit up to 4 units.</t>
         </is>
       </c>
-      <c r="K80" s="7" t="inlineStr">
+      <c r="K59" s="6" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice)</t>
         </is>
       </c>
-      <c r="L80" s="7" t="inlineStr">
+      <c r="L59" s="6" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M80" s="7" t="inlineStr">
-        <is>
-          <t>Variable Intermittently</t>
-        </is>
-      </c>
-      <c r="N80" s="7" t="n"/>
-      <c r="O80" s="7" t="n"/>
-      <c r="P80" s="7" t="n"/>
-      <c r="Q80" s="7" t="n"/>
-      <c r="R80" s="7" t="inlineStr">
-        <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="S80" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no learning outcomes published
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>add learning outcomes</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-repeatability uses non-standard phrasing
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reword to may be repeated for credit for a maximum of 4 units</t>
-          </r>
-        </is>
-      </c>
-      <c r="T80" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no outcomes published
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>to be drafted by area faculty</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="140" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>MUS 676</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Introduction to Orff Schulwerk</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>Music: Graduate Studies</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>C10 1u</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>Exploration of the Orff Schulwerk approach to music education. Focus on elementary music, improvisation, movement, and instruments. Includes curriculum development, lesson design, teaching methods, and supportive song, speech, and dance literature.</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="n"/>
-      <c r="H81" s="7" t="n"/>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Baccalaureate degree in music; 1+ years of K-12 music teaching experience</t>
-        </is>
-      </c>
-      <c r="J81" s="7" t="inlineStr">
-        <is>
-          <t>Repeatable for credit up to 4 units.</t>
-        </is>
-      </c>
-      <c r="K81" s="7" t="inlineStr">
-        <is>
-          <t>A-F or CR/NC (student choice)</t>
-        </is>
-      </c>
-      <c r="L81" s="7" t="inlineStr">
-        <is>
-          <t>On-ground.</t>
-        </is>
-      </c>
-      <c r="M81" s="7" t="inlineStr">
+      <c r="M59" s="6" t="inlineStr">
         <is>
           <t>Summer ONLY</t>
         </is>
       </c>
-      <c r="N81" s="7" t="n"/>
-      <c r="O81" s="7" t="n"/>
-      <c r="P81" s="7" t="inlineStr">
+      <c r="N59" s="6" t="n"/>
+      <c r="O59" s="6" t="n"/>
+      <c r="P59" s="6" t="inlineStr">
         <is>
           <t>1. Explain the core principles of Orff Schulwerk in music teaching and learning.
 2. Demonstrate musicianship through singing, movement, percussion, and improvisation.
@@ -8687,13 +6757,13 @@
 5. Lead inclusive classroom activities that support diverse learners.</t>
         </is>
       </c>
-      <c r="Q81" s="7" t="n"/>
-      <c r="R81" s="7" t="inlineStr">
+      <c r="Q59" s="6" t="n"/>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="S81" s="8" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8714,76 +6784,76 @@
           </r>
         </is>
       </c>
-      <c r="T81" s="7" t="n"/>
+      <c r="T59" s="6" t="n"/>
     </row>
-    <row r="82" ht="70" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
+    <row r="60" ht="70" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>MUS 678</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Introduction to Dalcroze Eurythmics</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>C10 1u</t>
         </is>
       </c>
-      <c r="F82" s="7" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <t>Study of Dalcroze Eurythmics approach. Emphasis on embodied rhythm, improvisation, solfège, and active listening. Includes curriculum planning, pedagogical methods, and movement-based strategies for developing musicianship and creative teaching.</t>
         </is>
       </c>
-      <c r="G82" s="7" t="n"/>
-      <c r="H82" s="7" t="n"/>
-      <c r="I82" s="7" t="inlineStr">
+      <c r="G60" s="6" t="n"/>
+      <c r="H60" s="6" t="n"/>
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>Baccalaureate degree in music; 1+ years of K-12 school music experience</t>
         </is>
       </c>
-      <c r="J82" s="7" t="inlineStr">
+      <c r="J60" s="6" t="inlineStr">
         <is>
           <t>Repeatable for credit up to 4 units.</t>
         </is>
       </c>
-      <c r="K82" s="7" t="inlineStr">
+      <c r="K60" s="6" t="inlineStr">
         <is>
           <t>A-F or CR/NC (student choice)</t>
         </is>
       </c>
-      <c r="L82" s="7" t="inlineStr">
+      <c r="L60" s="6" t="inlineStr">
         <is>
           <t>On-ground</t>
         </is>
       </c>
-      <c r="M82" s="7" t="inlineStr">
+      <c r="M60" s="6" t="inlineStr">
         <is>
           <t>Summer ONLY</t>
         </is>
       </c>
-      <c r="N82" s="7" t="n"/>
-      <c r="O82" s="7" t="n"/>
-      <c r="P82" s="7" t="n"/>
-      <c r="Q82" s="7" t="n"/>
-      <c r="R82" s="7" t="inlineStr">
+      <c r="N60" s="6" t="n"/>
+      <c r="O60" s="6" t="n"/>
+      <c r="P60" s="6" t="n"/>
+      <c r="Q60" s="6" t="n"/>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="S82" s="8" t="inlineStr">
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8822,7 +6892,7 @@
           </r>
         </is>
       </c>
-      <c r="T82" s="8" t="inlineStr">
+      <c r="T60" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8844,70 +6914,70 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="112" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
+    <row r="61" ht="112" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>MUS 690</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Independent Study</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>1–3</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Selected research topics agreed on between the student and the faculty supervising the course. A plan of work completion must be approved prior to proceeding with the project.</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>Department consent and minimum 3.0 GPA.</t>
         </is>
       </c>
-      <c r="H83" s="4" t="n"/>
-      <c r="I83" s="4" t="n"/>
-      <c r="J83" s="4" t="inlineStr">
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>May be repeated for credit with consent of instructor, for a maximum of 3 units.</t>
         </is>
       </c>
-      <c r="K83" s="4" t="inlineStr">
+      <c r="K61" s="4" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L83" s="4" t="inlineStr">
+      <c r="L61" s="4" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M83" s="4" t="n"/>
-      <c r="N83" s="4" t="n"/>
-      <c r="O83" s="4" t="n"/>
-      <c r="P83" s="4" t="n"/>
-      <c r="Q83" s="4" t="n"/>
-      <c r="R83" s="4" t="inlineStr">
+      <c r="M61" s="4" t="n"/>
+      <c r="N61" s="4" t="n"/>
+      <c r="O61" s="4" t="n"/>
+      <c r="P61" s="4" t="n"/>
+      <c r="Q61" s="4" t="n"/>
+      <c r="R61" s="4" t="inlineStr">
         <is>
           <t>2016-02-26</t>
         </is>
       </c>
-      <c r="S83" s="5" t="inlineStr">
+      <c r="S61" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8946,7 +7016,7 @@
           </r>
         </is>
       </c>
-      <c r="T83" s="5" t="inlineStr">
+      <c r="T61" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8968,76 +7038,76 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="112" customHeight="1">
-      <c r="A84" s="9" t="inlineStr">
+    <row r="62" ht="112" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>MUS 691</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>University Thesis</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>1–4</t>
         </is>
       </c>
-      <c r="E84" s="9" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="F84" s="9" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>Development and completion of a formal written thesis for submission to the university. Supervision by a departmental committee, at least one of whom must be a Cal State East Bay faculty member. Oral defense required. (See also “University Thesis Writing Guide,” www.csueastbay.edu/thesiswritingguide).</t>
         </is>
       </c>
-      <c r="G84" s="9" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>Department consent.</t>
         </is>
       </c>
-      <c r="H84" s="9" t="n"/>
-      <c r="I84" s="9" t="n"/>
-      <c r="J84" s="9" t="inlineStr">
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="inlineStr">
         <is>
           <t>Course may be repeated for credit for a maximum of 4 units.</t>
         </is>
       </c>
-      <c r="K84" s="9" t="inlineStr">
+      <c r="K62" s="8" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L84" s="9" t="inlineStr">
+      <c r="L62" s="8" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M84" s="9" t="n"/>
-      <c r="N84" s="9" t="n"/>
-      <c r="O84" s="9" t="n"/>
-      <c r="P84" s="9" t="inlineStr">
+      <c r="M62" s="8" t="n"/>
+      <c r="N62" s="8" t="n"/>
+      <c r="O62" s="8" t="n"/>
+      <c r="P62" s="8" t="inlineStr">
         <is>
           <t>1. Plan and complete a formal written thesis that demonstrates mastery in the areas of composition, music theory, music history, or music education.
 2. Address significant and relevant issues through critical and creative thinking and analytical reasoning.
 3. Work collaboratively and respectfully with their thesis committee.</t>
         </is>
       </c>
-      <c r="Q84" s="9" t="n"/>
-      <c r="R84" s="9" t="inlineStr">
+      <c r="Q62" s="8" t="n"/>
+      <c r="R62" s="8" t="inlineStr">
         <is>
           <t>2016-02-26</t>
         </is>
       </c>
-      <c r="S84" s="10" t="inlineStr">
+      <c r="S62" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9076,7 +7146,7 @@
           </r>
         </is>
       </c>
-      <c r="T84" s="10" t="inlineStr">
+      <c r="T62" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9098,76 +7168,76 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="112" customHeight="1">
-      <c r="A85" s="9" t="inlineStr">
+    <row r="63" ht="112" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>MUS 692</t>
         </is>
       </c>
-      <c r="B85" s="9" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>Comprehensive Exam Review</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D85" s="9" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>1–6</t>
         </is>
       </c>
-      <c r="E85" s="9" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>C36 1-6u</t>
         </is>
       </c>
-      <c r="F85" s="9" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>Selected readings in consultation with two faculty members in preparation for the Master’s Comprehensive Examination in music. The selected readings and the exams must be consistent with the student’s areas of concentration and approved by the faculty mentors.</t>
         </is>
       </c>
-      <c r="G85" s="9" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>Department consent.</t>
         </is>
       </c>
-      <c r="H85" s="9" t="n"/>
-      <c r="I85" s="9" t="n"/>
-      <c r="J85" s="9" t="inlineStr">
+      <c r="H63" s="8" t="n"/>
+      <c r="I63" s="8" t="n"/>
+      <c r="J63" s="8" t="inlineStr">
         <is>
           <t>May be repeated for credit for a maximum of 6 units.</t>
         </is>
       </c>
-      <c r="K85" s="9" t="inlineStr">
+      <c r="K63" s="8" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L85" s="9" t="inlineStr">
+      <c r="L63" s="8" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M85" s="9" t="n"/>
-      <c r="N85" s="9" t="n"/>
-      <c r="O85" s="9" t="n"/>
-      <c r="P85" s="9" t="inlineStr">
+      <c r="M63" s="8" t="n"/>
+      <c r="N63" s="8" t="n"/>
+      <c r="O63" s="8" t="n"/>
+      <c r="P63" s="8" t="inlineStr">
         <is>
           <t>1. Students will demonstrate the ability to complete in-depth research into selected areas within their particular disciplines.
 2. Students will demonstrate knowledge of significant scholarship and/or creative output, consistent with standard graduate level expectations, in their respective disciplines.
 3. Students will demonstrate their mastery via both oral and written means, in the form of papers or other scholarly documents as well as with an oral examination / defense.</t>
         </is>
       </c>
-      <c r="Q85" s="9" t="n"/>
-      <c r="R85" s="9" t="inlineStr">
+      <c r="Q63" s="8" t="n"/>
+      <c r="R63" s="8" t="inlineStr">
         <is>
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="S85" s="10" t="inlineStr">
+      <c r="S63" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9188,78 +7258,78 @@
           </r>
         </is>
       </c>
-      <c r="T85" s="9" t="n"/>
+      <c r="T63" s="8" t="n"/>
     </row>
-    <row r="86" ht="98" customHeight="1">
-      <c r="A86" s="4" t="inlineStr">
+    <row r="64" ht="98" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>MUS 693</t>
         </is>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Graduate Music Capstone</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>C25 1u</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>Students receive individualized guidance in the preparation and completion of their final capstone project. Students will develop an approach, timeline, and realize this project at the level of artistry and professionalism required to succeed in their field.</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n"/>
-      <c r="H86" s="4" t="n"/>
-      <c r="I86" s="4" t="n"/>
-      <c r="J86" s="4" t="inlineStr">
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
+      <c r="I64" s="4" t="n"/>
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>May be repeated for credit for a maximum of 3 units.</t>
         </is>
       </c>
-      <c r="K86" s="4" t="inlineStr">
+      <c r="K64" s="4" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L86" s="4" t="inlineStr">
+      <c r="L64" s="4" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M86" s="4" t="inlineStr">
+      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>Fall &amp; Spring</t>
         </is>
       </c>
-      <c r="N86" s="4" t="n"/>
-      <c r="O86" s="4" t="n"/>
-      <c r="P86" s="4" t="inlineStr">
+      <c r="N64" s="4" t="n"/>
+      <c r="O64" s="4" t="n"/>
+      <c r="P64" s="4" t="inlineStr">
         <is>
           <t>1. Strategize and execute a sophisticated project showcasing your expertise in your chosen area of emphasis.
 2. Tackle substantial and pertinent challenges using a combination of critical thinking, creative problem-solving, and analytical reasoning.
 3. Engage in collaborative efforts with a focus on fostering respect and effective teamwork.</t>
         </is>
       </c>
-      <c r="Q86" s="4" t="n"/>
-      <c r="R86" s="4" t="inlineStr">
+      <c r="Q64" s="4" t="n"/>
+      <c r="R64" s="4" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="S86" s="4" t="inlineStr">
+      <c r="S64" s="4" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9280,78 +7350,78 @@
           </r>
         </is>
       </c>
-      <c r="T86" s="4" t="n"/>
+      <c r="T64" s="4" t="n"/>
     </row>
-    <row r="87" ht="84" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
+    <row r="65" ht="84" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>MUS 697</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Issues in Music</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>Graduate seminar focused on readings, discussion, and research on significant issues in music.</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>Department consent.</t>
         </is>
       </c>
-      <c r="H87" s="7" t="n"/>
-      <c r="I87" s="7" t="n"/>
-      <c r="J87" s="7" t="inlineStr">
+      <c r="H65" s="6" t="n"/>
+      <c r="I65" s="6" t="n"/>
+      <c r="J65" s="6" t="inlineStr">
         <is>
           <t>May repeat once for credit for a maximum of 6 units when topic varies.</t>
         </is>
       </c>
-      <c r="K87" s="7" t="inlineStr">
+      <c r="K65" s="6" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L87" s="7" t="inlineStr">
+      <c r="L65" s="6" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M87" s="7" t="n"/>
-      <c r="N87" s="7" t="n"/>
-      <c r="O87" s="7" t="n"/>
-      <c r="P87" s="7" t="inlineStr">
+      <c r="M65" s="6" t="n"/>
+      <c r="N65" s="6" t="n"/>
+      <c r="O65" s="6" t="n"/>
+      <c r="P65" s="6" t="inlineStr">
         <is>
           <t>1. Address significant and relevant issues in music through critical and creative thinking and analytical reasoning.
 2. Clearly and persuasively communicate one’s findings to others.
 3. Work collaboratively and respectfully with classmates and instructors in, and outside of, the classroom.</t>
         </is>
       </c>
-      <c r="Q87" s="7" t="n"/>
-      <c r="R87" s="7" t="inlineStr">
+      <c r="Q65" s="6" t="n"/>
+      <c r="R65" s="6" t="inlineStr">
         <is>
           <t>2016-02-26</t>
         </is>
       </c>
-      <c r="S87" s="8" t="inlineStr">
+      <c r="S65" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9372,72 +7442,72 @@
           </r>
         </is>
       </c>
-      <c r="T87" s="7" t="n"/>
+      <c r="T65" s="6" t="n"/>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>MUS 698</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>1–3</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Formal advanced work opportunities integrating the academic program with their career aspirations. Integral advanced hands-on experience enhancing education and preparing for professional and personal success.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>Department consent and minimum 2.0 GPA.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="n"/>
-      <c r="I88" s="2" t="n"/>
-      <c r="J88" s="2" t="inlineStr">
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>May be repeated with department consent for a maximum of 6 units.</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>CR/NC grading only.</t>
         </is>
       </c>
-      <c r="L88" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M88" s="2" t="n"/>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="M66" s="2" t="n"/>
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>No units may be applied to the Music major; no more than 3 units may be applied to the Music</t>
         </is>
       </c>
-      <c r="O88" s="2" t="n"/>
-      <c r="P88" s="2" t="n"/>
-      <c r="Q88" s="2" t="n"/>
-      <c r="R88" s="2" t="n"/>
-      <c r="S88" s="3" t="inlineStr">
+      <c r="O66" s="2" t="n"/>
+      <c r="P66" s="2" t="n"/>
+      <c r="Q66" s="2" t="n"/>
+      <c r="R66" s="2" t="n"/>
+      <c r="S66" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9476,7 +7546,7 @@
           </r>
         </is>
       </c>
-      <c r="T88" s="3" t="inlineStr">
+      <c r="T66" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9498,63 +7568,63 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="112" customHeight="1">
-      <c r="A89" s="9" t="inlineStr">
+    <row r="67" ht="112" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>MUS 699</t>
         </is>
       </c>
-      <c r="B89" s="9" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>Departmental Thesis</t>
         </is>
       </c>
-      <c r="C89" s="9" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D89" s="9" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>1–6</t>
         </is>
       </c>
-      <c r="E89" s="9" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>C36 1-6u</t>
         </is>
       </c>
-      <c r="F89" s="9" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>Development and writing of a research paper for submission to the music department, using a department-specified format. Supervision by a departmental committee, at least two of whom must be faculty members of the department of music. Oral defense normally required.</t>
         </is>
       </c>
-      <c r="G89" s="9" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>Department consent</t>
         </is>
       </c>
-      <c r="H89" s="9" t="n"/>
-      <c r="I89" s="9" t="n"/>
-      <c r="J89" s="9" t="inlineStr">
+      <c r="H67" s="8" t="n"/>
+      <c r="I67" s="8" t="n"/>
+      <c r="J67" s="8" t="inlineStr">
         <is>
           <t>May be repeated for credit for a maximum of 6 units.</t>
         </is>
       </c>
-      <c r="K89" s="9" t="inlineStr">
+      <c r="K67" s="8" t="inlineStr">
         <is>
           <t>A-F grading only.</t>
         </is>
       </c>
-      <c r="L89" s="9" t="inlineStr">
+      <c r="L67" s="8" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M89" s="9" t="n"/>
-      <c r="N89" s="9" t="n"/>
-      <c r="O89" s="9" t="n"/>
-      <c r="P89" s="9" t="inlineStr">
+      <c r="M67" s="8" t="n"/>
+      <c r="N67" s="8" t="n"/>
+      <c r="O67" s="8" t="n"/>
+      <c r="P67" s="8" t="inlineStr">
         <is>
           <t>1. Complete in-depth research into selected areas within their particular disciplines.
 2. Demonstrate knowledge of significant scholarship and/or creative output, consistent with standard graduate level expectations, in their respective disciplines.
@@ -9562,13 +7632,13 @@
 4. Present an oral defense of the final document.</t>
         </is>
       </c>
-      <c r="Q89" s="9" t="n"/>
-      <c r="R89" s="9" t="inlineStr">
+      <c r="Q67" s="8" t="n"/>
+      <c r="R67" s="8" t="inlineStr">
         <is>
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="S89" s="10" t="inlineStr">
+      <c r="S67" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9589,10 +7659,10 @@
           </r>
         </is>
       </c>
-      <c r="T89" s="9" t="n"/>
+      <c r="T67" s="8" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T89"/>
+  <autoFilter ref="A1:T67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15450,4 +13520,2074 @@
   <autoFilter ref="A1:T17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
+    <col width="38" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="58.5" customWidth="1" min="19" max="19"/>
+    <col width="64" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>course</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>prerequisites</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>corequisites</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>repeatability</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>grading</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>instructional_methods</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>typically_offered</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>credit_restrictions</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>breadth</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>learning_outcomes</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ge_outcomes</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>last_proposal</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>findings_technical</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>findings_content</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MUS 231</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Basic String Techniques</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>C10 1u</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Presents pedagogy and techniques for teaching violin, viola, cello, and bass in a school ensemble setting.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>1. Learn the basic skills and mechanics involved with playing the violin, viola, cello, and double bass.
+2. Perform scales, studies, and solo material appropriate to elementary-level students.
+3. Implement pedagogical techniques and examine common issues/difficulties appropriate to beginning string students.
+4. Survey and analyze pedagogical materials, e.g. methods and solo literature, for elementary string students.</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>MUS 232</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Basic Woodwind Techniques</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>C10 1u</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Presents pedagogy and techniques for developing performance ability on flute, clarinet, saxophone, oboe, and bassoon.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>1. Learn the basic skills and mechanics involved with playing the flute, clarinet, saxophone, oboe, and bassoon.
+2. Perform scales, studies, and solo material appropriate to elementary-level students.
+3. Implement pedagogical techniques and examine common issues/difficulties appropriate to beginning woodwind students.
+4. Survey and analyze pedagogical materials, e.g. methods and solo literature, for elementary woodwind students.</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>MUS 233</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Basic Brass Techniques</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>C10 1u</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Presents pedagogy and techniques for developing performance ability on trumpet, French horn, trombone, and tuba.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1. Learn the basic skills and mechanics involved with playing the trumpet, French horn, trombone, and tuba.
+2. Perform scales, studies, and solo material appropriate to elementary-level brass students.
+3. Implement pedagogical techniques and examine common issues/difficulties appropriate to beginning brass students.
+4. Survey and analyze pedagogical materials, e.g. methods and solo literature, for elementary brass students.</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>MUS 234</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Basic Percussion Techniques</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>C10 1u</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Presents pedagogy and techniques for developing performance ability on percussion instruments.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>1. Learn the basic skills and mechanics involved with playing and teaching percussion instruments in a school setting.
+2. Perform scales, studies, and solo material appropriate to elementary-level students.
+3. Implement pedagogical techniques and examine common issues/difficulties appropriate to beginning percussion students.
+4. Survey and analyze pedagogical materials, e.g. methods and solo literature, for elementary percussion students.</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="n"/>
+      <c r="T5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>MUS 235</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Basic Guitar Techniques</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>C10 1u</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of playing guitar with emphasis on developing competencies sufficient to employ the instrument in an educational setting.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>1. Learn the basic skills and mechanics involved with playing the guitar and using the guitar as an accompanying instrument.
+2. Perform scales, chords, and solo material appropriate for beginning guitar student.
+3. Implement pedagogical techniques and examine common issues/difficulties appropriate to beginning guitarists.
+4. Survey and analyze pedagogical materials, e.g. methods and solo literature, for beginning guitar students.</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2016-05-01</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">last revised 2016-05-01, still on the 2016 conversion form
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>review the full record on the current form</t>
+          </r>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>MUS 236</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Basic Vocal Techniques</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>C10 1u</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Class instruction in fundamentals of singing.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1. Improve singing through regular practicing of vocal exercises and songs.
+2. Be come familiar with significant sources on vocal pedagogy and the art of singing.
+3. Demonstrate an understanding of the basics of breathing, posture, and good vocal tone production.
+4. Perform vocal music in solo and ensemble settings, demonstrating proper technique.
+5. Gain knowledge of vocal warm-ups and techniques for healthy vocal music as appropriate to a school setting.</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2016-05-01</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">last revised 2016-05-01, still on the 2016 conversion form
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>review the full record on the current form</t>
+          </r>
+        </is>
+      </c>
+      <c r="T7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MUS 238</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Band: Concert Band Workshop</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>C10 1u</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Beginning Inclusive Collegiate Band that is open to all students with instrumental experience. Led by music education majors, the ensemble performs repertoire designed to foster musical growth, practical teaching skills, and collaborative performance.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1 year experience on a band instrument or successful completion of Basic</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>May be repeated for credit for a maximum of 4 units.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>May not be used to satisfy chamber ensemble requirement for BA in music.</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1. Demonstrate developing proficiency on an instrument through consistent participation in an ensemble setting.
+2. Perform elementary-level repertoire appropriate for K-12 school ensembles with accuracy, expression, and ensemble awareness.
+3. Apply fundamental conducting and rehearsal techniques in a live ensemble context.
+4. Integrate prior knowledge of instrumental techniques into a heterogeneous group performance setting.
+5. Collaborate effectively with peers to foster musical growth, ensemble cohesion, and inclusive musicianship.</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>MUS 331</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Foundations of Music Education</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Overview of music education for prospective music educators, with a focus on K-12 music education. Topics include philosophy of music education, K-12 music pedagogy, and the history, economics, and policy of music education. Field trips may be required.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>A-F grading only.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>1. Reflect, analyze, and discuss the student’s own music education experiences,
+2. Demonstrate knowledge of the primary forms of both traditional and non-traditional music education in the contemporary United States,
+3. Observe and reflect on music education in a variety of K-12 school settings,
+4. Demonstrate understanding of major theories and approaches to music teaching and learning, including knowledge of major events in the history of American music education,
+5. Demonstrate knowledge of the California State and National Standards in music education,
+6. Demonstrate knowledge of the roles and issues of cultural diversity and special learners in today’s schools.</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2016-02-18</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">last revised 2016-02-18, still on the 2016 conversion form
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>review the full record on the current form</t>
+          </r>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MUS 335</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Technology for Music Educators</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>C05 1u + C13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Instruction in uses of audio software, and software for desktop, interactive, and music publishing to aid in the development of music education curricula, programs, and lessons. Seminar Units: 2; Activity Units: 1.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1. Mastery of live sound knowledge as it applies to k-12 environments, including microphones, PA setup and; usage, and logistically planning for amplifying ensembles.
+2. Ability to edit and master digital audio using a DAW.
+3. Advocate for music technology needs in the classroom through the drafting of grant proposals.
+4. Utilize music notation software with rehearsal software in order to create lessons and lesson plans otherwise not possible.
+5. Create learning modules in teams using video and audio editing software.</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2016-04-27</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>review the full record on the current form</t>
+          </r>
+        </is>
+      </c>
+      <c r="T10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="126" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>MUS 341</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Basic Conducting</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>C05 2u</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Basic techniques of conducting including simple, compound and asymmetrical meters, expression and interpretation through observation and laboratory experience.</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Junior, senior or post-baccalaureate standing.</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>1. Develop the skills needed by conductors with an emphasis on physical gesture, score study, and expression.
+2. Develop inner hearing and interpretation skills.
+3. Have knowledge of noteworthy conducting scholarship and materials.
+4. Demonstrate understanding via in-class conducting presentations Page: 1 &lt;- Back 10 … 12 | 13 | 14 | 15 | 16 | 17 | 18 | 19 | 20 | 21 | 22 … Forward 10 -&gt; 28 Contract All Courses | Print this Page</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="n"/>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>2016-04-26</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">classification holds 2 units of C05 where the course publishes 3, a quarter-conversion artifact
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>set the classification to C05 3u</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">
+last revised 2016-04-26, still on the 2016 conversion form
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>review the full record on the current form</t>
+          </r>
+        </is>
+      </c>
+      <c r="T11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MUS 431</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Elementary Music Teaching Methods</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>C05 3u</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Designed for prospective school music educators. Development of methods, techniques, and knowledge appropriate for teaching elementary general music classes. Study and exploration of elementary music instructional materials and topics. Field trips may be required.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Junior, senior or post-baccalaureate standing.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>May be repeated for credit for a maximum of 6 units.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1. To study and implement a variety of diverse approaches to teaching music to elementary level students.
+2. To become familiar with the methodologies of Orff, Kodály, Dalcroze, and Gordon (Music Learning Theory).
+3. To write lesson plans in a variety of formats, including the use of state and national standards for elementary general music.
+4. To plan, participate in, and reflect on several peer teaching episodes.
+5. To observe elementary general music teachers (Field Trips May Be Required).
+6. To become familiar with a wide variety of resources for teaching elementary music</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2016-04-27</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>review the full record on the current form</t>
+          </r>
+        </is>
+      </c>
+      <c r="T12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MUS 432</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Instrumental Music Teaching Methods</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>C05 3u</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Provides opportunity for students intending to become music teachers to develop rehearsal techniques, organizational procedures related to public school band and orchestra programs; become familiar with public school teaching materials; further develop conducting techniques; and improve secondary instruments skills.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>MUS 341.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1. To understand a variety of theories regarding the teaching of instrumental music,
+2. To familiarize the student with the National and State standards for instrumental music education and to apply them to instruction,
+3. To become familiar with and evaluate resources,
+4. To further develop score study, transposition, and conducting skills,
+5. To develop rehearsal planning and classroom management skills
+6. To perform on a secondary instrument in an ensemble,
+7. To develop a library of resources for future use as an instrumental music educator,
+8. To observe excellent elementary and secondary school instrumental music teachers. Field Trips May Be Required</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2016-04-27</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>review the full record on the current form</t>
+          </r>
+        </is>
+      </c>
+      <c r="T13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>MUS 433</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Choral Music Teaching Methods</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>C05 3u</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Development of rehearsal techniques and organizational procedures related to choirs and vocal ensembles in the elementary and secondary schools. Teaching materials and appropriate literature from various stylistic periods. Field trips may be required.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>MUS 341.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1. Develop musical, curricular, and organizational skills necessary to lead a choral program at the elementary and secondary level
+2. Refine choral conducting skills, building on the fundamental topics of conducting including inner hearing, breathing, scholarship and expressive interpretation.
+3. Develop knowledge of instructional materials and score-reading ability.
+4. Demonstrate the ability to conduct and teach choral music during in-class experiences.
+5. Develop familiarity with choral music education materials</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2016-04-27</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">last revised 2016-04-27, still on the 2016 conversion form
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>review the full record on the current form</t>
+          </r>
+        </is>
+      </c>
+      <c r="T14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="126" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MUS 441</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Intermediate Conducting</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>C05 2u</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Special techniques of choral conducting including vocal and score reading and analysis, interpretation, and rehearsal through observation and laboratory experience.</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>MUS 341 and junior, senior or post-baccalaureate standing.</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>May be repeated for credit for a maximum of 6 units.</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>1. Demonstrate the ability to analyze and read vocal and instrumental scores
+2. Independently conduct student choral and instrumental groups.
+3. Demonstrate mastery of standard conducting patterns and gestures.
+4. Conduct music in an interpretive and expressive manner.
+5. Demonstrate knowledge of notable conductors and conducting scholarship</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="n"/>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>2016-04-27</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">classification holds 2 units of C05 where the course publishes 3, a quarter-conversion artifact
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>set the classification to C05 3u</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">
+last revised 2016-04-27, still on the 2016 conversion form
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="11"/>
+            </rPr>
+            <t>review the full record on the current form</t>
+          </r>
+        </is>
+      </c>
+      <c r="T15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>MUS 445</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Piano Pedagogy</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>C02 2u</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>A comparison and analysis of current pedagogical approaches to the teaching of piano with attention to specific problems of the literature and technique, including appropriate studies in anatomy, physiology, and acoustics; particular emphasis upon the teaching of the younger student.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>May be repeated for credit for a maximum of 6 units.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Fall Alternate Years</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1. To establish an understanding of the layering of pedagogical concepts and skills in increasing levels of complexity
+2. To provide a structured and critical study of the most popular of the current beginning methods books and supplementary materials
+3. To study how learning takes place through an introductory survey of learning theories
+4. To make an in-depth study of the history and development of thought on piano technique, and its application to healthy practice techniques
+5. To cultivate awareness of effective teaching fundamentals of making music at the piano, including stylistic and expressive repertoire performance, and providing a solid technical foundation
+6. To prepare well-balanced and well-sequenced lesson plans and longer-term programs of study for students of various advancement levels</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>MUS 446</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Vocal Pedagogy</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to professional voice teaching. Examines methods, materials, resources, and techniques for teaching beginning voice students. Students will learn vocal anatomy, observe vocal instruction, and survey beginning and intermediate vocal repertoire.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>MUS 112, MUS 116.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>May be repeated for credit for a maximum of 4 units.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice).</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>On-ground, or Hybrid, or Online-Asynchronous.</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1. Develop pedagogical skills for teaching the beginning voice student
+2. Evaluate methods and materials available to the voice teacher
+3. Observe and analyze university-level secondary group voice classes
+4. Develop the ability to plan private lessons for peer and instructor feedback
+5. Explore the business aspects of operating an independent vocal studio
+6. Articulate a studio policy and marketing strategy
+7. Evaluate online and print resources relating to professional voice teaching including journals, magazines, books and conferences proceedings</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2019-02-17</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>MUS 495</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Music Education Practicum</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>C04 1u + C08</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Practicum experience in K-12 public school class and rehearsal settings, involving observation and teaching under the supervision of music faculty. Focus on practical skills. Regularly scheduled seminars. Field trips required.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Department consent.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>A-F grading only.</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Only open for credit to music education majors participating in the music single subject matter</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>1. Observe outstanding music teachers in authentic K-12 school based classroom and rehearsal settings.
+2. Observe a variety of age levels and disciplines.
+3. Experience periodic, supervised teaching experiences.
+4. Participate in regular seminars.
+5. Relate experiences to current, relevant issues, such as cultural and other forms of diversity, significant national and global events, etc</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2016-05-13</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">units publish as 1 where the record holds 2
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set units to 1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+last revised 2016-05-13, still on the 2016 conversion form
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>review the full record on the current form</t>
+          </r>
+        </is>
+      </c>
+      <c r="T18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>MUS 497</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Contemporary Issues in Music Education</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Music: Music Education</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>C05 3u</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Examination, discussion, and analysis of topics of consequence related to contemporary music teaching and learning.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>May be repeated for credit for a maximum of 6 units.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>A-F grading only.</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1. Examine, discuss, and analyze topics of consequence in contemporary music education.
+2. Present original views and conclusions related to contemporary music education.
+3. Relate contemporary events to prior events/developments in the field music education.
+4. Relate current issues to their implementation in contemporary school-based music education.</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2016-05-01</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">last revised 2016-05-01, still on the 2016 conversion form
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>review the full record on the current form</t>
+          </r>
+        </is>
+      </c>
+      <c r="T19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>MUS 631</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Teaching Music in Higher Education</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Music: Graduate Studies</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>C05 2u</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Preparation for careers in post-secondary education. Study of learning theories, curriculum development, assessment, and materials for teaching music in higher education.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>M.A. Music major.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>A-F grading only.</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>On-ground or Hybrid.</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Spring Alternate Years</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1. Become familiar with a variety of teaching techniques/situations, such as lectures, small groups, individual lessons, and small/large ensemble rehearsals.
+2. Create curricular materials such as lesson/rehearsal plans and syllabi.
+3. Participate in peer teaching situations.
+4. Survey current resources/practices in higher education, i.e. textbooks, online/hybrid options, etc.
+5. Create a CV and participate in a mock job interview for a college/university position.</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="n"/>
+      <c r="T20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>MUS 633</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Pedagogy of Music Theory</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Music: Graduate Studies</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Materials, organization, techniques, and problems of the first two years of collegiate theory and musicianship teaching. Bibliographical survey of texts and materials, sample teaching, and observation of collegiate theory classes.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Department consent.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Baccalaureate degree in music.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>A-F grading only.</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>1. Demonstrate familiarity with a variety of developmentally appropriate strategies for teaching collegiate music theory.
+2. Design instruction using a variety of modalities, accounting for learner differences.
+3. Demonstrate familiarity with and ability to evaluate curricular materials for music theory and musicianship (i.e. aural skills).
+4. Demonstrate familiarity with a variety of systems for rhythm (i.e Cheve, Gordon, takadimi), melody (solfegge), and overall approach (i.e. Kodaly).</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2019-02-15</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="n"/>
+      <c r="T21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>MUS 638</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>History and Philosophy of Music Education</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Music: Graduate Studies</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Study of historical and philosophical trends in music education, with an emphasis on their application to current practices, scholarship, and policy in music teaching and learning.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Department consent.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>A-F grading only.</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1. Read complex texts, create original arguments, analyze the arguments of others, and express these criticisms orally and in writing.
+2. Demonstrate knowledge of major philosophers in music and music education, their relevant concepts, theories, methods, and historical contexts.
+3. Relate significant significant topic in the history and philosophy of music education to current events in K-12 music education.
+4. Demonstrate knowledge of major historical movements and events in music education and relate them to modern movements and events in music education.
+5. Cultivate an appreciation for a diversity of ideas and values across time and for human difference in areas such as: religion, culture, ethnicity, race, class, sexuality, and gender.</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2019-02-15</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="70" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>MUS 671</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Kodály Pedagogy</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Music: Graduate Studies</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>C10 1u</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>An introduction to the philosophy and practice of the Kodály-based curriculum of music teaching and learning. Curriculum development, teaching techniques, lesson planning and supportive song literature including singing games and dances.</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Baccalaureate degree in music; School teaching experience in music</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Repeatable for credit up to 4 units.</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>A-F or CR/NC (student choice)</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>On-ground.</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>Variable Intermittently</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="6" t="n"/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">no learning outcomes published
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>add learning outcomes</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+repeatability uses non-standard phrasing
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>reword to may be repeated for credit for a maximum of 4 units</t>
+          </r>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">no outcomes published
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>to be drafted by area faculty</t>
+          </r>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:T23"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -6768,19 +6768,11 @@
           <r>
             <rPr>
               <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reword to may be repeated for credit for a maximum of 4 units</t>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>bank</t>
           </r>
         </is>
       </c>
@@ -6858,61 +6850,15 @@
           <r>
             <rPr>
               <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no learning outcomes published
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>add learning outcomes</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-repeatability uses non-standard phrasing
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reword to may be repeated for credit for a maximum of 4 units</t>
-          </r>
-        </is>
-      </c>
-      <c r="T60" s="7" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no outcomes published
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>to be drafted by area faculty</t>
-          </r>
-        </is>
-      </c>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>bank</t>
+          </r>
+        </is>
+      </c>
+      <c r="T60" s="7" t="n"/>
     </row>
     <row r="61" ht="112" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
@@ -7112,61 +7058,15 @@
           <r>
             <rPr>
               <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">description runs to 42 words, over the 40-word limit
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>shorten to 40 words or fewer</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-last revised 2016-02-26, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
-          </r>
-        </is>
-      </c>
-      <c r="T62" s="9" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">description
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Development and completion of a formal written thesis for submission to the university. Supervision by a departmental committee, at least one member of which must be a Cal State East Bay faculty member. Oral defense required.</t>
-          </r>
-        </is>
-      </c>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>discontinue</t>
+          </r>
+        </is>
+      </c>
+      <c r="T62" s="9" t="n"/>
     </row>
     <row r="63" ht="112" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
@@ -7242,19 +7142,11 @@
           <r>
             <rPr>
               <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">units publish as 1-6 where the record holds 6
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set units to 1-6</t>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>discontinue</t>
           </r>
         </is>
       </c>
@@ -7426,19 +7318,11 @@
           <r>
             <rPr>
               <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">last revised 2016-02-26, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>bank</t>
           </r>
         </is>
       </c>
@@ -7643,19 +7527,11 @@
           <r>
             <rPr>
               <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">units publish as 1-6 where the record holds 6
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set units to 1-6</t>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>discontinue</t>
           </r>
         </is>
       </c>
@@ -15530,61 +15406,15 @@
           <r>
             <rPr>
               <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no learning outcomes published
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>add learning outcomes</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-repeatability uses non-standard phrasing
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reword to may be repeated for credit for a maximum of 4 units</t>
-          </r>
-        </is>
-      </c>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">no outcomes published
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>to be drafted by area faculty</t>
-          </r>
-        </is>
-      </c>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>bank</t>
+          </r>
+        </is>
+      </c>
+      <c r="T23" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T23"/>

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -1157,27 +1157,7 @@
           <t>2023-09-14</t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reword to may be repeated for credit for a maximum of 6 units</t>
-          </r>
-        </is>
-      </c>
+      <c r="S8" s="3" t="n"/>
       <c r="T8" s="2" t="n"/>
     </row>
     <row r="9">
@@ -1250,27 +1230,7 @@
           <t>2023-09-14</t>
         </is>
       </c>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reword to may be repeated for credit for a maximum of 3 units</t>
-          </r>
-        </is>
-      </c>
+      <c r="S9" s="3" t="n"/>
       <c r="T9" s="2" t="n"/>
     </row>
     <row r="10" ht="126" customHeight="1">
@@ -4310,24 +4270,6 @@
               <sz val="10"/>
             </rPr>
             <t>add learning outcomes</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-repeatability uses non-standard phrasing
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reword to may be repeated for credit for a maximum of 9 units</t>
           </r>
         </is>
       </c>
@@ -11546,27 +11488,7 @@
           <t>2025-09-14</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reword to may be repeated for credit for a maximum of 8 units</t>
-          </r>
-        </is>
-      </c>
+      <c r="S2" s="3" t="n"/>
       <c r="T2" s="2" t="n"/>
     </row>
     <row r="3">
@@ -11951,27 +11873,7 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reword to may be repeated for credit for a maximum of 8 units</t>
-          </r>
-        </is>
-      </c>
+      <c r="S6" s="3" t="n"/>
       <c r="T6" s="3" t="inlineStr">
         <is>
           <r>
@@ -12076,25 +11978,7 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">repeatability uses non-standard phrasing
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reword to may be repeated for credit for a maximum of 8 units</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-grading A-F or CR/NC (student choice) where the chamber ensemble norm is A-F or CR/NC (student choice)
+            <t xml:space="preserve">grading A-F or CR/NC (student choice) where the chamber ensemble norm is A-F or CR/NC (student choice)
 </t>
           </r>
           <r>
@@ -12591,24 +12475,6 @@
               <sz val="10"/>
             </rPr>
             <t>shorten to 40 words or fewer</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-repeatability uses non-standard phrasing
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reword to may be repeated for credit for a maximum of 8 units</t>
           </r>
         </is>
       </c>

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -4259,7 +4259,27 @@
           <t>2020-10-06</t>
         </is>
       </c>
-      <c r="S33" s="5" t="n"/>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">the three Diversity Overlay outcomes sit in the course learning outcomes, and no course outcomes are published
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>add course learning outcomes and hold the overlay outcomes as breadth outcomes</t>
+          </r>
+        </is>
+      </c>
       <c r="T33" s="4" t="n"/>
     </row>
     <row r="34" ht="70" customHeight="1" s="12">

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -1364,7 +1364,7 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">corequisite carries no equivalence or consent path for transfer students
+            <t xml:space="preserve">prerequisite names the Music Theory Advisory Exam, no longer administered, and carries no equivalence or consent path
 </t>
           </r>
           <r>
@@ -1837,7 +1837,7 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-corequisite names MUS 118B, renumbered to MUS 119 in September 2019
+prerequisite carries no equivalence or consent path
 </t>
           </r>
           <r>
@@ -1855,7 +1855,7 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-corequisite carries no equivalence or consent path
+corequisite names MUS 118B, renumbered to MUS 119 in September 2019, and carries no equivalence or consent path
 </t>
           </r>
           <r>
@@ -2462,7 +2462,7 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-corequisite carries no equivalence or consent path for transfer students
+prerequisite carries no equivalence or consent path for transfer students
 </t>
           </r>
           <r>
@@ -2633,7 +2633,7 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-prerequisite and corequisite differ from the syllabus and carry no equivalence or consent path
+prerequisite names MUS 112 and MUS 116 where the syllabus names MUS 116, and carries no equivalence or consent path
 </t>
           </r>
           <r>
@@ -3019,17 +3019,17 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-05-09, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
+            <t xml:space="preserve">fixed at 1 unit, so a recitalist cannot enroll in the 2 units the handbook requires in the recital semester
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set units to 1–2</t>
           </r>
           <r>
             <rPr>
@@ -3037,17 +3037,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-classified S36 where other studio courses are C36
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reclassify to C36</t>
+classified S36 where the rest of the coaching series is C36
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>reclassify to C36 1u</t>
           </r>
           <r>
             <rPr>
@@ -3055,17 +3055,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-fixed at 1 unit, so a recitalist cannot enroll in the 2 units the handbook requires in the recital semester
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set units to 1–2</t>
+description is identical to MUS 481 and carries no level marker
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>revise the description</t>
           </r>
           <r>
             <rPr>
@@ -3073,17 +3073,35 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-no credit restriction published, though the handbook states coaching units do not count toward graduation requirements
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>add: Units may not be used towards the Music Major or Minor.</t>
+learning outcomes are identical to MUS 282, MUS 481, and MUS 482, are written for applied study, and name the primary instrument on a vocal course
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>revise the learning outcomes</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+repeat cap differs across the coaching series
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set repeatability to may be repeated for credit for a maximum of 16 units</t>
           </r>
         </is>
       </c>
@@ -3104,7 +3122,7 @@
               <color rgb="FFB03A2E"/>
               <sz val="10"/>
             </rPr>
-            <t>Individual coaching with a faculty coach on repertoire requiring a collaborative pianist, for students enrolled in applied study. Coaching times are arranged according to degree recital expectations. Requirements appear in the Music Student Handbook.</t>
+            <t>Individual vocal coaching with a collaborative pianist for music majors and minors at the lower division performance level. Coaching times arranged according to the expectations in the Music Student Handbook.</t>
           </r>
           <r>
             <rPr>
@@ -3112,17 +3130,20 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-outcomes are the generic applied study set, and outcome 2 addresses tone production on the primary instrument
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Prepare repertoire with a collaborative pianist to a performance standard. 2. Apply rehearsal technique to balance, ensemble coordination, and pacing with a collaborator. 3. Communicate interpretive decisions clearly to collaborating musicians. 4. Perform prepared repertoire with a collaborative pianist in juries and recitals.</t>
+learning outcomes
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Prepare vocal repertoire with a collaborative pianist, marking and rehearsing entrances, cutoffs, tempo, and balance.
+2. Apply diction and text translation to the delivery of the repertoire.
+3. Rehearse and perform with a collaborative pianist, responding to the accompaniment in the moment.
+4. Document the preparation of a work from first rehearsal to performance.</t>
           </r>
         </is>
       </c>
@@ -3212,17 +3233,17 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">last revised 2016-05-09, still on the 2016 conversion form
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>review the full record on the current form</t>
+            <t xml:space="preserve">fixed at 1 unit, so a recitalist cannot enroll in the 2 units the handbook requires in the recital semester
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set units to 1–2</t>
           </r>
           <r>
             <rPr>
@@ -3230,17 +3251,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-classified S36 where other studio courses are C36
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>reclassify to C36</t>
+classified S36 where the rest of the coaching series is C36
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>reclassify to C36 1u</t>
           </r>
           <r>
             <rPr>
@@ -3248,17 +3269,17 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-fixed at 1 unit, so a recitalist cannot enroll in the 2 units the handbook requires in the recital semester
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set units to 1–2</t>
+description is identical to MUS 482 and carries no level marker
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>revise the description</t>
           </r>
           <r>
             <rPr>
@@ -3266,17 +3287,35 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-no credit restriction published, though the handbook states coaching units do not count toward graduation requirements
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>add: Units may not be used towards the Music Major or Minor.</t>
+learning outcomes are identical to MUS 281, MUS 481, and MUS 482 and are written for applied study
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>revise the learning outcomes</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+repeat cap differs across the coaching series
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set repeatability to may be repeated for credit for a maximum of 16 units</t>
           </r>
         </is>
       </c>
@@ -3297,7 +3336,7 @@
               <color rgb="FFB03A2E"/>
               <sz val="10"/>
             </rPr>
-            <t>Individual coaching with a faculty coach on repertoire requiring a collaborative pianist, for students enrolled in applied study. Coaching times are arranged according to degree recital expectations. Requirements appear in the Music Student Handbook.</t>
+            <t>Individual instrumental coaching with a collaborative pianist for music majors and minors at the lower division performance level. Coaching times arranged according to the expectations in the Music Student Handbook.</t>
           </r>
           <r>
             <rPr>
@@ -3305,17 +3344,20 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-outcomes are the generic applied study set, and outcome 2 addresses tone production on the primary instrument
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Prepare repertoire with a collaborative pianist to a performance standard. 2. Apply rehearsal technique to balance, ensemble coordination, and pacing with a collaborator. 3. Communicate interpretive decisions clearly to collaborating musicians. 4. Perform prepared repertoire with a collaborative pianist in juries and recitals.</t>
+learning outcomes
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Prepare repertoire with a collaborative pianist, marking and rehearsing entrances, cutoffs, tempo, and balance.
+2. Apply articulation, phrasing, and intonation decisions to the delivery of the repertoire.
+3. Rehearse and perform with a collaborative pianist, responding to the accompaniment in the moment.
+4. Document the preparation of a work from first rehearsal to performance.</t>
           </r>
         </is>
       </c>
@@ -4977,17 +5019,71 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no credit restriction published, though the handbook states coaching units do not count toward graduation requirements
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>add: Units may not be used towards the Music Major or Minor.</t>
+            <t xml:space="preserve">classification records a 1-2 unit range where each unit carries the classification
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set the classification to C36 1u</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+description is identical to MUS 281 and carries no level marker
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>revise the description</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+learning outcomes are identical to MUS 281, MUS 282, and MUS 482, are written for applied study, and name the primary instrument on a vocal course
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>revise the learning outcomes</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+repeat cap differs across the coaching series
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set repeatability to may be repeated for credit for a maximum of 16 units</t>
           </r>
         </is>
       </c>
@@ -5008,7 +5104,7 @@
               <color rgb="FFB03A2E"/>
               <sz val="10"/>
             </rPr>
-            <t>Individual coaching with a faculty coach on repertoire requiring a collaborative pianist, for students enrolled in upper division applied study. Coaching times are arranged according to degree recital expectations. Requirements appear in the Music Student Handbook.</t>
+            <t>Individual vocal coaching with a collaborative pianist for music majors and minors at the upper division performance level, in preparation for the junior and senior recitals. Coaching times arranged according to the expectations in the Music Student Handbook.</t>
           </r>
           <r>
             <rPr>
@@ -5016,17 +5112,20 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-outcomes are the generic applied study set, and outcome 2 addresses tone production on the primary instrument
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Prepare repertoire with a collaborative pianist to a performance standard. 2. Apply rehearsal technique to balance, ensemble coordination, and pacing with a collaborator. 3. Communicate interpretive decisions clearly to collaborating musicians. 4. Perform prepared repertoire with a collaborative pianist in juries and recitals.</t>
+learning outcomes
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Build a recital program with a collaborative pianist, taking responsibility for repertoire, order, and pacing.
+2. Apply diction, translation, and poetic interpretation across repertoire in more than one language.
+3. Lead rehearsals with a collaborative pianist, setting the interpretive decisions and revising them across the preparation.
+4. Perform a program that meets the recital requirements in the Music Student Handbook.</t>
           </r>
         </is>
       </c>
@@ -5116,17 +5215,71 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">no credit restriction published, though the handbook states coaching units do not count toward graduation requirements
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>add: Units may not be used towards the Music Major or Minor.</t>
+            <t xml:space="preserve">classification records a 1-2 unit range where each unit carries the classification
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set the classification to C36 1u</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+description is identical to MUS 282 and carries no level marker
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>revise the description</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+learning outcomes are identical to MUS 281, MUS 282, and MUS 481 and are written for applied study
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>revise the learning outcomes</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+repeat cap differs across the coaching series
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set repeatability to may be repeated for credit for a maximum of 16 units</t>
           </r>
         </is>
       </c>
@@ -5147,7 +5300,7 @@
               <color rgb="FFB03A2E"/>
               <sz val="10"/>
             </rPr>
-            <t>Individual coaching with a faculty coach on repertoire requiring a collaborative pianist, for students enrolled in upper division applied study. Coaching times are arranged according to degree recital expectations. Requirements appear in the Music Student Handbook.</t>
+            <t>Individual instrumental coaching with a collaborative pianist for music majors and minors at the upper division performance level, in preparation for the junior and senior recitals. Coaching times arranged according to the expectations in the Music Student Handbook.</t>
           </r>
           <r>
             <rPr>
@@ -5155,17 +5308,20 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-outcomes are the generic applied study set, and outcome 2 addresses tone production on the primary instrument
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1. Prepare repertoire with a collaborative pianist to a performance standard. 2. Apply rehearsal technique to balance, ensemble coordination, and pacing with a collaborator. 3. Communicate interpretive decisions clearly to collaborating musicians. 4. Perform prepared repertoire with a collaborative pianist in juries and recitals.</t>
+learning outcomes
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Build a recital program with a collaborative pianist, taking responsibility for repertoire, order, and pacing.
+2. Apply articulation, phrasing, intonation, and stylistic decisions across repertoire from more than one period.
+3. Lead rehearsals with a collaborative pianist, setting the interpretive decisions and revising them across the preparation.
+4. Perform a program that meets the recital requirements in the Music Student Handbook.</t>
           </r>
         </is>
       </c>
@@ -5472,17 +5628,17 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">units publish as 1-3 where the record holds 1
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set units to 1-3</t>
+            <t xml:space="preserve">record holds 1 unit where the catalog publishes 1–3
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>correct the record to 1–3</t>
           </r>
           <r>
             <rPr>
@@ -5490,21 +5646,98 @@
               <sz val="10"/>
             </rPr>
             <t xml:space="preserve">
-record holds 1 unit where the catalog and handbook give 1–3
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>correct the record to 1–3</t>
-          </r>
-        </is>
-      </c>
-      <c r="T46" s="4" t="n"/>
+credit restriction keeps internship units off the major and minor
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>remove the credit restriction</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+description is the university-wide internship text, shared with every department
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>revise the description</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+learning outcomes state that outcomes vary
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>revise the learning outcomes</t>
+          </r>
+        </is>
+      </c>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Supervised work in a music-related organization or with a working musician, arranged through the department. Students hold assigned responsibilities and report on the placement.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+learning outcomes
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Apply musical, technical, and organizational skills from the curriculum in a working setting.
+2. Hold assigned responsibilities and meet the deadlines the placement sets.
+3. Communicate with supervisors, colleagues, and audiences in the conventions of the workplace.
+4. Document the work completed and what it contributed to the organization.</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -6348,9 +6581,65 @@
             </rPr>
             <t>remove or apply it across the series</t>
           </r>
-        </is>
-      </c>
-      <c r="T57" s="4" t="n"/>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+description is identical to MUS 660B and does not name voice
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>revise the description</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+repeat cap differs across the coaching series
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set repeatability to may be repeated for credit for a maximum of 16 units</t>
+          </r>
+        </is>
+      </c>
+      <c r="T57" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Individual vocal coaching with a collaborative pianist for graduate students, in preparation for the graduate recital. Coaching times arranged according to the expectations in the Graduate Student Handbook.</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="58" ht="140" customHeight="1" s="12">
       <c r="A58" s="4" t="inlineStr">
@@ -6462,9 +6751,65 @@
             </rPr>
             <t>remove or apply it across the series</t>
           </r>
-        </is>
-      </c>
-      <c r="T58" s="4" t="n"/>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+description is identical to MUS 660A and does not name instruments
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>revise the description</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+repeat cap differs across the coaching series
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set repeatability to may be repeated for credit for a maximum of 16 units</t>
+          </r>
+        </is>
+      </c>
+      <c r="T58" s="4" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Individual instrumental coaching with a collaborative pianist for graduate students, in preparation for the graduate recital. Coaching times arranged according to the expectations in the Graduate Student Handbook.</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="59" ht="140" customHeight="1" s="12">
       <c r="A59" s="6" t="inlineStr">
@@ -7049,7 +7394,7 @@
       <c r="T65" s="6" t="n"/>
     </row>
     <row r="66" s="12">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>MUS 698</t>
         </is>
@@ -7059,60 +7404,157 @@
           <t>Internship</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>Music: Graduate Studies</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>1–3</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>Formal advanced work opportunities integrating the academic program with their career aspirations. Integral advanced hands-on experience enhancing education and preparing for professional and personal success.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>Department consent and minimum 2.0 GPA.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="n"/>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="inlineStr">
         <is>
           <t>May be repeated with department consent for a maximum of 6 units.</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K66" s="4" t="inlineStr">
         <is>
           <t>CR/NC grading only.</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="L66" s="4" t="inlineStr">
         <is>
           <t>On-ground.</t>
         </is>
       </c>
-      <c r="M66" s="2" t="n"/>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="4" t="inlineStr">
         <is>
           <t>No units may be applied to the Music major; no more than 3 units may be applied to the Music</t>
         </is>
       </c>
-      <c r="O66" s="2" t="n"/>
-      <c r="P66" s="2" t="n"/>
-      <c r="Q66" s="2" t="n"/>
-      <c r="R66" s="2" t="n"/>
-      <c r="S66" s="3" t="n"/>
-      <c r="T66" s="3" t="n"/>
+      <c r="O66" s="4" t="n"/>
+      <c r="P66" s="4" t="n"/>
+      <c r="Q66" s="4" t="n"/>
+      <c r="R66" s="4" t="n"/>
+      <c r="S66" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">no proposal on record in the Curriculog archive under 698 or a predecessor number
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>confirm with APS where the record sits</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+description is the university-wide internship text with advanced inserted twice
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>revise the description</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+no learning outcomes published
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>add learning outcomes</t>
+          </r>
+        </is>
+      </c>
+      <c r="T66" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Supervised professional work in a music-related organization, arranged through the department. Students hold assigned responsibilities at a level consistent with graduate study and report on the placement.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+learning outcomes
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>1. Apply graduate-level musical and professional skills in a working setting.
+2. Hold assigned responsibilities and meet the deadlines the placement sets.
+3. Communicate with supervisors, colleagues, and audiences in the conventions of the workplace.
+4. Evaluate the placement against the aims of the degree and their own professional plans.</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="67" ht="112" customHeight="1" s="12">
       <c r="A67" s="8" t="inlineStr">

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -3047,7 +3047,7 @@
               <color rgb="FFB03A2E"/>
               <sz val="10"/>
             </rPr>
-            <t>reclassify to C36 1u</t>
+            <t>reclassify to C36 1-2u</t>
           </r>
           <r>
             <rPr>
@@ -3084,24 +3084,6 @@
               <sz val="10"/>
             </rPr>
             <t>revise the learning outcomes</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-repeat cap differs across the coaching series
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set repeatability to may be repeated for credit for a maximum of 16 units</t>
           </r>
         </is>
       </c>
@@ -3261,7 +3243,7 @@
               <color rgb="FFB03A2E"/>
               <sz val="10"/>
             </rPr>
-            <t>reclassify to C36 1u</t>
+            <t>reclassify to C36 1-2u</t>
           </r>
           <r>
             <rPr>
@@ -3298,24 +3280,6 @@
               <sz val="10"/>
             </rPr>
             <t>revise the learning outcomes</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-repeat cap differs across the coaching series
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set repeatability to may be repeated for credit for a maximum of 16 units</t>
           </r>
         </is>
       </c>
@@ -5019,25 +4983,7 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">classification records a 1-2 unit range where each unit carries the classification
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set the classification to C36 1u</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-description is identical to MUS 281 and carries no level marker
+            <t xml:space="preserve">description is identical to MUS 281 and carries no level marker
 </t>
           </r>
           <r>
@@ -5066,24 +5012,6 @@
               <sz val="10"/>
             </rPr>
             <t>revise the learning outcomes</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-repeat cap differs across the coaching series
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set repeatability to may be repeated for credit for a maximum of 16 units</t>
           </r>
         </is>
       </c>
@@ -5215,25 +5143,7 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">classification records a 1-2 unit range where each unit carries the classification
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set the classification to C36 1u</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-description is identical to MUS 282 and carries no level marker
+            <t xml:space="preserve">description is identical to MUS 282 and carries no level marker
 </t>
           </r>
           <r>
@@ -5262,24 +5172,6 @@
               <sz val="10"/>
             </rPr>
             <t>revise the learning outcomes</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-repeat cap differs across the coaching series
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set repeatability to may be repeated for credit for a maximum of 16 units</t>
           </r>
         </is>
       </c>
@@ -6569,7 +6461,25 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">prerequisite of department consent, absent on most graduate applied courses
+            <t xml:space="preserve">classification records 1 unit where the course publishes 1–2
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set the classification to C36 1-2u</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+prerequisite of department consent, absent on most graduate applied courses
 </t>
           </r>
           <r>
@@ -6598,24 +6508,6 @@
               <sz val="10"/>
             </rPr>
             <t>revise the description</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-repeat cap differs across the coaching series
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set repeatability to may be repeated for credit for a maximum of 16 units</t>
           </r>
         </is>
       </c>
@@ -6721,7 +6613,25 @@
               <rFont val="Arial"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">requires MUS 669, renumbered or discontinued
+            <t xml:space="preserve">classification records 1 unit where the course publishes 1–2
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="FFB03A2E"/>
+              <sz val="10"/>
+            </rPr>
+            <t>set the classification to C36 1-2u</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+requires MUS 669, renumbered or discontinued
 </t>
           </r>
           <r>
@@ -6768,24 +6678,6 @@
               <sz val="10"/>
             </rPr>
             <t>revise the description</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">
-repeat cap differs across the coaching series
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="FFB03A2E"/>
-              <sz val="10"/>
-            </rPr>
-            <t>set repeatability to may be repeated for credit for a maximum of 16 units</t>
           </r>
         </is>
       </c>

--- a/curriculum/catalog-audit/course-inventory.xlsx
+++ b/curriculum/catalog-audit/course-inventory.xlsx
@@ -6473,7 +6473,7 @@
       <c r="T9" s="3"/>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="2:21" ht="126" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B10" s="4" t="s">
         <v>79</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="2:21" ht="224" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
         <v>88</v>
       </c>
@@ -6577,7 +6577,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="2:21" ht="182" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B12" s="4" t="s">
         <v>97</v>
       </c>
@@ -6627,7 +6627,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="238" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
         <v>104</v>
       </c>
@@ -6679,7 +6679,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="2:21" ht="196" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B14" s="4" t="s">
         <v>110</v>
       </c>
@@ -6727,7 +6727,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="2:21" ht="252" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
         <v>117</v>
       </c>
@@ -6873,7 +6873,7 @@
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
     </row>
-    <row r="18" spans="1:21" ht="182" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B18" s="4" t="s">
         <v>141</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="210" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B19" s="4" t="s">
         <v>151</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="252" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
         <v>158</v>
       </c>
@@ -7075,7 +7075,7 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
     </row>
-    <row r="22" spans="1:21" ht="182" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B22" s="4" t="s">
         <v>169</v>
       </c>
@@ -7129,7 +7129,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="182" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B23" s="4" t="s">
         <v>181</v>
       </c>
@@ -7391,7 +7391,7 @@
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
     </row>
-    <row r="28" spans="1:21" ht="266" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B28" s="4" t="s">
         <v>214</v>
       </c>
@@ -7491,7 +7491,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="30" spans="1:21" s="12" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
         <v>797</v>
       </c>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="U30" s="6"/>
     </row>
-    <row r="31" spans="1:21" s="12" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="17" t="s">
         <v>797</v>
       </c>
@@ -7633,7 +7633,7 @@
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
     </row>
-    <row r="33" spans="1:21" s="11" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:21" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="17"/>
       <c r="B33" s="4" t="s">
         <v>249</v>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="U33" s="4"/>
     </row>
-    <row r="34" spans="1:21" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B34" s="4" t="s">
         <v>256</v>
       </c>
@@ -7730,7 +7730,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="35" spans="1:21" s="12" customFormat="1" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
         <v>797</v>
       </c>
@@ -7825,7 +7825,7 @@
       <c r="T36" s="3"/>
       <c r="U36" s="2"/>
     </row>
-    <row r="37" spans="1:21" ht="293" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B37" s="4" t="s">
         <v>276</v>
       </c>
@@ -7917,7 +7917,7 @@
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
     </row>
-    <row r="39" spans="1:21" ht="28" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>287</v>
       </c>
@@ -8007,7 +8007,7 @@
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
     </row>
-    <row r="41" spans="1:21" ht="182" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B41" s="4" t="s">
         <v>296</v>
       </c>
@@ -8061,7 +8061,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="182" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B42" s="4" t="s">
         <v>303</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
         <v>306</v>
       </c>
@@ -8161,7 +8161,7 @@
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
     </row>
-    <row r="44" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>312</v>
       </c>
@@ -8255,7 +8255,7 @@
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
     </row>
-    <row r="46" spans="1:21" s="11" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:21" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="17"/>
       <c r="B46" s="4" t="s">
         <v>324</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="U47" s="2"/>
     </row>
-    <row r="48" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
         <v>343</v>
       </c>
@@ -8402,7 +8402,7 @@
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
     </row>
-    <row r="49" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
         <v>350</v>
       </c>
@@ -8446,7 +8446,7 @@
       <c r="T49" s="2"/>
       <c r="U49" s="2"/>
     </row>
-    <row r="50" spans="1:21" ht="145" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B50" s="4" t="s">
         <v>354</v>
       </c>
@@ -8490,7 +8490,7 @@
       <c r="T50" s="4"/>
       <c r="U50" s="4"/>
     </row>
-    <row r="51" spans="1:21" ht="148" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B51" s="4" t="s">
         <v>357</v>
       </c>
@@ -8578,7 +8578,7 @@
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
     </row>
-    <row r="53" spans="1:21" ht="28" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
         <v>365</v>
       </c>
@@ -8622,7 +8622,7 @@
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
     </row>
-    <row r="54" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
         <v>370</v>
       </c>
@@ -8760,7 +8760,7 @@
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
     </row>
-    <row r="57" spans="1:21" ht="146" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B57" s="4" t="s">
         <v>387</v>
       </c>
@@ -8812,7 +8812,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="166" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B58" s="4" t="s">
         <v>395</v>
       </c>
@@ -8864,7 +8864,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="59" spans="1:21" s="20" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:21" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="16"/>
       <c r="B59" s="18" t="s">
         <v>402</v>
@@ -8913,7 +8913,7 @@
       <c r="T59" s="19"/>
       <c r="U59" s="18"/>
     </row>
-    <row r="60" spans="1:21" s="20" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:21" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="16"/>
       <c r="B60" s="18" t="s">
         <v>410</v>
@@ -8960,7 +8960,7 @@
       <c r="T60" s="19"/>
       <c r="U60" s="19"/>
     </row>
-    <row r="61" spans="1:21" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
         <v>414</v>
       </c>
@@ -9004,7 +9004,7 @@
       <c r="T61" s="3"/>
       <c r="U61" s="3"/>
     </row>
-    <row r="62" spans="1:21" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A62" s="17" t="s">
         <v>797</v>
       </c>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="U62" s="9"/>
     </row>
-    <row r="63" spans="1:21" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A63" s="17" t="s">
         <v>797</v>
       </c>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="U63" s="8"/>
     </row>
-    <row r="64" spans="1:21" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B64" s="4" t="s">
         <v>433</v>
       </c>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="U64" s="4"/>
     </row>
-    <row r="65" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B65" s="6" t="s">
         <v>440</v>
       </c>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="U65" s="6"/>
     </row>
-    <row r="66" spans="1:21" ht="167" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B66" s="4" t="s">
         <v>445</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A67" s="17" t="s">
         <v>797</v>
       </c>
